--- a/10_要件/SERP100_帳票定義書_環境証明書申請内容.xlsx
+++ b/10_要件/SERP100_帳票定義書_環境証明書申請内容.xlsx
@@ -1,10 +1,11 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="4" rupBuild="14420"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="27932"/>
   <workbookPr filterPrivacy="1" showInkAnnotation="0" codeName="ThisWorkbook"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5A622AC4-3051-4700-81D6-B034C98E390B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="930" yWindow="75" windowWidth="15120" windowHeight="7455"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="表紙" sheetId="9" r:id="rId1"/>
@@ -19,12 +20,64 @@
     <definedName name="関連表" localSheetId="2" hidden="1">#REF!</definedName>
     <definedName name="関連表" hidden="1">#REF!</definedName>
   </definedNames>
-  <calcPr calcId="162913"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
+<file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
+  <authors>
+    <author>作成者</author>
+  </authors>
+  <commentList>
+    <comment ref="C31" authorId="0" shapeId="0" xr:uid="{1B96F192-8430-490A-836B-8C93BA7240DA}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="MS P ゴシック"/>
+            <family val="3"/>
+            <charset val="128"/>
+          </rPr>
+          <t>作成者:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="MS P ゴシック"/>
+            <family val="3"/>
+            <charset val="128"/>
+          </rPr>
+          <t xml:space="preserve">
+新システムは表示しない</t>
+        </r>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="399" uniqueCount="150">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="348" uniqueCount="138">
   <si>
     <t>作成者</t>
     <rPh sb="0" eb="3">
@@ -845,77 +898,11 @@
     <phoneticPr fontId="3"/>
   </si>
   <si>
-    <t>newProductClass</t>
-    <phoneticPr fontId="3"/>
-  </si>
-  <si>
-    <t>productSalesStatusClass</t>
-    <phoneticPr fontId="3"/>
-  </si>
-  <si>
-    <t>pcnNo</t>
-    <phoneticPr fontId="3"/>
-  </si>
-  <si>
-    <t>オリジナル</t>
-    <phoneticPr fontId="3"/>
-  </si>
-  <si>
-    <t>生産終了予定品</t>
-    <rPh sb="0" eb="2">
-      <t>セイサン</t>
-    </rPh>
-    <rPh sb="2" eb="4">
-      <t>シュウリョウ</t>
-    </rPh>
-    <rPh sb="4" eb="6">
-      <t>ヨテイ</t>
-    </rPh>
-    <rPh sb="6" eb="7">
-      <t>ヒン</t>
-    </rPh>
-    <phoneticPr fontId="3"/>
-  </si>
-  <si>
-    <t>新製品区分</t>
-    <rPh sb="0" eb="3">
-      <t>シンセイヒン</t>
-    </rPh>
-    <rPh sb="3" eb="5">
-      <t>クブン</t>
-    </rPh>
-    <phoneticPr fontId="3"/>
-  </si>
-  <si>
-    <t>製品販売状況</t>
-    <rPh sb="0" eb="2">
-      <t>セイヒン</t>
-    </rPh>
-    <rPh sb="2" eb="4">
-      <t>ハンバイ</t>
-    </rPh>
-    <rPh sb="4" eb="6">
-      <t>ジョウキョウ</t>
-    </rPh>
-    <phoneticPr fontId="3"/>
-  </si>
-  <si>
-    <t>PCN番号</t>
-    <rPh sb="3" eb="5">
-      <t>バンゴウ</t>
-    </rPh>
-    <phoneticPr fontId="3"/>
-  </si>
-  <si>
     <t>※1</t>
     <phoneticPr fontId="3"/>
   </si>
   <si>
     <t>値がないときとはレコードなしや値がnullの場合を指す。従って、例えば値がスペースなどのときは、スペースという値があると判定</t>
-    <phoneticPr fontId="3"/>
-  </si>
-  <si>
-    <t>2024-01</t>
     <phoneticPr fontId="3"/>
   </si>
   <si>
@@ -931,39 +918,6 @@
   </si>
   <si>
     <t>導出元：HrsChemicalSubstanceEntry.clCode</t>
-    <rPh sb="0" eb="2">
-      <t>ドウシュツ</t>
-    </rPh>
-    <rPh sb="2" eb="3">
-      <t>モト</t>
-    </rPh>
-    <phoneticPr fontId="3"/>
-  </si>
-  <si>
-    <t>導出元：HrsChemicalSubstanceEntry.newProductClass
-※値がない場合、"-"（ハイフン）を出力　備考の※1参照</t>
-    <rPh sb="0" eb="2">
-      <t>ドウシュツ</t>
-    </rPh>
-    <rPh sb="2" eb="3">
-      <t>モト</t>
-    </rPh>
-    <phoneticPr fontId="3"/>
-  </si>
-  <si>
-    <t>導出元：HrsChemicalSubstanceEntry.productSalesStatusClass
-※値がない場合、"-"（ハイフン）を出力　備考の※1参照</t>
-    <rPh sb="0" eb="2">
-      <t>ドウシュツ</t>
-    </rPh>
-    <rPh sb="2" eb="3">
-      <t>モト</t>
-    </rPh>
-    <phoneticPr fontId="3"/>
-  </si>
-  <si>
-    <t>導出元：HrsChemicalSubstanceEntry.pcnNo
-※値がない場合、"-"（ハイフン）を出力　備考の※1参照</t>
     <rPh sb="0" eb="2">
       <t>ドウシュツ</t>
     </rPh>
@@ -1239,7 +1193,7 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="x14ac x16r2 xr xr9">
   <numFmts count="7">
     <numFmt numFmtId="176" formatCode="&quot;¥&quot;#,##0_);[Red]\(&quot;¥&quot;#,##0\)"/>
     <numFmt numFmtId="177" formatCode="&quot;¥&quot;#,##0.00_);[Red]\(&quot;¥&quot;#,##0.00\)"/>
@@ -1249,7 +1203,7 @@
     <numFmt numFmtId="181" formatCode="0.00_);[Red]\(0.00\)"/>
     <numFmt numFmtId="182" formatCode="0.00&quot;　版&quot;"/>
   </numFmts>
-  <fonts count="38" x14ac:knownFonts="1">
+  <fonts count="40">
     <font>
       <sz val="11"/>
       <name val="ＭＳ Ｐゴシック"/>
@@ -1526,6 +1480,21 @@
       <strike/>
       <sz val="11"/>
       <name val="Meiryo UI"/>
+      <family val="3"/>
+      <charset val="128"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color indexed="81"/>
+      <name val="MS P ゴシック"/>
+      <family val="3"/>
+      <charset val="128"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="9"/>
+      <color indexed="81"/>
+      <name val="MS P ゴシック"/>
       <family val="3"/>
       <charset val="128"/>
     </font>
@@ -2886,8 +2855,8 @@
     </xf>
   </cellXfs>
   <cellStyles count="55">
-    <cellStyle name=" LBP-830 LIPS4" xfId="1"/>
-    <cellStyle name="0,0_x000d_ NA_x000d_ " xfId="2"/>
+    <cellStyle name=" LBP-830 LIPS4" xfId="1" xr:uid="{00000000-0005-0000-0000-000000000000}"/>
+    <cellStyle name="0,0_x000d_ NA_x000d_ " xfId="2" xr:uid="{00000000-0005-0000-0000-000001000000}"/>
     <cellStyle name="20% - アクセント 1" xfId="30" builtinId="30" hidden="1"/>
     <cellStyle name="20% - アクセント 2" xfId="34" builtinId="34" hidden="1"/>
     <cellStyle name="20% - アクセント 3" xfId="38" builtinId="38" hidden="1"/>
@@ -2906,8 +2875,8 @@
     <cellStyle name="60% - アクセント 4" xfId="44" builtinId="44" hidden="1"/>
     <cellStyle name="60% - アクセント 5" xfId="48" builtinId="48" hidden="1"/>
     <cellStyle name="60% - アクセント 6" xfId="52" builtinId="52" hidden="1"/>
-    <cellStyle name="Followed Hyperlink" xfId="3"/>
-    <cellStyle name="Hyperlink" xfId="4"/>
+    <cellStyle name="Followed Hyperlink" xfId="3" xr:uid="{00000000-0005-0000-0000-000014000000}"/>
+    <cellStyle name="Hyperlink" xfId="4" xr:uid="{00000000-0005-0000-0000-000015000000}"/>
     <cellStyle name="アクセント 1" xfId="29" builtinId="29" hidden="1"/>
     <cellStyle name="アクセント 2" xfId="33" builtinId="33" hidden="1"/>
     <cellStyle name="アクセント 3" xfId="37" builtinId="37" hidden="1"/>
@@ -2923,8 +2892,8 @@
     <cellStyle name="悪い" xfId="18" builtinId="27" hidden="1"/>
     <cellStyle name="計算" xfId="22" builtinId="22" hidden="1"/>
     <cellStyle name="警告文" xfId="25" builtinId="11" hidden="1"/>
-    <cellStyle name="桁蟻唇Ｆ [0.00]_NT Server " xfId="5"/>
-    <cellStyle name="桁蟻唇Ｆ_NT Server " xfId="6"/>
+    <cellStyle name="桁蟻唇Ｆ [0.00]_NT Server " xfId="5" xr:uid="{00000000-0005-0000-0000-000025000000}"/>
+    <cellStyle name="桁蟻唇Ｆ_NT Server " xfId="6" xr:uid="{00000000-0005-0000-0000-000026000000}"/>
     <cellStyle name="桁区切り" xfId="8" builtinId="6" hidden="1"/>
     <cellStyle name="桁区切り [0.00]" xfId="7" builtinId="3" hidden="1"/>
     <cellStyle name="見出し 1" xfId="13" builtinId="16" hidden="1"/>
@@ -2938,8 +2907,8 @@
     <cellStyle name="通貨 [0.00]" xfId="9" builtinId="4" hidden="1"/>
     <cellStyle name="入力" xfId="20" builtinId="20" hidden="1"/>
     <cellStyle name="標準" xfId="0" builtinId="0"/>
-    <cellStyle name="標準 2" xfId="53"/>
-    <cellStyle name="標準_4_開発要件書" xfId="54"/>
+    <cellStyle name="標準 2" xfId="53" xr:uid="{00000000-0005-0000-0000-000034000000}"/>
+    <cellStyle name="標準_4_開発要件書" xfId="54" xr:uid="{00000000-0005-0000-0000-000035000000}"/>
     <cellStyle name="良い" xfId="17" builtinId="26" hidden="1"/>
   </cellStyles>
   <dxfs count="2">
@@ -2967,7 +2936,7 @@
     </dxf>
   </dxfs>
   <tableStyles count="1" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16">
-    <tableStyle name="MySqlDefault" pivot="0" table="0" count="2">
+    <tableStyle name="MySqlDefault" pivot="0" table="0" count="2" xr9:uid="{00000000-0011-0000-FFFF-FFFF00000000}">
       <tableStyleElement type="wholeTable" dxfId="1"/>
       <tableStyleElement type="headerRow" dxfId="0"/>
     </tableStyle>
@@ -3299,9 +3268,9 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="D3:BD35"/>
-  <sheetFormatPr defaultColWidth="1.625" defaultRowHeight="12.75" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr defaultColWidth="1.625" defaultRowHeight="12.75"/>
   <cols>
     <col min="1" max="6" width="1.625" style="1"/>
     <col min="7" max="7" width="1.625" style="1" customWidth="1"/>
@@ -3434,19 +3403,19 @@
     <col min="16136" max="16384" width="1.625" style="1"/>
   </cols>
   <sheetData>
-    <row r="3" spans="4:37" ht="14.45" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="3" spans="4:37" ht="14.45" customHeight="1">
       <c r="D3" s="10" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="4" spans="4:37" ht="14.45" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="4" spans="4:37" ht="14.45" customHeight="1">
       <c r="D4" s="10" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="5" spans="4:37" ht="14.45" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="6" spans="4:37" ht="14.45" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="7" spans="4:37" ht="14.45" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="5" spans="4:37" ht="14.45" customHeight="1"/>
+    <row r="6" spans="4:37" ht="14.45" customHeight="1"/>
+    <row r="7" spans="4:37" ht="14.45" customHeight="1">
       <c r="E7" s="2"/>
       <c r="G7" s="78" t="s">
         <v>107</v>
@@ -3482,7 +3451,7 @@
       <c r="AJ7" s="78"/>
       <c r="AK7" s="78"/>
     </row>
-    <row r="8" spans="4:37" ht="14.45" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="8" spans="4:37" ht="14.45" customHeight="1">
       <c r="E8" s="2"/>
       <c r="G8" s="78"/>
       <c r="H8" s="78"/>
@@ -3516,19 +3485,19 @@
       <c r="AJ8" s="78"/>
       <c r="AK8" s="78"/>
     </row>
-    <row r="9" spans="4:37" ht="14.45" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="9" spans="4:37" ht="14.45" customHeight="1">
       <c r="E9" s="2"/>
       <c r="G9" s="1" t="s">
         <v>108</v>
       </c>
     </row>
-    <row r="10" spans="4:37" ht="14.45" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="10" spans="4:37" ht="14.45" customHeight="1">
       <c r="E10" s="2"/>
     </row>
-    <row r="11" spans="4:37" ht="14.45" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="11" spans="4:37" ht="14.45" customHeight="1">
       <c r="E11" s="2"/>
     </row>
-    <row r="12" spans="4:37" ht="14.45" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="12" spans="4:37" ht="14.45" customHeight="1">
       <c r="E12" s="2"/>
       <c r="G12" s="79">
         <f>MAX(改版履歴!B4:B32)</f>
@@ -3565,25 +3534,25 @@
       <c r="AJ12" s="79"/>
       <c r="AK12" s="79"/>
     </row>
-    <row r="13" spans="4:37" ht="14.45" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="14" spans="4:37" ht="14.45" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="15" spans="4:37" ht="14.45" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="16" spans="4:37" ht="14.45" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="17" spans="34:47" ht="14.45" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="18" spans="34:47" ht="14.45" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="19" spans="34:47" ht="14.45" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="20" spans="34:47" ht="14.45" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="21" spans="34:47" ht="14.45" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="22" spans="34:47" ht="14.45" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="23" spans="34:47" ht="14.45" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="24" spans="34:47" ht="14.45" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="25" spans="34:47" ht="14.45" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="26" spans="34:47" ht="14.45" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="27" spans="34:47" ht="14.45" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="28" spans="34:47" ht="14.45" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="29" spans="34:47" ht="14.45" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="30" spans="34:47" ht="14.45" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="31" spans="34:47" ht="14.45" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="13" spans="4:37" ht="14.45" customHeight="1"/>
+    <row r="14" spans="4:37" ht="14.45" customHeight="1"/>
+    <row r="15" spans="4:37" ht="14.45" customHeight="1"/>
+    <row r="16" spans="4:37" ht="14.45" customHeight="1"/>
+    <row r="17" spans="34:47" ht="14.45" customHeight="1"/>
+    <row r="18" spans="34:47" ht="14.45" customHeight="1"/>
+    <row r="19" spans="34:47" ht="14.45" customHeight="1"/>
+    <row r="20" spans="34:47" ht="14.45" customHeight="1"/>
+    <row r="21" spans="34:47" ht="14.45" customHeight="1"/>
+    <row r="22" spans="34:47" ht="14.45" customHeight="1"/>
+    <row r="23" spans="34:47" ht="14.45" customHeight="1"/>
+    <row r="24" spans="34:47" ht="14.45" customHeight="1"/>
+    <row r="25" spans="34:47" ht="14.45" customHeight="1"/>
+    <row r="26" spans="34:47" ht="14.45" customHeight="1"/>
+    <row r="27" spans="34:47" ht="14.45" customHeight="1"/>
+    <row r="28" spans="34:47" ht="14.45" customHeight="1"/>
+    <row r="29" spans="34:47" ht="14.45" customHeight="1"/>
+    <row r="30" spans="34:47" ht="14.45" customHeight="1"/>
+    <row r="31" spans="34:47" ht="14.45" customHeight="1">
       <c r="AH31" s="80">
         <f>MAX(改版履歴!D4:D32)</f>
         <v>45370</v>
@@ -3602,8 +3571,8 @@
       <c r="AT31" s="80"/>
       <c r="AU31" s="80"/>
     </row>
-    <row r="32" spans="34:47" ht="14.45" customHeight="1" x14ac:dyDescent="0.15"/>
-    <row r="33" spans="26:56" ht="14.45" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="32" spans="34:47" ht="14.45" customHeight="1"/>
+    <row r="33" spans="26:56" ht="14.45" customHeight="1">
       <c r="Z33" s="81" t="s">
         <v>6</v>
       </c>
@@ -3638,7 +3607,7 @@
       <c r="BC33" s="81"/>
       <c r="BD33" s="81"/>
     </row>
-    <row r="34" spans="26:56" ht="14.45" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="34" spans="26:56" ht="14.45" customHeight="1">
       <c r="Z34" s="81"/>
       <c r="AA34" s="81"/>
       <c r="AB34" s="81"/>
@@ -3671,7 +3640,7 @@
       <c r="BC34" s="81"/>
       <c r="BD34" s="81"/>
     </row>
-    <row r="35" spans="26:56" ht="14.45" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="35" spans="26:56" ht="14.45" customHeight="1">
       <c r="AF35" s="82"/>
       <c r="AG35" s="82"/>
       <c r="AH35" s="82"/>
@@ -3707,9 +3676,9 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="B1:G32"/>
-  <sheetFormatPr defaultRowHeight="11.25" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr defaultRowHeight="11.25"/>
   <cols>
     <col min="1" max="1" width="1.875" style="3" customWidth="1"/>
     <col min="2" max="2" width="5.625" style="13" customWidth="1"/>
@@ -4225,7 +4194,7 @@
     <col min="16136" max="16384" width="9" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:7" ht="17.25" x14ac:dyDescent="0.15">
+    <row r="1" spans="2:7" ht="17.25">
       <c r="B1" s="83" t="s">
         <v>7</v>
       </c>
@@ -4234,7 +4203,7 @@
       <c r="E1" s="83"/>
       <c r="F1" s="83"/>
     </row>
-    <row r="3" spans="2:7" x14ac:dyDescent="0.15">
+    <row r="3" spans="2:7">
       <c r="B3" s="11" t="s">
         <v>8</v>
       </c>
@@ -4251,7 +4220,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="4" spans="2:7" x14ac:dyDescent="0.15">
+    <row r="4" spans="2:7">
       <c r="B4" s="12">
         <v>1</v>
       </c>
@@ -4268,7 +4237,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="5" spans="2:7" ht="22.5" x14ac:dyDescent="0.15">
+    <row r="5" spans="2:7" ht="22.5">
       <c r="B5" s="12">
         <v>1.01</v>
       </c>
@@ -4285,7 +4254,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="6" spans="2:7" ht="33.75" x14ac:dyDescent="0.15">
+    <row r="6" spans="2:7" ht="33.75">
       <c r="B6" s="12">
         <v>1.02</v>
       </c>
@@ -4302,7 +4271,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="7" spans="2:7" ht="22.5" x14ac:dyDescent="0.15">
+    <row r="7" spans="2:7" ht="22.5">
       <c r="B7" s="12">
         <v>1.03</v>
       </c>
@@ -4319,7 +4288,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="8" spans="2:7" ht="22.5" x14ac:dyDescent="0.15">
+    <row r="8" spans="2:7" ht="22.5">
       <c r="B8" s="12">
         <v>1.04</v>
       </c>
@@ -4336,7 +4305,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="9" spans="2:7" ht="45" x14ac:dyDescent="0.15">
+    <row r="9" spans="2:7" ht="45">
       <c r="B9" s="12">
         <v>1.05</v>
       </c>
@@ -4350,24 +4319,24 @@
         <v>115</v>
       </c>
       <c r="F9" s="6" t="s">
-        <v>148</v>
+        <v>136</v>
       </c>
     </row>
-    <row r="10" spans="2:7" x14ac:dyDescent="0.15">
+    <row r="10" spans="2:7">
       <c r="B10" s="12"/>
       <c r="C10" s="6"/>
       <c r="D10" s="7"/>
       <c r="E10" s="6"/>
       <c r="F10" s="6"/>
     </row>
-    <row r="11" spans="2:7" x14ac:dyDescent="0.15">
+    <row r="11" spans="2:7">
       <c r="B11" s="12"/>
       <c r="C11" s="6"/>
       <c r="D11" s="7"/>
       <c r="E11" s="6"/>
       <c r="F11" s="6"/>
     </row>
-    <row r="12" spans="2:7" x14ac:dyDescent="0.15">
+    <row r="12" spans="2:7">
       <c r="B12" s="12"/>
       <c r="C12" s="6"/>
       <c r="D12" s="7"/>
@@ -4375,140 +4344,140 @@
       <c r="F12" s="6"/>
       <c r="G12" s="8"/>
     </row>
-    <row r="13" spans="2:7" x14ac:dyDescent="0.15">
+    <row r="13" spans="2:7">
       <c r="B13" s="12"/>
       <c r="C13" s="6"/>
       <c r="D13" s="7"/>
       <c r="E13" s="6"/>
       <c r="F13" s="6"/>
     </row>
-    <row r="14" spans="2:7" x14ac:dyDescent="0.15">
+    <row r="14" spans="2:7">
       <c r="B14" s="12"/>
       <c r="C14" s="6"/>
       <c r="D14" s="7"/>
       <c r="E14" s="6"/>
       <c r="F14" s="6"/>
     </row>
-    <row r="15" spans="2:7" x14ac:dyDescent="0.15">
+    <row r="15" spans="2:7">
       <c r="B15" s="12"/>
       <c r="C15" s="6"/>
       <c r="D15" s="7"/>
       <c r="E15" s="6"/>
       <c r="F15" s="6"/>
     </row>
-    <row r="16" spans="2:7" x14ac:dyDescent="0.15">
+    <row r="16" spans="2:7">
       <c r="B16" s="12"/>
       <c r="C16" s="6"/>
       <c r="D16" s="7"/>
       <c r="E16" s="6"/>
       <c r="F16" s="6"/>
     </row>
-    <row r="17" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="17" spans="2:6">
       <c r="B17" s="12"/>
       <c r="C17" s="6"/>
       <c r="D17" s="7"/>
       <c r="E17" s="6"/>
       <c r="F17" s="6"/>
     </row>
-    <row r="18" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="18" spans="2:6">
       <c r="B18" s="12"/>
       <c r="C18" s="6"/>
       <c r="D18" s="7"/>
       <c r="E18" s="6"/>
       <c r="F18" s="6"/>
     </row>
-    <row r="19" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="19" spans="2:6">
       <c r="B19" s="12"/>
       <c r="C19" s="6"/>
       <c r="D19" s="7"/>
       <c r="E19" s="6"/>
       <c r="F19" s="6"/>
     </row>
-    <row r="20" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="20" spans="2:6">
       <c r="B20" s="12"/>
       <c r="C20" s="6"/>
       <c r="D20" s="7"/>
       <c r="E20" s="6"/>
       <c r="F20" s="6"/>
     </row>
-    <row r="21" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="21" spans="2:6">
       <c r="B21" s="12"/>
       <c r="C21" s="6"/>
       <c r="D21" s="7"/>
       <c r="E21" s="6"/>
       <c r="F21" s="6"/>
     </row>
-    <row r="22" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="22" spans="2:6">
       <c r="B22" s="12"/>
       <c r="C22" s="6"/>
       <c r="D22" s="7"/>
       <c r="E22" s="6"/>
       <c r="F22" s="6"/>
     </row>
-    <row r="23" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="23" spans="2:6">
       <c r="B23" s="12"/>
       <c r="C23" s="6"/>
       <c r="D23" s="7"/>
       <c r="E23" s="6"/>
       <c r="F23" s="6"/>
     </row>
-    <row r="24" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="24" spans="2:6">
       <c r="B24" s="12"/>
       <c r="C24" s="6"/>
       <c r="D24" s="7"/>
       <c r="E24" s="6"/>
       <c r="F24" s="6"/>
     </row>
-    <row r="25" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="25" spans="2:6">
       <c r="B25" s="12"/>
       <c r="C25" s="6"/>
       <c r="D25" s="7"/>
       <c r="E25" s="6"/>
       <c r="F25" s="6"/>
     </row>
-    <row r="26" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="26" spans="2:6">
       <c r="B26" s="12"/>
       <c r="C26" s="6"/>
       <c r="D26" s="7"/>
       <c r="E26" s="6"/>
       <c r="F26" s="6"/>
     </row>
-    <row r="27" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="27" spans="2:6">
       <c r="B27" s="12"/>
       <c r="C27" s="6"/>
       <c r="D27" s="7"/>
       <c r="E27" s="6"/>
       <c r="F27" s="6"/>
     </row>
-    <row r="28" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="28" spans="2:6">
       <c r="B28" s="12"/>
       <c r="C28" s="6"/>
       <c r="D28" s="7"/>
       <c r="E28" s="6"/>
       <c r="F28" s="6"/>
     </row>
-    <row r="29" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="29" spans="2:6">
       <c r="B29" s="12"/>
       <c r="C29" s="6"/>
       <c r="D29" s="7"/>
       <c r="E29" s="6"/>
       <c r="F29" s="6"/>
     </row>
-    <row r="30" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="30" spans="2:6">
       <c r="B30" s="12"/>
       <c r="C30" s="6"/>
       <c r="D30" s="7"/>
       <c r="E30" s="6"/>
       <c r="F30" s="6"/>
     </row>
-    <row r="31" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="31" spans="2:6">
       <c r="B31" s="12"/>
       <c r="C31" s="6"/>
       <c r="D31" s="7"/>
       <c r="E31" s="6"/>
       <c r="F31" s="6"/>
     </row>
-    <row r="32" spans="2:6" x14ac:dyDescent="0.15">
+    <row r="32" spans="2:6">
       <c r="B32" s="12"/>
       <c r="C32" s="6"/>
       <c r="D32" s="7"/>
@@ -4530,13 +4499,13 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <sheetPr>
     <tabColor rgb="FFFF0000"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:CO59"/>
-  <sheetFormatPr defaultColWidth="2.625" defaultRowHeight="15.75" x14ac:dyDescent="0.15"/>
+  <dimension ref="A1:CO56"/>
+  <sheetFormatPr defaultColWidth="2.625" defaultRowHeight="15.75"/>
   <cols>
     <col min="1" max="2" width="2.625" style="20"/>
     <col min="3" max="8" width="2.625" style="21"/>
@@ -4545,7 +4514,7 @@
     <col min="49" max="16384" width="2.625" style="20"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:90" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="1" spans="1:90" ht="13.5" customHeight="1">
       <c r="A1" s="165" t="s">
         <v>76</v>
       </c>
@@ -4625,7 +4594,7 @@
       <c r="BI1" s="164"/>
       <c r="BJ1" s="164"/>
     </row>
-    <row r="2" spans="1:90" ht="25.5" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="2" spans="1:90" ht="25.5" customHeight="1">
       <c r="A2" s="165"/>
       <c r="B2" s="165"/>
       <c r="C2" s="165"/>
@@ -4708,7 +4677,7 @@
       <c r="BI2" s="168"/>
       <c r="BJ2" s="168"/>
     </row>
-    <row r="4" spans="1:90" x14ac:dyDescent="0.15">
+    <row r="4" spans="1:90">
       <c r="A4" s="133" t="s">
         <v>15</v>
       </c>
@@ -4719,7 +4688,7 @@
       <c r="F4" s="134"/>
       <c r="G4" s="135"/>
     </row>
-    <row r="5" spans="1:90" s="23" customFormat="1" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="5" spans="1:90" s="23" customFormat="1" ht="13.5" customHeight="1">
       <c r="A5" s="136" t="s">
         <v>106</v>
       </c>
@@ -4810,7 +4779,7 @@
       <c r="CH5" s="137"/>
       <c r="CI5" s="138"/>
     </row>
-    <row r="6" spans="1:90" s="23" customFormat="1" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="6" spans="1:90" s="23" customFormat="1" ht="13.5" customHeight="1">
       <c r="A6" s="139"/>
       <c r="B6" s="140"/>
       <c r="C6" s="140"/>
@@ -4899,7 +4868,7 @@
       <c r="CH6" s="140"/>
       <c r="CI6" s="141"/>
     </row>
-    <row r="7" spans="1:90" s="23" customFormat="1" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="7" spans="1:90" s="23" customFormat="1" ht="13.5" customHeight="1">
       <c r="A7" s="142"/>
       <c r="B7" s="143"/>
       <c r="C7" s="143"/>
@@ -4988,7 +4957,7 @@
       <c r="CH7" s="143"/>
       <c r="CI7" s="144"/>
     </row>
-    <row r="8" spans="1:90" s="23" customFormat="1" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="8" spans="1:90" s="23" customFormat="1" ht="13.5" customHeight="1">
       <c r="A8" s="20"/>
       <c r="B8" s="20"/>
       <c r="C8" s="21"/>
@@ -5077,7 +5046,7 @@
       <c r="CH8" s="20"/>
       <c r="CI8" s="20"/>
     </row>
-    <row r="9" spans="1:90" s="28" customFormat="1" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="9" spans="1:90" s="28" customFormat="1" ht="13.5" customHeight="1">
       <c r="A9" s="145" t="s">
         <v>16</v>
       </c>
@@ -5171,7 +5140,7 @@
       <c r="CK9" s="27"/>
       <c r="CL9" s="27"/>
     </row>
-    <row r="10" spans="1:90" s="29" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="10" spans="1:90" s="29" customFormat="1">
       <c r="A10" s="148" t="s">
         <v>17</v>
       </c>
@@ -5267,7 +5236,7 @@
       <c r="CK10" s="151"/>
       <c r="CL10" s="151"/>
     </row>
-    <row r="11" spans="1:90" s="29" customFormat="1" ht="159" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="11" spans="1:90" s="29" customFormat="1" ht="159" customHeight="1">
       <c r="A11" s="148" t="s">
         <v>18</v>
       </c>
@@ -5279,7 +5248,7 @@
       <c r="G11" s="149"/>
       <c r="H11" s="150"/>
       <c r="I11" s="170" t="s">
-        <v>149</v>
+        <v>137</v>
       </c>
       <c r="J11" s="171"/>
       <c r="K11" s="171"/>
@@ -5363,7 +5332,7 @@
       <c r="CK11" s="171"/>
       <c r="CL11" s="171"/>
     </row>
-    <row r="12" spans="1:90" s="29" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="12" spans="1:90" s="29" customFormat="1">
       <c r="A12" s="172" t="s">
         <v>19</v>
       </c>
@@ -5459,7 +5428,7 @@
       <c r="CK12" s="173"/>
       <c r="CL12" s="173"/>
     </row>
-    <row r="13" spans="1:90" s="29" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="13" spans="1:90" s="29" customFormat="1">
       <c r="A13" s="157" t="s">
         <v>78</v>
       </c>
@@ -5571,7 +5540,7 @@
       <c r="CK13" s="155"/>
       <c r="CL13" s="156"/>
     </row>
-    <row r="14" spans="1:90" s="29" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="14" spans="1:90" s="29" customFormat="1">
       <c r="A14" s="157" t="s">
         <v>79</v>
       </c>
@@ -5683,7 +5652,7 @@
       <c r="CK14" s="155"/>
       <c r="CL14" s="156"/>
     </row>
-    <row r="15" spans="1:90" s="29" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="15" spans="1:90" s="29" customFormat="1">
       <c r="A15" s="157" t="s">
         <v>28</v>
       </c>
@@ -5795,7 +5764,7 @@
       <c r="CK15" s="155"/>
       <c r="CL15" s="156"/>
     </row>
-    <row r="16" spans="1:90" s="30" customFormat="1" ht="91.5" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="16" spans="1:90" s="30" customFormat="1" ht="91.5" customHeight="1">
       <c r="A16" s="177" t="s">
         <v>5</v>
       </c>
@@ -5891,7 +5860,7 @@
       <c r="CK16" s="179"/>
       <c r="CL16" s="180"/>
     </row>
-    <row r="17" spans="1:93" s="29" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="17" spans="1:93" s="29" customFormat="1">
       <c r="A17" s="31"/>
       <c r="B17" s="31"/>
       <c r="C17" s="32"/>
@@ -5983,7 +5952,7 @@
       <c r="CK17" s="31"/>
       <c r="CL17" s="31"/>
     </row>
-    <row r="18" spans="1:93" s="15" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="18" spans="1:93" s="15" customFormat="1">
       <c r="A18" s="145" t="s">
         <v>68</v>
       </c>
@@ -6077,7 +6046,7 @@
       <c r="CK18" s="16"/>
       <c r="CL18" s="16"/>
     </row>
-    <row r="19" spans="1:93" s="15" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="19" spans="1:93" s="15" customFormat="1">
       <c r="A19" s="112" t="s">
         <v>32</v>
       </c>
@@ -6198,7 +6167,7 @@
       <c r="CH19" s="113"/>
       <c r="CI19" s="114"/>
     </row>
-    <row r="20" spans="1:93" s="15" customFormat="1" ht="87.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="20" spans="1:93" s="15" customFormat="1" ht="87.75" customHeight="1">
       <c r="A20" s="115"/>
       <c r="B20" s="117"/>
       <c r="C20" s="115"/>
@@ -6295,7 +6264,7 @@
       <c r="CH20" s="116"/>
       <c r="CI20" s="117"/>
     </row>
-    <row r="21" spans="1:93" s="15" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="21" spans="1:93" s="15" customFormat="1">
       <c r="A21" s="96" t="s">
         <v>67</v>
       </c>
@@ -6422,7 +6391,7 @@
       <c r="CH21" s="106"/>
       <c r="CI21" s="107"/>
     </row>
-    <row r="22" spans="1:93" s="29" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="22" spans="1:93" s="29" customFormat="1">
       <c r="A22" s="31"/>
       <c r="B22" s="31"/>
       <c r="C22" s="32"/>
@@ -6511,7 +6480,7 @@
       <c r="CH22" s="31"/>
       <c r="CI22" s="31"/>
     </row>
-    <row r="23" spans="1:93" s="15" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="23" spans="1:93" s="15" customFormat="1">
       <c r="A23" s="145" t="s">
         <v>43</v>
       </c>
@@ -6602,7 +6571,7 @@
       <c r="CH23" s="16"/>
       <c r="CI23" s="16"/>
     </row>
-    <row r="24" spans="1:93" s="15" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="24" spans="1:93" s="15" customFormat="1" ht="15.75" customHeight="1">
       <c r="A24" s="112" t="s">
         <v>32</v>
       </c>
@@ -6729,7 +6698,7 @@
       <c r="CN24" s="95"/>
       <c r="CO24" s="95"/>
     </row>
-    <row r="25" spans="1:93" s="15" customFormat="1" ht="82.5" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="25" spans="1:93" s="15" customFormat="1" ht="82.5" customHeight="1">
       <c r="A25" s="115"/>
       <c r="B25" s="117"/>
       <c r="C25" s="115"/>
@@ -6832,7 +6801,7 @@
       <c r="CN25" s="95"/>
       <c r="CO25" s="95"/>
     </row>
-    <row r="26" spans="1:93" s="63" customFormat="1" ht="44.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="26" spans="1:93" s="63" customFormat="1" ht="44.25" customHeight="1">
       <c r="A26" s="221">
         <f>ROW()-25</f>
         <v>1</v>
@@ -6937,7 +6906,7 @@
       <c r="BM26" s="128"/>
       <c r="BN26" s="129"/>
       <c r="BO26" s="218" t="s">
-        <v>142</v>
+        <v>133</v>
       </c>
       <c r="BP26" s="219"/>
       <c r="BQ26" s="219"/>
@@ -6960,7 +6929,7 @@
       <c r="CH26" s="219"/>
       <c r="CI26" s="220"/>
     </row>
-    <row r="27" spans="1:93" s="63" customFormat="1" ht="44.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="27" spans="1:93" s="63" customFormat="1" ht="44.25" customHeight="1">
       <c r="A27" s="96">
         <f>ROW()-25</f>
         <v>2</v>
@@ -7065,7 +7034,7 @@
       <c r="BM27" s="103"/>
       <c r="BN27" s="104"/>
       <c r="BO27" s="218" t="s">
-        <v>143</v>
+        <v>134</v>
       </c>
       <c r="BP27" s="219"/>
       <c r="BQ27" s="219"/>
@@ -7088,398 +7057,394 @@
       <c r="CH27" s="219"/>
       <c r="CI27" s="220"/>
     </row>
-    <row r="28" spans="1:93" s="63" customFormat="1" ht="44.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A28" s="221">
-        <f>ROW()-25</f>
+    <row r="28" spans="1:93" s="63" customFormat="1" ht="44.25" customHeight="1">
+      <c r="A28" s="96">
+        <f t="shared" ref="A28:A35" si="0">ROW()-25</f>
         <v>3</v>
       </c>
-      <c r="B28" s="222"/>
-      <c r="C28" s="223" t="s">
-        <v>136</v>
-      </c>
-      <c r="D28" s="224"/>
-      <c r="E28" s="224"/>
-      <c r="F28" s="224"/>
-      <c r="G28" s="224"/>
-      <c r="H28" s="225"/>
-      <c r="I28" s="218" t="s">
-        <v>131</v>
-      </c>
-      <c r="J28" s="219"/>
-      <c r="K28" s="219"/>
-      <c r="L28" s="219"/>
-      <c r="M28" s="219"/>
-      <c r="N28" s="220"/>
-      <c r="O28" s="120" t="s">
+      <c r="B28" s="98"/>
+      <c r="C28" s="200" t="s">
+        <v>110</v>
+      </c>
+      <c r="D28" s="201"/>
+      <c r="E28" s="201"/>
+      <c r="F28" s="201"/>
+      <c r="G28" s="201"/>
+      <c r="H28" s="202"/>
+      <c r="I28" s="105" t="s">
+        <v>93</v>
+      </c>
+      <c r="J28" s="106"/>
+      <c r="K28" s="106"/>
+      <c r="L28" s="106"/>
+      <c r="M28" s="106"/>
+      <c r="N28" s="107"/>
+      <c r="O28" s="89" t="s">
         <v>46</v>
       </c>
-      <c r="P28" s="121"/>
-      <c r="Q28" s="122"/>
-      <c r="R28" s="73" t="s">
-        <v>14</v>
-      </c>
-      <c r="S28" s="73" t="s">
-        <v>14</v>
-      </c>
-      <c r="T28" s="73" t="s">
+      <c r="P28" s="90"/>
+      <c r="Q28" s="91"/>
+      <c r="R28" s="34" t="s">
+        <v>57</v>
+      </c>
+      <c r="S28" s="34" t="s">
+        <v>57</v>
+      </c>
+      <c r="T28" s="34" t="s">
         <v>42</v>
       </c>
-      <c r="U28" s="73" t="s">
-        <v>14</v>
-      </c>
-      <c r="V28" s="206">
+      <c r="U28" s="34" t="s">
+        <v>57</v>
+      </c>
+      <c r="V28" s="203">
         <v>255</v>
       </c>
-      <c r="W28" s="207"/>
-      <c r="X28" s="208"/>
-      <c r="Y28" s="206" t="s">
-        <v>14</v>
-      </c>
-      <c r="Z28" s="207"/>
-      <c r="AA28" s="208"/>
-      <c r="AB28" s="92" t="s">
+      <c r="W28" s="204"/>
+      <c r="X28" s="205"/>
+      <c r="Y28" s="203" t="s">
+        <v>57</v>
+      </c>
+      <c r="Z28" s="204"/>
+      <c r="AA28" s="205"/>
+      <c r="AB28" s="87" t="s">
         <v>47</v>
       </c>
-      <c r="AC28" s="123"/>
-      <c r="AD28" s="123"/>
-      <c r="AE28" s="123"/>
-      <c r="AF28" s="93"/>
-      <c r="AG28" s="92" t="s">
+      <c r="AC28" s="190"/>
+      <c r="AD28" s="190"/>
+      <c r="AE28" s="190"/>
+      <c r="AF28" s="88"/>
+      <c r="AG28" s="87" t="s">
         <v>51</v>
       </c>
-      <c r="AH28" s="93"/>
-      <c r="AI28" s="92" t="s">
+      <c r="AH28" s="88"/>
+      <c r="AI28" s="87" t="s">
+        <v>42</v>
+      </c>
+      <c r="AJ28" s="88"/>
+      <c r="AK28" s="89" t="s">
         <v>51</v>
       </c>
-      <c r="AJ28" s="93"/>
-      <c r="AK28" s="120" t="s">
+      <c r="AL28" s="90"/>
+      <c r="AM28" s="91"/>
+      <c r="AN28" s="87" t="s">
         <v>51</v>
       </c>
-      <c r="AL28" s="121"/>
-      <c r="AM28" s="122"/>
-      <c r="AN28" s="92" t="s">
+      <c r="AO28" s="190"/>
+      <c r="AP28" s="190"/>
+      <c r="AQ28" s="190"/>
+      <c r="AR28" s="190"/>
+      <c r="AS28" s="190"/>
+      <c r="AT28" s="190"/>
+      <c r="AU28" s="88"/>
+      <c r="AV28" s="84" t="s">
+        <v>113</v>
+      </c>
+      <c r="AW28" s="85"/>
+      <c r="AX28" s="85"/>
+      <c r="AY28" s="85"/>
+      <c r="AZ28" s="85"/>
+      <c r="BA28" s="85"/>
+      <c r="BB28" s="85"/>
+      <c r="BC28" s="85"/>
+      <c r="BD28" s="85"/>
+      <c r="BE28" s="85"/>
+      <c r="BF28" s="85"/>
+      <c r="BG28" s="86"/>
+      <c r="BH28" s="102" t="s">
+        <v>57</v>
+      </c>
+      <c r="BI28" s="103"/>
+      <c r="BJ28" s="103"/>
+      <c r="BK28" s="104"/>
+      <c r="BL28" s="102" t="s">
+        <v>57</v>
+      </c>
+      <c r="BM28" s="103"/>
+      <c r="BN28" s="104"/>
+      <c r="BO28" s="209" t="s">
+        <v>135</v>
+      </c>
+      <c r="BP28" s="210"/>
+      <c r="BQ28" s="210"/>
+      <c r="BR28" s="210"/>
+      <c r="BS28" s="210"/>
+      <c r="BT28" s="210"/>
+      <c r="BU28" s="210"/>
+      <c r="BV28" s="210"/>
+      <c r="BW28" s="210"/>
+      <c r="BX28" s="210"/>
+      <c r="BY28" s="210"/>
+      <c r="BZ28" s="210"/>
+      <c r="CA28" s="210"/>
+      <c r="CB28" s="210"/>
+      <c r="CC28" s="210"/>
+      <c r="CD28" s="210"/>
+      <c r="CE28" s="210"/>
+      <c r="CF28" s="210"/>
+      <c r="CG28" s="210"/>
+      <c r="CH28" s="210"/>
+      <c r="CI28" s="211"/>
+    </row>
+    <row r="29" spans="1:93" s="63" customFormat="1" ht="44.25" customHeight="1">
+      <c r="A29" s="96">
+        <f t="shared" si="0"/>
+        <v>4</v>
+      </c>
+      <c r="B29" s="98"/>
+      <c r="C29" s="200" t="s">
+        <v>94</v>
+      </c>
+      <c r="D29" s="201"/>
+      <c r="E29" s="201"/>
+      <c r="F29" s="201"/>
+      <c r="G29" s="201"/>
+      <c r="H29" s="202"/>
+      <c r="I29" s="105" t="s">
+        <v>95</v>
+      </c>
+      <c r="J29" s="106"/>
+      <c r="K29" s="106"/>
+      <c r="L29" s="106"/>
+      <c r="M29" s="106"/>
+      <c r="N29" s="107"/>
+      <c r="O29" s="89" t="s">
+        <v>46</v>
+      </c>
+      <c r="P29" s="90"/>
+      <c r="Q29" s="91"/>
+      <c r="R29" s="34" t="s">
+        <v>57</v>
+      </c>
+      <c r="S29" s="34" t="s">
+        <v>57</v>
+      </c>
+      <c r="T29" s="34" t="s">
+        <v>42</v>
+      </c>
+      <c r="U29" s="34" t="s">
+        <v>57</v>
+      </c>
+      <c r="V29" s="203">
+        <v>255</v>
+      </c>
+      <c r="W29" s="204"/>
+      <c r="X29" s="205"/>
+      <c r="Y29" s="203" t="s">
+        <v>57</v>
+      </c>
+      <c r="Z29" s="204"/>
+      <c r="AA29" s="205"/>
+      <c r="AB29" s="87" t="s">
+        <v>47</v>
+      </c>
+      <c r="AC29" s="190"/>
+      <c r="AD29" s="190"/>
+      <c r="AE29" s="190"/>
+      <c r="AF29" s="88"/>
+      <c r="AG29" s="87" t="s">
         <v>51</v>
       </c>
-      <c r="AO28" s="123"/>
-      <c r="AP28" s="123"/>
-      <c r="AQ28" s="123"/>
-      <c r="AR28" s="123"/>
-      <c r="AS28" s="123"/>
-      <c r="AT28" s="123"/>
-      <c r="AU28" s="93"/>
-      <c r="AV28" s="124" t="s">
-        <v>134</v>
-      </c>
-      <c r="AW28" s="125"/>
-      <c r="AX28" s="125"/>
-      <c r="AY28" s="125"/>
-      <c r="AZ28" s="125"/>
-      <c r="BA28" s="125"/>
-      <c r="BB28" s="125"/>
-      <c r="BC28" s="125"/>
-      <c r="BD28" s="125"/>
-      <c r="BE28" s="125"/>
-      <c r="BF28" s="125"/>
-      <c r="BG28" s="126"/>
-      <c r="BH28" s="127" t="s">
-        <v>14</v>
-      </c>
-      <c r="BI28" s="128"/>
-      <c r="BJ28" s="128"/>
-      <c r="BK28" s="129"/>
-      <c r="BL28" s="127" t="s">
-        <v>14</v>
-      </c>
-      <c r="BM28" s="128"/>
-      <c r="BN28" s="129"/>
-      <c r="BO28" s="218" t="s">
-        <v>144</v>
-      </c>
-      <c r="BP28" s="219"/>
-      <c r="BQ28" s="219"/>
-      <c r="BR28" s="219"/>
-      <c r="BS28" s="219"/>
-      <c r="BT28" s="219"/>
-      <c r="BU28" s="219"/>
-      <c r="BV28" s="219"/>
-      <c r="BW28" s="219"/>
-      <c r="BX28" s="219"/>
-      <c r="BY28" s="219"/>
-      <c r="BZ28" s="219"/>
-      <c r="CA28" s="219"/>
-      <c r="CB28" s="219"/>
-      <c r="CC28" s="219"/>
-      <c r="CD28" s="219"/>
-      <c r="CE28" s="219"/>
-      <c r="CF28" s="219"/>
-      <c r="CG28" s="219"/>
-      <c r="CH28" s="219"/>
-      <c r="CI28" s="220"/>
+      <c r="AH29" s="88"/>
+      <c r="AI29" s="87" t="s">
+        <v>42</v>
+      </c>
+      <c r="AJ29" s="88"/>
+      <c r="AK29" s="89" t="s">
+        <v>51</v>
+      </c>
+      <c r="AL29" s="90"/>
+      <c r="AM29" s="91"/>
+      <c r="AN29" s="87" t="s">
+        <v>51</v>
+      </c>
+      <c r="AO29" s="190"/>
+      <c r="AP29" s="190"/>
+      <c r="AQ29" s="190"/>
+      <c r="AR29" s="190"/>
+      <c r="AS29" s="190"/>
+      <c r="AT29" s="190"/>
+      <c r="AU29" s="88"/>
+      <c r="AV29" s="84" t="s">
+        <v>96</v>
+      </c>
+      <c r="AW29" s="85"/>
+      <c r="AX29" s="85"/>
+      <c r="AY29" s="85"/>
+      <c r="AZ29" s="85"/>
+      <c r="BA29" s="85"/>
+      <c r="BB29" s="85"/>
+      <c r="BC29" s="85"/>
+      <c r="BD29" s="85"/>
+      <c r="BE29" s="85"/>
+      <c r="BF29" s="85"/>
+      <c r="BG29" s="86"/>
+      <c r="BH29" s="102" t="s">
+        <v>57</v>
+      </c>
+      <c r="BI29" s="103"/>
+      <c r="BJ29" s="103"/>
+      <c r="BK29" s="104"/>
+      <c r="BL29" s="102" t="s">
+        <v>57</v>
+      </c>
+      <c r="BM29" s="103"/>
+      <c r="BN29" s="104"/>
+      <c r="BO29" s="212"/>
+      <c r="BP29" s="213"/>
+      <c r="BQ29" s="213"/>
+      <c r="BR29" s="213"/>
+      <c r="BS29" s="213"/>
+      <c r="BT29" s="213"/>
+      <c r="BU29" s="213"/>
+      <c r="BV29" s="213"/>
+      <c r="BW29" s="213"/>
+      <c r="BX29" s="213"/>
+      <c r="BY29" s="213"/>
+      <c r="BZ29" s="213"/>
+      <c r="CA29" s="213"/>
+      <c r="CB29" s="213"/>
+      <c r="CC29" s="213"/>
+      <c r="CD29" s="213"/>
+      <c r="CE29" s="213"/>
+      <c r="CF29" s="213"/>
+      <c r="CG29" s="213"/>
+      <c r="CH29" s="213"/>
+      <c r="CI29" s="214"/>
     </row>
-    <row r="29" spans="1:93" s="63" customFormat="1" ht="44.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A29" s="221">
-        <f t="shared" ref="A29:A30" si="0">ROW()-25</f>
-        <v>4</v>
-      </c>
-      <c r="B29" s="222"/>
-      <c r="C29" s="223" t="s">
-        <v>137</v>
-      </c>
-      <c r="D29" s="224"/>
-      <c r="E29" s="224"/>
-      <c r="F29" s="224"/>
-      <c r="G29" s="224"/>
-      <c r="H29" s="225"/>
-      <c r="I29" s="218" t="s">
-        <v>132</v>
-      </c>
-      <c r="J29" s="219"/>
-      <c r="K29" s="219"/>
-      <c r="L29" s="219"/>
-      <c r="M29" s="219"/>
-      <c r="N29" s="220"/>
-      <c r="O29" s="120" t="s">
-        <v>46</v>
-      </c>
-      <c r="P29" s="121"/>
-      <c r="Q29" s="122"/>
-      <c r="R29" s="73" t="s">
-        <v>14</v>
-      </c>
-      <c r="S29" s="73" t="s">
-        <v>14</v>
-      </c>
-      <c r="T29" s="73" t="s">
-        <v>42</v>
-      </c>
-      <c r="U29" s="73" t="s">
-        <v>14</v>
-      </c>
-      <c r="V29" s="206">
-        <v>255</v>
-      </c>
-      <c r="W29" s="207"/>
-      <c r="X29" s="208"/>
-      <c r="Y29" s="206" t="s">
-        <v>14</v>
-      </c>
-      <c r="Z29" s="207"/>
-      <c r="AA29" s="208"/>
-      <c r="AB29" s="92" t="s">
-        <v>47</v>
-      </c>
-      <c r="AC29" s="123"/>
-      <c r="AD29" s="123"/>
-      <c r="AE29" s="123"/>
-      <c r="AF29" s="93"/>
-      <c r="AG29" s="92" t="s">
-        <v>51</v>
-      </c>
-      <c r="AH29" s="93"/>
-      <c r="AI29" s="92" t="s">
-        <v>51</v>
-      </c>
-      <c r="AJ29" s="93"/>
-      <c r="AK29" s="120" t="s">
-        <v>51</v>
-      </c>
-      <c r="AL29" s="121"/>
-      <c r="AM29" s="122"/>
-      <c r="AN29" s="92" t="s">
-        <v>51</v>
-      </c>
-      <c r="AO29" s="123"/>
-      <c r="AP29" s="123"/>
-      <c r="AQ29" s="123"/>
-      <c r="AR29" s="123"/>
-      <c r="AS29" s="123"/>
-      <c r="AT29" s="123"/>
-      <c r="AU29" s="93"/>
-      <c r="AV29" s="124" t="s">
-        <v>135</v>
-      </c>
-      <c r="AW29" s="125"/>
-      <c r="AX29" s="125"/>
-      <c r="AY29" s="125"/>
-      <c r="AZ29" s="125"/>
-      <c r="BA29" s="125"/>
-      <c r="BB29" s="125"/>
-      <c r="BC29" s="125"/>
-      <c r="BD29" s="125"/>
-      <c r="BE29" s="125"/>
-      <c r="BF29" s="125"/>
-      <c r="BG29" s="126"/>
-      <c r="BH29" s="127" t="s">
-        <v>14</v>
-      </c>
-      <c r="BI29" s="128"/>
-      <c r="BJ29" s="128"/>
-      <c r="BK29" s="129"/>
-      <c r="BL29" s="127" t="s">
-        <v>14</v>
-      </c>
-      <c r="BM29" s="128"/>
-      <c r="BN29" s="129"/>
-      <c r="BO29" s="218" t="s">
-        <v>145</v>
-      </c>
-      <c r="BP29" s="219"/>
-      <c r="BQ29" s="219"/>
-      <c r="BR29" s="219"/>
-      <c r="BS29" s="219"/>
-      <c r="BT29" s="219"/>
-      <c r="BU29" s="219"/>
-      <c r="BV29" s="219"/>
-      <c r="BW29" s="219"/>
-      <c r="BX29" s="219"/>
-      <c r="BY29" s="219"/>
-      <c r="BZ29" s="219"/>
-      <c r="CA29" s="219"/>
-      <c r="CB29" s="219"/>
-      <c r="CC29" s="219"/>
-      <c r="CD29" s="219"/>
-      <c r="CE29" s="219"/>
-      <c r="CF29" s="219"/>
-      <c r="CG29" s="219"/>
-      <c r="CH29" s="219"/>
-      <c r="CI29" s="220"/>
-    </row>
-    <row r="30" spans="1:93" s="63" customFormat="1" ht="44.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A30" s="221">
+    <row r="30" spans="1:93" s="63" customFormat="1" ht="44.25" customHeight="1">
+      <c r="A30" s="96">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="B30" s="222"/>
-      <c r="C30" s="223" t="s">
-        <v>138</v>
-      </c>
-      <c r="D30" s="224"/>
-      <c r="E30" s="224"/>
-      <c r="F30" s="224"/>
-      <c r="G30" s="224"/>
-      <c r="H30" s="225"/>
-      <c r="I30" s="218" t="s">
-        <v>133</v>
-      </c>
-      <c r="J30" s="219"/>
-      <c r="K30" s="219"/>
-      <c r="L30" s="219"/>
-      <c r="M30" s="219"/>
-      <c r="N30" s="220"/>
-      <c r="O30" s="120" t="s">
+      <c r="B30" s="98"/>
+      <c r="C30" s="197" t="s">
+        <v>97</v>
+      </c>
+      <c r="D30" s="198"/>
+      <c r="E30" s="198"/>
+      <c r="F30" s="198"/>
+      <c r="G30" s="198"/>
+      <c r="H30" s="199"/>
+      <c r="I30" s="105" t="s">
+        <v>98</v>
+      </c>
+      <c r="J30" s="106"/>
+      <c r="K30" s="106"/>
+      <c r="L30" s="106"/>
+      <c r="M30" s="106"/>
+      <c r="N30" s="107"/>
+      <c r="O30" s="89" t="s">
         <v>46</v>
       </c>
-      <c r="P30" s="121"/>
-      <c r="Q30" s="122"/>
-      <c r="R30" s="73" t="s">
-        <v>14</v>
-      </c>
-      <c r="S30" s="73" t="s">
-        <v>14</v>
-      </c>
-      <c r="T30" s="73" t="s">
+      <c r="P30" s="90"/>
+      <c r="Q30" s="91"/>
+      <c r="R30" s="34" t="s">
+        <v>57</v>
+      </c>
+      <c r="S30" s="34" t="s">
+        <v>57</v>
+      </c>
+      <c r="T30" s="34" t="s">
         <v>42</v>
       </c>
-      <c r="U30" s="73" t="s">
-        <v>14</v>
-      </c>
-      <c r="V30" s="206">
+      <c r="U30" s="34" t="s">
+        <v>57</v>
+      </c>
+      <c r="V30" s="203">
         <v>255</v>
       </c>
-      <c r="W30" s="207"/>
-      <c r="X30" s="208"/>
-      <c r="Y30" s="206" t="s">
-        <v>14</v>
-      </c>
-      <c r="Z30" s="207"/>
-      <c r="AA30" s="208"/>
-      <c r="AB30" s="92" t="s">
+      <c r="W30" s="204"/>
+      <c r="X30" s="205"/>
+      <c r="Y30" s="203" t="s">
+        <v>57</v>
+      </c>
+      <c r="Z30" s="204"/>
+      <c r="AA30" s="205"/>
+      <c r="AB30" s="87" t="s">
         <v>47</v>
       </c>
-      <c r="AC30" s="123"/>
-      <c r="AD30" s="123"/>
-      <c r="AE30" s="123"/>
-      <c r="AF30" s="93"/>
-      <c r="AG30" s="92" t="s">
+      <c r="AC30" s="190"/>
+      <c r="AD30" s="190"/>
+      <c r="AE30" s="190"/>
+      <c r="AF30" s="88"/>
+      <c r="AG30" s="87" t="s">
         <v>51</v>
       </c>
-      <c r="AH30" s="93"/>
-      <c r="AI30" s="92" t="s">
+      <c r="AH30" s="88"/>
+      <c r="AI30" s="87" t="s">
+        <v>42</v>
+      </c>
+      <c r="AJ30" s="88"/>
+      <c r="AK30" s="89" t="s">
         <v>51</v>
       </c>
-      <c r="AJ30" s="93"/>
-      <c r="AK30" s="120" t="s">
+      <c r="AL30" s="90"/>
+      <c r="AM30" s="91"/>
+      <c r="AN30" s="87" t="s">
         <v>51</v>
       </c>
-      <c r="AL30" s="121"/>
-      <c r="AM30" s="122"/>
-      <c r="AN30" s="92" t="s">
-        <v>51</v>
-      </c>
-      <c r="AO30" s="123"/>
-      <c r="AP30" s="123"/>
-      <c r="AQ30" s="123"/>
-      <c r="AR30" s="123"/>
-      <c r="AS30" s="123"/>
-      <c r="AT30" s="123"/>
-      <c r="AU30" s="93"/>
-      <c r="AV30" s="124" t="s">
-        <v>141</v>
-      </c>
-      <c r="AW30" s="125"/>
-      <c r="AX30" s="125"/>
-      <c r="AY30" s="125"/>
-      <c r="AZ30" s="125"/>
-      <c r="BA30" s="125"/>
-      <c r="BB30" s="125"/>
-      <c r="BC30" s="125"/>
-      <c r="BD30" s="125"/>
-      <c r="BE30" s="125"/>
-      <c r="BF30" s="125"/>
-      <c r="BG30" s="126"/>
-      <c r="BH30" s="127" t="s">
-        <v>14</v>
-      </c>
-      <c r="BI30" s="128"/>
-      <c r="BJ30" s="128"/>
-      <c r="BK30" s="129"/>
-      <c r="BL30" s="127" t="s">
-        <v>14</v>
-      </c>
-      <c r="BM30" s="128"/>
-      <c r="BN30" s="129"/>
-      <c r="BO30" s="218" t="s">
-        <v>146</v>
-      </c>
-      <c r="BP30" s="219"/>
-      <c r="BQ30" s="219"/>
-      <c r="BR30" s="219"/>
-      <c r="BS30" s="219"/>
-      <c r="BT30" s="219"/>
-      <c r="BU30" s="219"/>
-      <c r="BV30" s="219"/>
-      <c r="BW30" s="219"/>
-      <c r="BX30" s="219"/>
-      <c r="BY30" s="219"/>
-      <c r="BZ30" s="219"/>
-      <c r="CA30" s="219"/>
-      <c r="CB30" s="219"/>
-      <c r="CC30" s="219"/>
-      <c r="CD30" s="219"/>
-      <c r="CE30" s="219"/>
-      <c r="CF30" s="219"/>
-      <c r="CG30" s="219"/>
-      <c r="CH30" s="219"/>
-      <c r="CI30" s="220"/>
+      <c r="AO30" s="190"/>
+      <c r="AP30" s="190"/>
+      <c r="AQ30" s="190"/>
+      <c r="AR30" s="190"/>
+      <c r="AS30" s="190"/>
+      <c r="AT30" s="190"/>
+      <c r="AU30" s="88"/>
+      <c r="AV30" s="84" t="s">
+        <v>96</v>
+      </c>
+      <c r="AW30" s="85"/>
+      <c r="AX30" s="85"/>
+      <c r="AY30" s="85"/>
+      <c r="AZ30" s="85"/>
+      <c r="BA30" s="85"/>
+      <c r="BB30" s="85"/>
+      <c r="BC30" s="85"/>
+      <c r="BD30" s="85"/>
+      <c r="BE30" s="85"/>
+      <c r="BF30" s="85"/>
+      <c r="BG30" s="86"/>
+      <c r="BH30" s="102" t="s">
+        <v>57</v>
+      </c>
+      <c r="BI30" s="103"/>
+      <c r="BJ30" s="103"/>
+      <c r="BK30" s="104"/>
+      <c r="BL30" s="102" t="s">
+        <v>57</v>
+      </c>
+      <c r="BM30" s="103"/>
+      <c r="BN30" s="104"/>
+      <c r="BO30" s="212"/>
+      <c r="BP30" s="213"/>
+      <c r="BQ30" s="213"/>
+      <c r="BR30" s="213"/>
+      <c r="BS30" s="213"/>
+      <c r="BT30" s="213"/>
+      <c r="BU30" s="213"/>
+      <c r="BV30" s="213"/>
+      <c r="BW30" s="213"/>
+      <c r="BX30" s="213"/>
+      <c r="BY30" s="213"/>
+      <c r="BZ30" s="213"/>
+      <c r="CA30" s="213"/>
+      <c r="CB30" s="213"/>
+      <c r="CC30" s="213"/>
+      <c r="CD30" s="213"/>
+      <c r="CE30" s="213"/>
+      <c r="CF30" s="213"/>
+      <c r="CG30" s="213"/>
+      <c r="CH30" s="213"/>
+      <c r="CI30" s="214"/>
     </row>
-    <row r="31" spans="1:93" s="63" customFormat="1" ht="44.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="31" spans="1:93" s="63" customFormat="1" ht="44.25" customHeight="1">
       <c r="A31" s="96">
-        <f t="shared" ref="A31:A38" si="1">ROW()-25</f>
+        <f t="shared" si="0"/>
         <v>6</v>
       </c>
       <c r="B31" s="98"/>
       <c r="C31" s="200" t="s">
-        <v>110</v>
+        <v>99</v>
       </c>
       <c r="D31" s="201"/>
       <c r="E31" s="201"/>
@@ -7487,7 +7452,7 @@
       <c r="G31" s="201"/>
       <c r="H31" s="202"/>
       <c r="I31" s="105" t="s">
-        <v>93</v>
+        <v>100</v>
       </c>
       <c r="J31" s="106"/>
       <c r="K31" s="106"/>
@@ -7552,7 +7517,7 @@
       <c r="AT31" s="190"/>
       <c r="AU31" s="88"/>
       <c r="AV31" s="84" t="s">
-        <v>113</v>
+        <v>96</v>
       </c>
       <c r="AW31" s="85"/>
       <c r="AX31" s="85"/>
@@ -7576,38 +7541,36 @@
       </c>
       <c r="BM31" s="103"/>
       <c r="BN31" s="104"/>
-      <c r="BO31" s="209" t="s">
-        <v>147</v>
-      </c>
-      <c r="BP31" s="210"/>
-      <c r="BQ31" s="210"/>
-      <c r="BR31" s="210"/>
-      <c r="BS31" s="210"/>
-      <c r="BT31" s="210"/>
-      <c r="BU31" s="210"/>
-      <c r="BV31" s="210"/>
-      <c r="BW31" s="210"/>
-      <c r="BX31" s="210"/>
-      <c r="BY31" s="210"/>
-      <c r="BZ31" s="210"/>
-      <c r="CA31" s="210"/>
-      <c r="CB31" s="210"/>
-      <c r="CC31" s="210"/>
-      <c r="CD31" s="210"/>
-      <c r="CE31" s="210"/>
-      <c r="CF31" s="210"/>
-      <c r="CG31" s="210"/>
-      <c r="CH31" s="210"/>
-      <c r="CI31" s="211"/>
+      <c r="BO31" s="212"/>
+      <c r="BP31" s="213"/>
+      <c r="BQ31" s="213"/>
+      <c r="BR31" s="213"/>
+      <c r="BS31" s="213"/>
+      <c r="BT31" s="213"/>
+      <c r="BU31" s="213"/>
+      <c r="BV31" s="213"/>
+      <c r="BW31" s="213"/>
+      <c r="BX31" s="213"/>
+      <c r="BY31" s="213"/>
+      <c r="BZ31" s="213"/>
+      <c r="CA31" s="213"/>
+      <c r="CB31" s="213"/>
+      <c r="CC31" s="213"/>
+      <c r="CD31" s="213"/>
+      <c r="CE31" s="213"/>
+      <c r="CF31" s="213"/>
+      <c r="CG31" s="213"/>
+      <c r="CH31" s="213"/>
+      <c r="CI31" s="214"/>
     </row>
-    <row r="32" spans="1:93" s="63" customFormat="1" ht="44.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="32" spans="1:93" s="63" customFormat="1" ht="44.25" customHeight="1">
       <c r="A32" s="96">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>7</v>
       </c>
       <c r="B32" s="98"/>
       <c r="C32" s="200" t="s">
-        <v>94</v>
+        <v>111</v>
       </c>
       <c r="D32" s="201"/>
       <c r="E32" s="201"/>
@@ -7615,7 +7578,7 @@
       <c r="G32" s="201"/>
       <c r="H32" s="202"/>
       <c r="I32" s="105" t="s">
-        <v>95</v>
+        <v>101</v>
       </c>
       <c r="J32" s="106"/>
       <c r="K32" s="106"/>
@@ -7726,22 +7689,22 @@
       <c r="CH32" s="213"/>
       <c r="CI32" s="214"/>
     </row>
-    <row r="33" spans="1:90" s="63" customFormat="1" ht="44.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="33" spans="1:90" s="63" customFormat="1" ht="44.25" customHeight="1">
       <c r="A33" s="96">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>8</v>
       </c>
       <c r="B33" s="98"/>
-      <c r="C33" s="197" t="s">
-        <v>97</v>
-      </c>
-      <c r="D33" s="198"/>
-      <c r="E33" s="198"/>
-      <c r="F33" s="198"/>
-      <c r="G33" s="198"/>
-      <c r="H33" s="199"/>
+      <c r="C33" s="200" t="s">
+        <v>112</v>
+      </c>
+      <c r="D33" s="201"/>
+      <c r="E33" s="201"/>
+      <c r="F33" s="201"/>
+      <c r="G33" s="201"/>
+      <c r="H33" s="202"/>
       <c r="I33" s="105" t="s">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="J33" s="106"/>
       <c r="K33" s="106"/>
@@ -7852,22 +7815,22 @@
       <c r="CH33" s="213"/>
       <c r="CI33" s="214"/>
     </row>
-    <row r="34" spans="1:90" s="63" customFormat="1" ht="44.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="34" spans="1:90" s="63" customFormat="1" ht="44.25" customHeight="1">
       <c r="A34" s="96">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>9</v>
       </c>
       <c r="B34" s="98"/>
-      <c r="C34" s="200" t="s">
-        <v>99</v>
-      </c>
-      <c r="D34" s="201"/>
-      <c r="E34" s="201"/>
-      <c r="F34" s="201"/>
-      <c r="G34" s="201"/>
-      <c r="H34" s="202"/>
+      <c r="C34" s="197" t="s">
+        <v>103</v>
+      </c>
+      <c r="D34" s="198"/>
+      <c r="E34" s="198"/>
+      <c r="F34" s="198"/>
+      <c r="G34" s="198"/>
+      <c r="H34" s="199"/>
       <c r="I34" s="105" t="s">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="J34" s="106"/>
       <c r="K34" s="106"/>
@@ -7978,22 +7941,22 @@
       <c r="CH34" s="213"/>
       <c r="CI34" s="214"/>
     </row>
-    <row r="35" spans="1:90" s="63" customFormat="1" ht="44.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="35" spans="1:90" s="74" customFormat="1" ht="44.25" customHeight="1">
       <c r="A35" s="96">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>10</v>
       </c>
       <c r="B35" s="98"/>
-      <c r="C35" s="200" t="s">
-        <v>111</v>
-      </c>
-      <c r="D35" s="201"/>
-      <c r="E35" s="201"/>
-      <c r="F35" s="201"/>
-      <c r="G35" s="201"/>
-      <c r="H35" s="202"/>
+      <c r="C35" s="197" t="s">
+        <v>122</v>
+      </c>
+      <c r="D35" s="198"/>
+      <c r="E35" s="198"/>
+      <c r="F35" s="198"/>
+      <c r="G35" s="198"/>
+      <c r="H35" s="199"/>
       <c r="I35" s="105" t="s">
-        <v>101</v>
+        <v>123</v>
       </c>
       <c r="J35" s="106"/>
       <c r="K35" s="106"/>
@@ -8006,16 +7969,16 @@
       <c r="P35" s="90"/>
       <c r="Q35" s="91"/>
       <c r="R35" s="34" t="s">
-        <v>57</v>
+        <v>14</v>
       </c>
       <c r="S35" s="34" t="s">
-        <v>57</v>
+        <v>14</v>
       </c>
       <c r="T35" s="34" t="s">
         <v>42</v>
       </c>
       <c r="U35" s="34" t="s">
-        <v>57</v>
+        <v>14</v>
       </c>
       <c r="V35" s="203">
         <v>255</v>
@@ -8023,7 +7986,7 @@
       <c r="W35" s="204"/>
       <c r="X35" s="205"/>
       <c r="Y35" s="203" t="s">
-        <v>57</v>
+        <v>14</v>
       </c>
       <c r="Z35" s="204"/>
       <c r="AA35" s="205"/>
@@ -8071,1224 +8034,1122 @@
       <c r="BE35" s="85"/>
       <c r="BF35" s="85"/>
       <c r="BG35" s="86"/>
-      <c r="BH35" s="102" t="s">
-        <v>57</v>
-      </c>
-      <c r="BI35" s="103"/>
-      <c r="BJ35" s="103"/>
-      <c r="BK35" s="104"/>
-      <c r="BL35" s="102" t="s">
-        <v>57</v>
-      </c>
-      <c r="BM35" s="103"/>
-      <c r="BN35" s="104"/>
-      <c r="BO35" s="212"/>
-      <c r="BP35" s="213"/>
-      <c r="BQ35" s="213"/>
-      <c r="BR35" s="213"/>
-      <c r="BS35" s="213"/>
-      <c r="BT35" s="213"/>
-      <c r="BU35" s="213"/>
-      <c r="BV35" s="213"/>
-      <c r="BW35" s="213"/>
-      <c r="BX35" s="213"/>
-      <c r="BY35" s="213"/>
-      <c r="BZ35" s="213"/>
-      <c r="CA35" s="213"/>
-      <c r="CB35" s="213"/>
-      <c r="CC35" s="213"/>
-      <c r="CD35" s="213"/>
-      <c r="CE35" s="213"/>
-      <c r="CF35" s="213"/>
-      <c r="CG35" s="213"/>
-      <c r="CH35" s="213"/>
-      <c r="CI35" s="214"/>
+      <c r="BH35" s="127" t="s">
+        <v>14</v>
+      </c>
+      <c r="BI35" s="128"/>
+      <c r="BJ35" s="128"/>
+      <c r="BK35" s="129"/>
+      <c r="BL35" s="127" t="s">
+        <v>14</v>
+      </c>
+      <c r="BM35" s="128"/>
+      <c r="BN35" s="129"/>
+      <c r="BO35" s="215"/>
+      <c r="BP35" s="216"/>
+      <c r="BQ35" s="216"/>
+      <c r="BR35" s="216"/>
+      <c r="BS35" s="216"/>
+      <c r="BT35" s="216"/>
+      <c r="BU35" s="216"/>
+      <c r="BV35" s="216"/>
+      <c r="BW35" s="216"/>
+      <c r="BX35" s="216"/>
+      <c r="BY35" s="216"/>
+      <c r="BZ35" s="216"/>
+      <c r="CA35" s="216"/>
+      <c r="CB35" s="216"/>
+      <c r="CC35" s="216"/>
+      <c r="CD35" s="216"/>
+      <c r="CE35" s="216"/>
+      <c r="CF35" s="216"/>
+      <c r="CG35" s="216"/>
+      <c r="CH35" s="216"/>
+      <c r="CI35" s="217"/>
     </row>
-    <row r="36" spans="1:90" s="63" customFormat="1" ht="44.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A36" s="96">
-        <f t="shared" si="1"/>
-        <v>11</v>
-      </c>
-      <c r="B36" s="98"/>
-      <c r="C36" s="200" t="s">
-        <v>112</v>
-      </c>
-      <c r="D36" s="201"/>
-      <c r="E36" s="201"/>
-      <c r="F36" s="201"/>
-      <c r="G36" s="201"/>
-      <c r="H36" s="202"/>
-      <c r="I36" s="105" t="s">
-        <v>102</v>
-      </c>
-      <c r="J36" s="106"/>
-      <c r="K36" s="106"/>
-      <c r="L36" s="106"/>
-      <c r="M36" s="106"/>
-      <c r="N36" s="107"/>
-      <c r="O36" s="89" t="s">
-        <v>46</v>
-      </c>
-      <c r="P36" s="90"/>
-      <c r="Q36" s="91"/>
-      <c r="R36" s="34" t="s">
-        <v>57</v>
-      </c>
-      <c r="S36" s="34" t="s">
-        <v>57</v>
-      </c>
-      <c r="T36" s="34" t="s">
-        <v>42</v>
-      </c>
-      <c r="U36" s="34" t="s">
-        <v>57</v>
-      </c>
-      <c r="V36" s="203">
-        <v>255</v>
-      </c>
-      <c r="W36" s="204"/>
-      <c r="X36" s="205"/>
-      <c r="Y36" s="203" t="s">
-        <v>57</v>
-      </c>
-      <c r="Z36" s="204"/>
-      <c r="AA36" s="205"/>
-      <c r="AB36" s="87" t="s">
-        <v>47</v>
-      </c>
-      <c r="AC36" s="190"/>
-      <c r="AD36" s="190"/>
-      <c r="AE36" s="190"/>
-      <c r="AF36" s="88"/>
-      <c r="AG36" s="87" t="s">
+    <row r="36" spans="1:90" s="18" customFormat="1">
+      <c r="A36" s="35"/>
+      <c r="B36" s="35"/>
+      <c r="C36" s="36"/>
+      <c r="D36" s="36"/>
+      <c r="E36" s="36"/>
+      <c r="F36" s="36"/>
+      <c r="G36" s="36"/>
+      <c r="H36" s="36"/>
+      <c r="I36" s="36"/>
+      <c r="J36" s="36"/>
+      <c r="K36" s="36"/>
+      <c r="L36" s="36"/>
+      <c r="M36" s="36"/>
+      <c r="N36" s="36"/>
+      <c r="O36" s="36"/>
+      <c r="P36" s="36"/>
+      <c r="Q36" s="37"/>
+      <c r="R36" s="37"/>
+      <c r="S36" s="37"/>
+      <c r="T36" s="37"/>
+      <c r="U36" s="37"/>
+      <c r="V36" s="37"/>
+      <c r="W36" s="37"/>
+      <c r="X36" s="37"/>
+      <c r="Y36" s="37"/>
+      <c r="Z36" s="37"/>
+      <c r="AA36" s="37"/>
+      <c r="AB36" s="37"/>
+      <c r="AC36" s="37"/>
+      <c r="AD36" s="37"/>
+      <c r="AE36" s="37"/>
+      <c r="AF36" s="37"/>
+      <c r="AG36" s="37"/>
+      <c r="AH36" s="37"/>
+      <c r="AI36" s="37"/>
+      <c r="AJ36" s="37"/>
+      <c r="AK36" s="36"/>
+      <c r="AL36" s="37"/>
+      <c r="AM36" s="36"/>
+      <c r="AN36" s="36"/>
+      <c r="AO36" s="36"/>
+      <c r="AP36" s="36"/>
+      <c r="AQ36" s="36"/>
+      <c r="AR36" s="37"/>
+      <c r="AS36" s="37"/>
+      <c r="AT36" s="37"/>
+      <c r="AU36" s="37"/>
+      <c r="AV36" s="38"/>
+      <c r="AW36" s="37"/>
+      <c r="AX36" s="36"/>
+      <c r="AY36" s="36"/>
+      <c r="AZ36" s="36"/>
+      <c r="BA36" s="36"/>
+      <c r="BB36" s="36"/>
+      <c r="BC36" s="36"/>
+      <c r="BD36" s="36"/>
+      <c r="BE36" s="36"/>
+      <c r="BF36" s="36"/>
+      <c r="BG36" s="36"/>
+      <c r="BH36" s="36"/>
+      <c r="BI36" s="36"/>
+      <c r="BJ36" s="36"/>
+      <c r="BK36" s="36"/>
+      <c r="BL36" s="36"/>
+      <c r="BM36" s="36"/>
+      <c r="BN36" s="36"/>
+      <c r="BO36" s="36"/>
+      <c r="BP36" s="36"/>
+      <c r="BQ36" s="36"/>
+      <c r="BR36" s="36"/>
+      <c r="BS36" s="36"/>
+      <c r="BT36" s="36"/>
+      <c r="BU36" s="36"/>
+      <c r="BV36" s="36"/>
+      <c r="BW36" s="36"/>
+      <c r="BX36" s="36"/>
+      <c r="BY36" s="36"/>
+      <c r="BZ36" s="36"/>
+      <c r="CA36" s="36"/>
+      <c r="CB36" s="36"/>
+      <c r="CC36" s="36"/>
+      <c r="CD36" s="36"/>
+      <c r="CE36" s="39"/>
+      <c r="CF36" s="39"/>
+      <c r="CG36" s="39"/>
+      <c r="CH36" s="39"/>
+      <c r="CI36" s="39"/>
+      <c r="CJ36" s="39"/>
+      <c r="CK36" s="39"/>
+      <c r="CL36" s="39"/>
+    </row>
+    <row r="37" spans="1:90" s="18" customFormat="1">
+      <c r="A37" s="194" t="s">
+        <v>60</v>
+      </c>
+      <c r="B37" s="195"/>
+      <c r="C37" s="195"/>
+      <c r="D37" s="195"/>
+      <c r="E37" s="195"/>
+      <c r="F37" s="195"/>
+      <c r="G37" s="195"/>
+      <c r="H37" s="196"/>
+      <c r="I37" s="16"/>
+      <c r="J37" s="16"/>
+      <c r="K37" s="16"/>
+      <c r="L37" s="16"/>
+      <c r="M37" s="16"/>
+      <c r="N37" s="16"/>
+      <c r="O37" s="16"/>
+      <c r="P37" s="16"/>
+      <c r="Q37" s="16"/>
+      <c r="R37" s="16"/>
+      <c r="S37" s="16"/>
+      <c r="T37" s="16"/>
+      <c r="U37" s="16"/>
+      <c r="V37" s="16"/>
+      <c r="W37" s="16"/>
+      <c r="X37" s="16"/>
+      <c r="Y37" s="16"/>
+      <c r="Z37" s="16"/>
+      <c r="AA37" s="16"/>
+      <c r="AB37" s="16"/>
+      <c r="AC37" s="16"/>
+      <c r="AD37" s="16"/>
+      <c r="AE37" s="16"/>
+      <c r="AF37" s="16"/>
+      <c r="AG37" s="16"/>
+      <c r="AH37" s="16"/>
+      <c r="AI37" s="16"/>
+      <c r="AJ37" s="16"/>
+      <c r="AK37" s="16"/>
+      <c r="AL37" s="16"/>
+      <c r="AM37" s="16"/>
+      <c r="AN37" s="16"/>
+      <c r="AO37" s="16"/>
+      <c r="AP37" s="16"/>
+      <c r="AQ37" s="16"/>
+      <c r="AR37" s="16"/>
+      <c r="AS37" s="16"/>
+      <c r="AT37" s="16"/>
+      <c r="AU37" s="16"/>
+      <c r="AV37" s="16"/>
+      <c r="AW37" s="16"/>
+      <c r="AX37" s="16"/>
+      <c r="AY37" s="16"/>
+      <c r="AZ37" s="16"/>
+      <c r="BA37" s="16"/>
+      <c r="BB37" s="16"/>
+      <c r="BC37" s="16"/>
+      <c r="BD37" s="16"/>
+      <c r="BE37" s="16"/>
+      <c r="BF37" s="16"/>
+      <c r="BG37" s="16"/>
+      <c r="BH37" s="16"/>
+      <c r="BI37" s="16"/>
+      <c r="BJ37" s="16"/>
+      <c r="BK37" s="16"/>
+      <c r="BL37" s="16"/>
+      <c r="BM37" s="16"/>
+      <c r="BN37" s="16"/>
+      <c r="BO37" s="16"/>
+      <c r="BP37" s="16"/>
+      <c r="BQ37" s="16"/>
+      <c r="BR37" s="16"/>
+      <c r="BS37" s="16"/>
+      <c r="BT37" s="16"/>
+      <c r="BU37" s="16"/>
+      <c r="BV37" s="16"/>
+      <c r="BW37" s="16"/>
+      <c r="BX37" s="16"/>
+      <c r="BY37" s="16"/>
+      <c r="BZ37" s="16"/>
+      <c r="CA37" s="16"/>
+      <c r="CB37" s="16"/>
+      <c r="CC37" s="16"/>
+      <c r="CD37" s="16"/>
+      <c r="CE37" s="16"/>
+      <c r="CF37" s="16"/>
+      <c r="CG37" s="16"/>
+      <c r="CH37" s="16"/>
+      <c r="CI37" s="16"/>
+    </row>
+    <row r="38" spans="1:90" s="19" customFormat="1">
+      <c r="A38" s="112" t="s">
+        <v>32</v>
+      </c>
+      <c r="B38" s="114"/>
+      <c r="C38" s="112" t="s">
+        <v>61</v>
+      </c>
+      <c r="D38" s="113"/>
+      <c r="E38" s="113"/>
+      <c r="F38" s="113"/>
+      <c r="G38" s="113"/>
+      <c r="H38" s="114"/>
+      <c r="I38" s="112" t="s">
+        <v>33</v>
+      </c>
+      <c r="J38" s="113"/>
+      <c r="K38" s="113"/>
+      <c r="L38" s="113"/>
+      <c r="M38" s="113"/>
+      <c r="N38" s="114"/>
+      <c r="O38" s="181" t="s">
+        <v>62</v>
+      </c>
+      <c r="P38" s="182"/>
+      <c r="Q38" s="183"/>
+      <c r="R38" s="130" t="s">
+        <v>34</v>
+      </c>
+      <c r="S38" s="131"/>
+      <c r="T38" s="131"/>
+      <c r="U38" s="132"/>
+      <c r="V38" s="181" t="s">
+        <v>35</v>
+      </c>
+      <c r="W38" s="182"/>
+      <c r="X38" s="183"/>
+      <c r="Y38" s="181" t="s">
+        <v>36</v>
+      </c>
+      <c r="Z38" s="182"/>
+      <c r="AA38" s="183"/>
+      <c r="AB38" s="112" t="s">
+        <v>37</v>
+      </c>
+      <c r="AC38" s="113"/>
+      <c r="AD38" s="113"/>
+      <c r="AE38" s="113"/>
+      <c r="AF38" s="114"/>
+      <c r="AG38" s="112" t="s">
+        <v>63</v>
+      </c>
+      <c r="AH38" s="114"/>
+      <c r="AI38" s="112" t="s">
+        <v>44</v>
+      </c>
+      <c r="AJ38" s="114"/>
+      <c r="AK38" s="112" t="s">
+        <v>45</v>
+      </c>
+      <c r="AL38" s="113"/>
+      <c r="AM38" s="114"/>
+      <c r="AN38" s="112" t="s">
+        <v>38</v>
+      </c>
+      <c r="AO38" s="113"/>
+      <c r="AP38" s="113"/>
+      <c r="AQ38" s="113"/>
+      <c r="AR38" s="113"/>
+      <c r="AS38" s="113"/>
+      <c r="AT38" s="113"/>
+      <c r="AU38" s="114"/>
+      <c r="AV38" s="112" t="s">
+        <v>39</v>
+      </c>
+      <c r="AW38" s="113"/>
+      <c r="AX38" s="113"/>
+      <c r="AY38" s="113"/>
+      <c r="AZ38" s="113"/>
+      <c r="BA38" s="113"/>
+      <c r="BB38" s="113"/>
+      <c r="BC38" s="113"/>
+      <c r="BD38" s="113"/>
+      <c r="BE38" s="113"/>
+      <c r="BF38" s="113"/>
+      <c r="BG38" s="114"/>
+      <c r="BH38" s="108" t="s">
+        <v>40</v>
+      </c>
+      <c r="BI38" s="109"/>
+      <c r="BJ38" s="109"/>
+      <c r="BK38" s="109"/>
+      <c r="BL38" s="108" t="s">
+        <v>65</v>
+      </c>
+      <c r="BM38" s="109"/>
+      <c r="BN38" s="109"/>
+      <c r="BO38" s="112" t="s">
+        <v>41</v>
+      </c>
+      <c r="BP38" s="113"/>
+      <c r="BQ38" s="113"/>
+      <c r="BR38" s="113"/>
+      <c r="BS38" s="113"/>
+      <c r="BT38" s="113"/>
+      <c r="BU38" s="113"/>
+      <c r="BV38" s="113"/>
+      <c r="BW38" s="113"/>
+      <c r="BX38" s="113"/>
+      <c r="BY38" s="113"/>
+      <c r="BZ38" s="113"/>
+      <c r="CA38" s="113"/>
+      <c r="CB38" s="113"/>
+      <c r="CC38" s="113"/>
+      <c r="CD38" s="113"/>
+      <c r="CE38" s="113"/>
+      <c r="CF38" s="113"/>
+      <c r="CG38" s="113"/>
+      <c r="CH38" s="113"/>
+      <c r="CI38" s="114"/>
+    </row>
+    <row r="39" spans="1:90" s="19" customFormat="1" ht="83.25" customHeight="1">
+      <c r="A39" s="115"/>
+      <c r="B39" s="117"/>
+      <c r="C39" s="115"/>
+      <c r="D39" s="116"/>
+      <c r="E39" s="116"/>
+      <c r="F39" s="116"/>
+      <c r="G39" s="116"/>
+      <c r="H39" s="117"/>
+      <c r="I39" s="115"/>
+      <c r="J39" s="116"/>
+      <c r="K39" s="116"/>
+      <c r="L39" s="116"/>
+      <c r="M39" s="116"/>
+      <c r="N39" s="117"/>
+      <c r="O39" s="184"/>
+      <c r="P39" s="185"/>
+      <c r="Q39" s="186"/>
+      <c r="R39" s="17" t="s">
+        <v>54</v>
+      </c>
+      <c r="S39" s="17" t="s">
+        <v>66</v>
+      </c>
+      <c r="T39" s="17" t="s">
+        <v>55</v>
+      </c>
+      <c r="U39" s="17" t="s">
+        <v>56</v>
+      </c>
+      <c r="V39" s="184"/>
+      <c r="W39" s="185"/>
+      <c r="X39" s="186"/>
+      <c r="Y39" s="184"/>
+      <c r="Z39" s="185"/>
+      <c r="AA39" s="186"/>
+      <c r="AB39" s="115"/>
+      <c r="AC39" s="116"/>
+      <c r="AD39" s="116"/>
+      <c r="AE39" s="116"/>
+      <c r="AF39" s="117"/>
+      <c r="AG39" s="115"/>
+      <c r="AH39" s="117"/>
+      <c r="AI39" s="115"/>
+      <c r="AJ39" s="117"/>
+      <c r="AK39" s="115"/>
+      <c r="AL39" s="116"/>
+      <c r="AM39" s="117"/>
+      <c r="AN39" s="115"/>
+      <c r="AO39" s="116"/>
+      <c r="AP39" s="116"/>
+      <c r="AQ39" s="116"/>
+      <c r="AR39" s="116"/>
+      <c r="AS39" s="116"/>
+      <c r="AT39" s="116"/>
+      <c r="AU39" s="117"/>
+      <c r="AV39" s="115"/>
+      <c r="AW39" s="116"/>
+      <c r="AX39" s="116"/>
+      <c r="AY39" s="116"/>
+      <c r="AZ39" s="116"/>
+      <c r="BA39" s="116"/>
+      <c r="BB39" s="116"/>
+      <c r="BC39" s="116"/>
+      <c r="BD39" s="116"/>
+      <c r="BE39" s="116"/>
+      <c r="BF39" s="116"/>
+      <c r="BG39" s="117"/>
+      <c r="BH39" s="110"/>
+      <c r="BI39" s="111"/>
+      <c r="BJ39" s="111"/>
+      <c r="BK39" s="111"/>
+      <c r="BL39" s="110"/>
+      <c r="BM39" s="111"/>
+      <c r="BN39" s="111"/>
+      <c r="BO39" s="115"/>
+      <c r="BP39" s="116"/>
+      <c r="BQ39" s="116"/>
+      <c r="BR39" s="116"/>
+      <c r="BS39" s="116"/>
+      <c r="BT39" s="116"/>
+      <c r="BU39" s="116"/>
+      <c r="BV39" s="116"/>
+      <c r="BW39" s="116"/>
+      <c r="BX39" s="116"/>
+      <c r="BY39" s="116"/>
+      <c r="BZ39" s="116"/>
+      <c r="CA39" s="116"/>
+      <c r="CB39" s="116"/>
+      <c r="CC39" s="116"/>
+      <c r="CD39" s="116"/>
+      <c r="CE39" s="116"/>
+      <c r="CF39" s="116"/>
+      <c r="CG39" s="116"/>
+      <c r="CH39" s="116"/>
+      <c r="CI39" s="117"/>
+    </row>
+    <row r="40" spans="1:90" s="19" customFormat="1">
+      <c r="A40" s="96" t="s">
+        <v>59</v>
+      </c>
+      <c r="B40" s="98"/>
+      <c r="C40" s="96" t="s">
+        <v>67</v>
+      </c>
+      <c r="D40" s="97"/>
+      <c r="E40" s="97"/>
+      <c r="F40" s="97"/>
+      <c r="G40" s="97"/>
+      <c r="H40" s="98"/>
+      <c r="I40" s="87" t="s">
+        <v>59</v>
+      </c>
+      <c r="J40" s="190"/>
+      <c r="K40" s="190"/>
+      <c r="L40" s="190"/>
+      <c r="M40" s="190"/>
+      <c r="N40" s="88"/>
+      <c r="O40" s="89" t="s">
         <v>51</v>
       </c>
-      <c r="AH36" s="88"/>
-      <c r="AI36" s="87" t="s">
-        <v>42</v>
-      </c>
-      <c r="AJ36" s="88"/>
-      <c r="AK36" s="89" t="s">
+      <c r="P40" s="90"/>
+      <c r="Q40" s="91"/>
+      <c r="R40" s="14" t="s">
+        <v>67</v>
+      </c>
+      <c r="S40" s="14" t="s">
+        <v>58</v>
+      </c>
+      <c r="T40" s="14" t="s">
+        <v>59</v>
+      </c>
+      <c r="U40" s="14" t="s">
+        <v>67</v>
+      </c>
+      <c r="V40" s="191" t="s">
+        <v>58</v>
+      </c>
+      <c r="W40" s="192"/>
+      <c r="X40" s="193"/>
+      <c r="Y40" s="191" t="s">
+        <v>59</v>
+      </c>
+      <c r="Z40" s="192"/>
+      <c r="AA40" s="193"/>
+      <c r="AB40" s="96" t="s">
         <v>51</v>
       </c>
-      <c r="AL36" s="90"/>
-      <c r="AM36" s="91"/>
-      <c r="AN36" s="87" t="s">
+      <c r="AC40" s="97"/>
+      <c r="AD40" s="97"/>
+      <c r="AE40" s="97"/>
+      <c r="AF40" s="98"/>
+      <c r="AG40" s="96" t="s">
         <v>51</v>
       </c>
-      <c r="AO36" s="190"/>
-      <c r="AP36" s="190"/>
-      <c r="AQ36" s="190"/>
-      <c r="AR36" s="190"/>
-      <c r="AS36" s="190"/>
-      <c r="AT36" s="190"/>
-      <c r="AU36" s="88"/>
-      <c r="AV36" s="84" t="s">
-        <v>96</v>
-      </c>
-      <c r="AW36" s="85"/>
-      <c r="AX36" s="85"/>
-      <c r="AY36" s="85"/>
-      <c r="AZ36" s="85"/>
-      <c r="BA36" s="85"/>
-      <c r="BB36" s="85"/>
-      <c r="BC36" s="85"/>
-      <c r="BD36" s="85"/>
-      <c r="BE36" s="85"/>
-      <c r="BF36" s="85"/>
-      <c r="BG36" s="86"/>
-      <c r="BH36" s="102" t="s">
-        <v>57</v>
-      </c>
-      <c r="BI36" s="103"/>
-      <c r="BJ36" s="103"/>
-      <c r="BK36" s="104"/>
-      <c r="BL36" s="102" t="s">
-        <v>57</v>
-      </c>
-      <c r="BM36" s="103"/>
-      <c r="BN36" s="104"/>
-      <c r="BO36" s="212"/>
-      <c r="BP36" s="213"/>
-      <c r="BQ36" s="213"/>
-      <c r="BR36" s="213"/>
-      <c r="BS36" s="213"/>
-      <c r="BT36" s="213"/>
-      <c r="BU36" s="213"/>
-      <c r="BV36" s="213"/>
-      <c r="BW36" s="213"/>
-      <c r="BX36" s="213"/>
-      <c r="BY36" s="213"/>
-      <c r="BZ36" s="213"/>
-      <c r="CA36" s="213"/>
-      <c r="CB36" s="213"/>
-      <c r="CC36" s="213"/>
-      <c r="CD36" s="213"/>
-      <c r="CE36" s="213"/>
-      <c r="CF36" s="213"/>
-      <c r="CG36" s="213"/>
-      <c r="CH36" s="213"/>
-      <c r="CI36" s="214"/>
+      <c r="AH40" s="98"/>
+      <c r="AI40" s="96" t="s">
+        <v>51</v>
+      </c>
+      <c r="AJ40" s="98"/>
+      <c r="AK40" s="89" t="s">
+        <v>51</v>
+      </c>
+      <c r="AL40" s="90"/>
+      <c r="AM40" s="91"/>
+      <c r="AN40" s="96" t="s">
+        <v>51</v>
+      </c>
+      <c r="AO40" s="97"/>
+      <c r="AP40" s="97"/>
+      <c r="AQ40" s="97"/>
+      <c r="AR40" s="97"/>
+      <c r="AS40" s="97"/>
+      <c r="AT40" s="97"/>
+      <c r="AU40" s="98"/>
+      <c r="AV40" s="99" t="s">
+        <v>58</v>
+      </c>
+      <c r="AW40" s="100"/>
+      <c r="AX40" s="100"/>
+      <c r="AY40" s="100"/>
+      <c r="AZ40" s="100"/>
+      <c r="BA40" s="100"/>
+      <c r="BB40" s="100"/>
+      <c r="BC40" s="100"/>
+      <c r="BD40" s="100"/>
+      <c r="BE40" s="100"/>
+      <c r="BF40" s="100"/>
+      <c r="BG40" s="101"/>
+      <c r="BH40" s="102" t="s">
+        <v>67</v>
+      </c>
+      <c r="BI40" s="103"/>
+      <c r="BJ40" s="103"/>
+      <c r="BK40" s="104"/>
+      <c r="BL40" s="102" t="s">
+        <v>59</v>
+      </c>
+      <c r="BM40" s="103"/>
+      <c r="BN40" s="104"/>
+      <c r="BO40" s="102" t="s">
+        <v>58</v>
+      </c>
+      <c r="BP40" s="103"/>
+      <c r="BQ40" s="103"/>
+      <c r="BR40" s="103"/>
+      <c r="BS40" s="103"/>
+      <c r="BT40" s="103"/>
+      <c r="BU40" s="103"/>
+      <c r="BV40" s="103"/>
+      <c r="BW40" s="103"/>
+      <c r="BX40" s="103"/>
+      <c r="BY40" s="103"/>
+      <c r="BZ40" s="103"/>
+      <c r="CA40" s="103"/>
+      <c r="CB40" s="103"/>
+      <c r="CC40" s="103"/>
+      <c r="CD40" s="103"/>
+      <c r="CE40" s="103"/>
+      <c r="CF40" s="103"/>
+      <c r="CG40" s="103"/>
+      <c r="CH40" s="103"/>
+      <c r="CI40" s="104"/>
     </row>
-    <row r="37" spans="1:90" s="63" customFormat="1" ht="44.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A37" s="96">
-        <f t="shared" si="1"/>
-        <v>12</v>
-      </c>
-      <c r="B37" s="98"/>
-      <c r="C37" s="197" t="s">
-        <v>103</v>
-      </c>
-      <c r="D37" s="198"/>
-      <c r="E37" s="198"/>
-      <c r="F37" s="198"/>
-      <c r="G37" s="198"/>
-      <c r="H37" s="199"/>
-      <c r="I37" s="105" t="s">
-        <v>104</v>
-      </c>
-      <c r="J37" s="106"/>
-      <c r="K37" s="106"/>
-      <c r="L37" s="106"/>
-      <c r="M37" s="106"/>
-      <c r="N37" s="107"/>
-      <c r="O37" s="89" t="s">
-        <v>46</v>
-      </c>
-      <c r="P37" s="90"/>
-      <c r="Q37" s="91"/>
-      <c r="R37" s="34" t="s">
-        <v>57</v>
-      </c>
-      <c r="S37" s="34" t="s">
-        <v>57</v>
-      </c>
-      <c r="T37" s="34" t="s">
-        <v>42</v>
-      </c>
-      <c r="U37" s="34" t="s">
-        <v>57</v>
-      </c>
-      <c r="V37" s="203">
-        <v>255</v>
-      </c>
-      <c r="W37" s="204"/>
-      <c r="X37" s="205"/>
-      <c r="Y37" s="203" t="s">
-        <v>57</v>
-      </c>
-      <c r="Z37" s="204"/>
-      <c r="AA37" s="205"/>
-      <c r="AB37" s="87" t="s">
-        <v>47</v>
-      </c>
-      <c r="AC37" s="190"/>
-      <c r="AD37" s="190"/>
-      <c r="AE37" s="190"/>
-      <c r="AF37" s="88"/>
-      <c r="AG37" s="87" t="s">
-        <v>51</v>
-      </c>
-      <c r="AH37" s="88"/>
-      <c r="AI37" s="87" t="s">
-        <v>42</v>
-      </c>
-      <c r="AJ37" s="88"/>
-      <c r="AK37" s="89" t="s">
-        <v>51</v>
-      </c>
-      <c r="AL37" s="90"/>
-      <c r="AM37" s="91"/>
-      <c r="AN37" s="87" t="s">
-        <v>51</v>
-      </c>
-      <c r="AO37" s="190"/>
-      <c r="AP37" s="190"/>
-      <c r="AQ37" s="190"/>
-      <c r="AR37" s="190"/>
-      <c r="AS37" s="190"/>
-      <c r="AT37" s="190"/>
-      <c r="AU37" s="88"/>
-      <c r="AV37" s="84" t="s">
-        <v>96</v>
-      </c>
-      <c r="AW37" s="85"/>
-      <c r="AX37" s="85"/>
-      <c r="AY37" s="85"/>
-      <c r="AZ37" s="85"/>
-      <c r="BA37" s="85"/>
-      <c r="BB37" s="85"/>
-      <c r="BC37" s="85"/>
-      <c r="BD37" s="85"/>
-      <c r="BE37" s="85"/>
-      <c r="BF37" s="85"/>
-      <c r="BG37" s="86"/>
-      <c r="BH37" s="102" t="s">
-        <v>57</v>
-      </c>
-      <c r="BI37" s="103"/>
-      <c r="BJ37" s="103"/>
-      <c r="BK37" s="104"/>
-      <c r="BL37" s="102" t="s">
-        <v>57</v>
-      </c>
-      <c r="BM37" s="103"/>
-      <c r="BN37" s="104"/>
-      <c r="BO37" s="212"/>
-      <c r="BP37" s="213"/>
-      <c r="BQ37" s="213"/>
-      <c r="BR37" s="213"/>
-      <c r="BS37" s="213"/>
-      <c r="BT37" s="213"/>
-      <c r="BU37" s="213"/>
-      <c r="BV37" s="213"/>
-      <c r="BW37" s="213"/>
-      <c r="BX37" s="213"/>
-      <c r="BY37" s="213"/>
-      <c r="BZ37" s="213"/>
-      <c r="CA37" s="213"/>
-      <c r="CB37" s="213"/>
-      <c r="CC37" s="213"/>
-      <c r="CD37" s="213"/>
-      <c r="CE37" s="213"/>
-      <c r="CF37" s="213"/>
-      <c r="CG37" s="213"/>
-      <c r="CH37" s="213"/>
-      <c r="CI37" s="214"/>
+    <row r="41" spans="1:90" s="29" customFormat="1">
+      <c r="A41" s="40"/>
+      <c r="B41" s="40"/>
+      <c r="C41" s="41"/>
+      <c r="D41" s="41"/>
+      <c r="E41" s="41"/>
+      <c r="F41" s="41"/>
+      <c r="G41" s="41"/>
+      <c r="H41" s="41"/>
+      <c r="I41" s="41"/>
+      <c r="J41" s="41"/>
+      <c r="K41" s="41"/>
+      <c r="L41" s="41"/>
+      <c r="M41" s="41"/>
+      <c r="N41" s="41"/>
+      <c r="O41" s="41"/>
+      <c r="P41" s="41"/>
+      <c r="Q41" s="42"/>
+      <c r="R41" s="42"/>
+      <c r="S41" s="42"/>
+      <c r="T41" s="42"/>
+      <c r="U41" s="42"/>
+      <c r="V41" s="42"/>
+      <c r="W41" s="42"/>
+      <c r="X41" s="42"/>
+      <c r="Y41" s="42"/>
+      <c r="Z41" s="42"/>
+      <c r="AA41" s="42"/>
+      <c r="AB41" s="42"/>
+      <c r="AC41" s="42"/>
+      <c r="AD41" s="42"/>
+      <c r="AE41" s="42"/>
+      <c r="AF41" s="42"/>
+      <c r="AG41" s="42"/>
+      <c r="AH41" s="42"/>
+      <c r="AI41" s="42"/>
+      <c r="AJ41" s="42"/>
+      <c r="AK41" s="41"/>
+      <c r="AL41" s="42"/>
+      <c r="AM41" s="41"/>
+      <c r="AN41" s="41"/>
+      <c r="AO41" s="41"/>
+      <c r="AP41" s="41"/>
+      <c r="AQ41" s="41"/>
+      <c r="AR41" s="42"/>
+      <c r="AS41" s="42"/>
+      <c r="AT41" s="42"/>
+      <c r="AU41" s="42"/>
+      <c r="AV41" s="43"/>
+      <c r="AW41" s="42"/>
+      <c r="AX41" s="41"/>
+      <c r="AY41" s="41"/>
+      <c r="AZ41" s="41"/>
+      <c r="BA41" s="41"/>
+      <c r="BB41" s="41"/>
+      <c r="BC41" s="41"/>
+      <c r="BD41" s="41"/>
+      <c r="BE41" s="41"/>
+      <c r="BF41" s="41"/>
+      <c r="BG41" s="41"/>
+      <c r="BH41" s="41"/>
+      <c r="BI41" s="41"/>
+      <c r="BJ41" s="41"/>
+      <c r="BK41" s="41"/>
+      <c r="BL41" s="41"/>
+      <c r="BM41" s="41"/>
+      <c r="BN41" s="41"/>
+      <c r="BO41" s="41"/>
+      <c r="BP41" s="41"/>
+      <c r="BQ41" s="41"/>
+      <c r="BR41" s="41"/>
+      <c r="BS41" s="41"/>
+      <c r="BT41" s="41"/>
+      <c r="BU41" s="41"/>
+      <c r="BV41" s="41"/>
+      <c r="BW41" s="41"/>
+      <c r="BX41" s="41"/>
+      <c r="BY41" s="41"/>
+      <c r="BZ41" s="41"/>
+      <c r="CA41" s="41"/>
+      <c r="CB41" s="41"/>
+      <c r="CC41" s="41"/>
+      <c r="CD41" s="41"/>
+      <c r="CE41" s="44"/>
+      <c r="CF41" s="44"/>
+      <c r="CG41" s="44"/>
+      <c r="CH41" s="44"/>
+      <c r="CI41" s="44"/>
+      <c r="CJ41" s="44"/>
+      <c r="CK41" s="44"/>
+      <c r="CL41" s="44"/>
     </row>
-    <row r="38" spans="1:90" s="74" customFormat="1" ht="44.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A38" s="96">
-        <f t="shared" si="1"/>
-        <v>13</v>
-      </c>
-      <c r="B38" s="98"/>
-      <c r="C38" s="197" t="s">
-        <v>122</v>
-      </c>
-      <c r="D38" s="198"/>
-      <c r="E38" s="198"/>
-      <c r="F38" s="198"/>
-      <c r="G38" s="198"/>
-      <c r="H38" s="199"/>
-      <c r="I38" s="105" t="s">
-        <v>123</v>
-      </c>
-      <c r="J38" s="106"/>
-      <c r="K38" s="106"/>
-      <c r="L38" s="106"/>
-      <c r="M38" s="106"/>
-      <c r="N38" s="107"/>
-      <c r="O38" s="89" t="s">
-        <v>46</v>
-      </c>
-      <c r="P38" s="90"/>
-      <c r="Q38" s="91"/>
-      <c r="R38" s="34" t="s">
-        <v>14</v>
-      </c>
-      <c r="S38" s="34" t="s">
-        <v>14</v>
-      </c>
-      <c r="T38" s="34" t="s">
-        <v>42</v>
-      </c>
-      <c r="U38" s="34" t="s">
-        <v>14</v>
-      </c>
-      <c r="V38" s="203">
-        <v>255</v>
-      </c>
-      <c r="W38" s="204"/>
-      <c r="X38" s="205"/>
-      <c r="Y38" s="203" t="s">
-        <v>14</v>
-      </c>
-      <c r="Z38" s="204"/>
-      <c r="AA38" s="205"/>
-      <c r="AB38" s="87" t="s">
-        <v>47</v>
-      </c>
-      <c r="AC38" s="190"/>
-      <c r="AD38" s="190"/>
-      <c r="AE38" s="190"/>
-      <c r="AF38" s="88"/>
-      <c r="AG38" s="87" t="s">
-        <v>51</v>
-      </c>
-      <c r="AH38" s="88"/>
-      <c r="AI38" s="87" t="s">
-        <v>42</v>
-      </c>
-      <c r="AJ38" s="88"/>
-      <c r="AK38" s="89" t="s">
-        <v>51</v>
-      </c>
-      <c r="AL38" s="90"/>
-      <c r="AM38" s="91"/>
-      <c r="AN38" s="87" t="s">
-        <v>51</v>
-      </c>
-      <c r="AO38" s="190"/>
-      <c r="AP38" s="190"/>
-      <c r="AQ38" s="190"/>
-      <c r="AR38" s="190"/>
-      <c r="AS38" s="190"/>
-      <c r="AT38" s="190"/>
-      <c r="AU38" s="88"/>
-      <c r="AV38" s="84" t="s">
-        <v>96</v>
-      </c>
-      <c r="AW38" s="85"/>
-      <c r="AX38" s="85"/>
-      <c r="AY38" s="85"/>
-      <c r="AZ38" s="85"/>
-      <c r="BA38" s="85"/>
-      <c r="BB38" s="85"/>
-      <c r="BC38" s="85"/>
-      <c r="BD38" s="85"/>
-      <c r="BE38" s="85"/>
-      <c r="BF38" s="85"/>
-      <c r="BG38" s="86"/>
-      <c r="BH38" s="127" t="s">
-        <v>14</v>
-      </c>
-      <c r="BI38" s="128"/>
-      <c r="BJ38" s="128"/>
-      <c r="BK38" s="129"/>
-      <c r="BL38" s="127" t="s">
-        <v>14</v>
-      </c>
-      <c r="BM38" s="128"/>
-      <c r="BN38" s="129"/>
-      <c r="BO38" s="215"/>
-      <c r="BP38" s="216"/>
-      <c r="BQ38" s="216"/>
-      <c r="BR38" s="216"/>
-      <c r="BS38" s="216"/>
-      <c r="BT38" s="216"/>
-      <c r="BU38" s="216"/>
-      <c r="BV38" s="216"/>
-      <c r="BW38" s="216"/>
-      <c r="BX38" s="216"/>
-      <c r="BY38" s="216"/>
-      <c r="BZ38" s="216"/>
-      <c r="CA38" s="216"/>
-      <c r="CB38" s="216"/>
-      <c r="CC38" s="216"/>
-      <c r="CD38" s="216"/>
-      <c r="CE38" s="216"/>
-      <c r="CF38" s="216"/>
-      <c r="CG38" s="216"/>
-      <c r="CH38" s="216"/>
-      <c r="CI38" s="217"/>
+    <row r="42" spans="1:90" s="29" customFormat="1">
+      <c r="A42" s="187" t="s">
+        <v>48</v>
+      </c>
+      <c r="B42" s="188"/>
+      <c r="C42" s="188"/>
+      <c r="D42" s="188"/>
+      <c r="E42" s="188"/>
+      <c r="F42" s="188"/>
+      <c r="G42" s="188"/>
+      <c r="H42" s="189"/>
+      <c r="I42" s="45"/>
+      <c r="J42" s="45"/>
+      <c r="K42" s="45"/>
+      <c r="L42" s="45"/>
+      <c r="M42" s="45"/>
+      <c r="N42" s="45"/>
+      <c r="O42" s="45"/>
+      <c r="P42" s="45"/>
+      <c r="Q42" s="46"/>
+      <c r="R42" s="46"/>
+      <c r="S42" s="46"/>
+      <c r="T42" s="46"/>
+      <c r="U42" s="46"/>
+      <c r="V42" s="46"/>
+      <c r="W42" s="46"/>
+      <c r="X42" s="46"/>
+      <c r="Y42" s="46"/>
+      <c r="Z42" s="46"/>
+      <c r="AA42" s="46"/>
+      <c r="AB42" s="46"/>
+      <c r="AC42" s="46"/>
+      <c r="AD42" s="46"/>
+      <c r="AE42" s="46"/>
+      <c r="AF42" s="46"/>
+      <c r="AG42" s="46"/>
+      <c r="AH42" s="46"/>
+      <c r="AI42" s="46"/>
+      <c r="AJ42" s="46"/>
+      <c r="AK42" s="45"/>
+      <c r="AL42" s="46"/>
+      <c r="AM42" s="45"/>
+      <c r="AN42" s="45"/>
+      <c r="AO42" s="45"/>
+      <c r="AP42" s="45"/>
+      <c r="AQ42" s="45"/>
+      <c r="AR42" s="45"/>
+      <c r="AS42" s="45"/>
+      <c r="AT42" s="45"/>
+      <c r="AU42" s="45"/>
+      <c r="AV42" s="47"/>
+      <c r="AW42" s="45"/>
+      <c r="AX42" s="45"/>
+      <c r="AY42" s="45"/>
+      <c r="AZ42" s="45"/>
+      <c r="BA42" s="45"/>
+      <c r="BB42" s="45"/>
+      <c r="BC42" s="45"/>
+      <c r="BD42" s="45"/>
+      <c r="BE42" s="45"/>
+      <c r="BF42" s="45"/>
+      <c r="BG42" s="48"/>
+      <c r="BH42" s="48"/>
+      <c r="BI42" s="48"/>
+      <c r="BJ42" s="45"/>
+      <c r="BK42" s="45"/>
+      <c r="BL42" s="45"/>
+      <c r="BM42" s="45"/>
+      <c r="BN42" s="45"/>
+      <c r="BO42" s="45"/>
+      <c r="BP42" s="45"/>
+      <c r="BQ42" s="45"/>
+      <c r="BR42" s="45"/>
+      <c r="BS42" s="45"/>
+      <c r="BT42" s="45"/>
+      <c r="BU42" s="45"/>
+      <c r="BV42" s="45"/>
+      <c r="BW42" s="45"/>
+      <c r="BX42" s="45"/>
+      <c r="BY42" s="45"/>
+      <c r="BZ42" s="45"/>
+      <c r="CA42" s="45"/>
+      <c r="CB42" s="45"/>
+      <c r="CC42" s="45"/>
+      <c r="CD42" s="45"/>
+      <c r="CE42" s="45"/>
+      <c r="CF42" s="45"/>
+      <c r="CG42" s="45"/>
+      <c r="CH42" s="45"/>
+      <c r="CI42" s="45"/>
+      <c r="CJ42" s="45"/>
+      <c r="CK42" s="45"/>
+      <c r="CL42" s="45"/>
     </row>
-    <row r="39" spans="1:90" s="18" customFormat="1" x14ac:dyDescent="0.15">
-      <c r="A39" s="35"/>
-      <c r="B39" s="35"/>
-      <c r="C39" s="36"/>
-      <c r="D39" s="36"/>
-      <c r="E39" s="36"/>
-      <c r="F39" s="36"/>
-      <c r="G39" s="36"/>
-      <c r="H39" s="36"/>
-      <c r="I39" s="36"/>
-      <c r="J39" s="36"/>
-      <c r="K39" s="36"/>
-      <c r="L39" s="36"/>
-      <c r="M39" s="36"/>
-      <c r="N39" s="36"/>
-      <c r="O39" s="36"/>
-      <c r="P39" s="36"/>
-      <c r="Q39" s="37"/>
-      <c r="R39" s="37"/>
-      <c r="S39" s="37"/>
-      <c r="T39" s="37"/>
-      <c r="U39" s="37"/>
-      <c r="V39" s="37"/>
-      <c r="W39" s="37"/>
-      <c r="X39" s="37"/>
-      <c r="Y39" s="37"/>
-      <c r="Z39" s="37"/>
-      <c r="AA39" s="37"/>
-      <c r="AB39" s="37"/>
-      <c r="AC39" s="37"/>
-      <c r="AD39" s="37"/>
-      <c r="AE39" s="37"/>
-      <c r="AF39" s="37"/>
-      <c r="AG39" s="37"/>
-      <c r="AH39" s="37"/>
-      <c r="AI39" s="37"/>
-      <c r="AJ39" s="37"/>
-      <c r="AK39" s="36"/>
-      <c r="AL39" s="37"/>
-      <c r="AM39" s="36"/>
-      <c r="AN39" s="36"/>
-      <c r="AO39" s="36"/>
-      <c r="AP39" s="36"/>
-      <c r="AQ39" s="36"/>
-      <c r="AR39" s="37"/>
-      <c r="AS39" s="37"/>
-      <c r="AT39" s="37"/>
-      <c r="AU39" s="37"/>
-      <c r="AV39" s="38"/>
-      <c r="AW39" s="37"/>
-      <c r="AX39" s="36"/>
-      <c r="AY39" s="36"/>
-      <c r="AZ39" s="36"/>
-      <c r="BA39" s="36"/>
-      <c r="BB39" s="36"/>
-      <c r="BC39" s="36"/>
-      <c r="BD39" s="36"/>
-      <c r="BE39" s="36"/>
-      <c r="BF39" s="36"/>
-      <c r="BG39" s="36"/>
-      <c r="BH39" s="36"/>
-      <c r="BI39" s="36"/>
-      <c r="BJ39" s="36"/>
-      <c r="BK39" s="36"/>
-      <c r="BL39" s="36"/>
-      <c r="BM39" s="36"/>
-      <c r="BN39" s="36"/>
-      <c r="BO39" s="36"/>
-      <c r="BP39" s="36"/>
-      <c r="BQ39" s="36"/>
-      <c r="BR39" s="36"/>
-      <c r="BS39" s="36"/>
-      <c r="BT39" s="36"/>
-      <c r="BU39" s="36"/>
-      <c r="BV39" s="36"/>
-      <c r="BW39" s="36"/>
-      <c r="BX39" s="36"/>
-      <c r="BY39" s="36"/>
-      <c r="BZ39" s="36"/>
-      <c r="CA39" s="36"/>
-      <c r="CB39" s="36"/>
-      <c r="CC39" s="36"/>
-      <c r="CD39" s="36"/>
-      <c r="CE39" s="39"/>
-      <c r="CF39" s="39"/>
-      <c r="CG39" s="39"/>
-      <c r="CH39" s="39"/>
-      <c r="CI39" s="39"/>
-      <c r="CJ39" s="39"/>
-      <c r="CK39" s="39"/>
-      <c r="CL39" s="39"/>
+    <row r="43" spans="1:90" s="29" customFormat="1" ht="13.5" customHeight="1">
+      <c r="A43" s="64"/>
+      <c r="B43" s="65"/>
+      <c r="C43" s="65"/>
+      <c r="D43" s="65"/>
+      <c r="E43" s="65"/>
+      <c r="F43" s="65"/>
+      <c r="G43" s="65"/>
+      <c r="H43" s="65"/>
+      <c r="I43" s="65"/>
+      <c r="J43" s="65"/>
+      <c r="K43" s="65"/>
+      <c r="L43" s="65"/>
+      <c r="M43" s="65"/>
+      <c r="N43" s="65"/>
+      <c r="O43" s="65"/>
+      <c r="P43" s="65"/>
+      <c r="Q43" s="65"/>
+      <c r="R43" s="65"/>
+      <c r="S43" s="65"/>
+      <c r="T43" s="65"/>
+      <c r="U43" s="65"/>
+      <c r="V43" s="65"/>
+      <c r="W43" s="65"/>
+      <c r="X43" s="65"/>
+      <c r="Y43" s="65"/>
+      <c r="Z43" s="65"/>
+      <c r="AA43" s="65"/>
+      <c r="AB43" s="65"/>
+      <c r="AC43" s="65"/>
+      <c r="AD43" s="65"/>
+      <c r="AE43" s="65"/>
+      <c r="AF43" s="65"/>
+      <c r="AG43" s="65"/>
+      <c r="AH43" s="65"/>
+      <c r="AI43" s="65"/>
+      <c r="AJ43" s="65"/>
+      <c r="AK43" s="65"/>
+      <c r="AL43" s="65"/>
+      <c r="AM43" s="65"/>
+      <c r="AN43" s="65"/>
+      <c r="AO43" s="65"/>
+      <c r="AP43" s="65"/>
+      <c r="AQ43" s="65"/>
+      <c r="AR43" s="65"/>
+      <c r="AS43" s="65"/>
+      <c r="AT43" s="65"/>
+      <c r="AU43" s="65"/>
+      <c r="AV43" s="65"/>
+      <c r="AW43" s="65"/>
+      <c r="AX43" s="65"/>
+      <c r="AY43" s="65"/>
+      <c r="AZ43" s="65"/>
+      <c r="BA43" s="65"/>
+      <c r="BB43" s="65"/>
+      <c r="BC43" s="65"/>
+      <c r="BD43" s="65"/>
+      <c r="BE43" s="65"/>
+      <c r="BF43" s="65"/>
+      <c r="BG43" s="65"/>
+      <c r="BH43" s="65"/>
+      <c r="BI43" s="65"/>
+      <c r="BJ43" s="65"/>
+      <c r="BK43" s="65"/>
+      <c r="BL43" s="65"/>
+      <c r="BM43" s="65"/>
+      <c r="BN43" s="65"/>
+      <c r="BO43" s="65"/>
+      <c r="BP43" s="65"/>
+      <c r="BQ43" s="65"/>
+      <c r="BR43" s="65"/>
+      <c r="BS43" s="65"/>
+      <c r="BT43" s="65"/>
+      <c r="BU43" s="65"/>
+      <c r="BV43" s="65"/>
+      <c r="BW43" s="65"/>
+      <c r="BX43" s="65"/>
+      <c r="BY43" s="65"/>
+      <c r="BZ43" s="65"/>
+      <c r="CA43" s="65"/>
+      <c r="CB43" s="65"/>
+      <c r="CC43" s="65"/>
+      <c r="CD43" s="65"/>
+      <c r="CE43" s="65"/>
+      <c r="CF43" s="65"/>
+      <c r="CG43" s="65"/>
+      <c r="CH43" s="65"/>
+      <c r="CI43" s="65"/>
+      <c r="CJ43" s="65"/>
+      <c r="CK43" s="65"/>
+      <c r="CL43" s="66"/>
     </row>
-    <row r="40" spans="1:90" s="18" customFormat="1" x14ac:dyDescent="0.15">
-      <c r="A40" s="194" t="s">
-        <v>60</v>
-      </c>
-      <c r="B40" s="195"/>
-      <c r="C40" s="195"/>
-      <c r="D40" s="195"/>
-      <c r="E40" s="195"/>
-      <c r="F40" s="195"/>
-      <c r="G40" s="195"/>
-      <c r="H40" s="196"/>
-      <c r="I40" s="16"/>
-      <c r="J40" s="16"/>
-      <c r="K40" s="16"/>
-      <c r="L40" s="16"/>
-      <c r="M40" s="16"/>
-      <c r="N40" s="16"/>
-      <c r="O40" s="16"/>
-      <c r="P40" s="16"/>
-      <c r="Q40" s="16"/>
-      <c r="R40" s="16"/>
-      <c r="S40" s="16"/>
-      <c r="T40" s="16"/>
-      <c r="U40" s="16"/>
-      <c r="V40" s="16"/>
-      <c r="W40" s="16"/>
-      <c r="X40" s="16"/>
-      <c r="Y40" s="16"/>
-      <c r="Z40" s="16"/>
-      <c r="AA40" s="16"/>
-      <c r="AB40" s="16"/>
-      <c r="AC40" s="16"/>
-      <c r="AD40" s="16"/>
-      <c r="AE40" s="16"/>
-      <c r="AF40" s="16"/>
-      <c r="AG40" s="16"/>
-      <c r="AH40" s="16"/>
-      <c r="AI40" s="16"/>
-      <c r="AJ40" s="16"/>
-      <c r="AK40" s="16"/>
-      <c r="AL40" s="16"/>
-      <c r="AM40" s="16"/>
-      <c r="AN40" s="16"/>
-      <c r="AO40" s="16"/>
-      <c r="AP40" s="16"/>
-      <c r="AQ40" s="16"/>
-      <c r="AR40" s="16"/>
-      <c r="AS40" s="16"/>
-      <c r="AT40" s="16"/>
-      <c r="AU40" s="16"/>
-      <c r="AV40" s="16"/>
-      <c r="AW40" s="16"/>
-      <c r="AX40" s="16"/>
-      <c r="AY40" s="16"/>
-      <c r="AZ40" s="16"/>
-      <c r="BA40" s="16"/>
-      <c r="BB40" s="16"/>
-      <c r="BC40" s="16"/>
-      <c r="BD40" s="16"/>
-      <c r="BE40" s="16"/>
-      <c r="BF40" s="16"/>
-      <c r="BG40" s="16"/>
-      <c r="BH40" s="16"/>
-      <c r="BI40" s="16"/>
-      <c r="BJ40" s="16"/>
-      <c r="BK40" s="16"/>
-      <c r="BL40" s="16"/>
-      <c r="BM40" s="16"/>
-      <c r="BN40" s="16"/>
-      <c r="BO40" s="16"/>
-      <c r="BP40" s="16"/>
-      <c r="BQ40" s="16"/>
-      <c r="BR40" s="16"/>
-      <c r="BS40" s="16"/>
-      <c r="BT40" s="16"/>
-      <c r="BU40" s="16"/>
-      <c r="BV40" s="16"/>
-      <c r="BW40" s="16"/>
-      <c r="BX40" s="16"/>
-      <c r="BY40" s="16"/>
-      <c r="BZ40" s="16"/>
-      <c r="CA40" s="16"/>
-      <c r="CB40" s="16"/>
-      <c r="CC40" s="16"/>
-      <c r="CD40" s="16"/>
-      <c r="CE40" s="16"/>
-      <c r="CF40" s="16"/>
-      <c r="CG40" s="16"/>
-      <c r="CH40" s="16"/>
-      <c r="CI40" s="16"/>
+    <row r="44" spans="1:90" s="29" customFormat="1">
+      <c r="A44" s="67"/>
+      <c r="B44" s="68"/>
+      <c r="C44" s="68"/>
+      <c r="D44" s="68"/>
+      <c r="E44" s="68"/>
+      <c r="F44" s="68"/>
+      <c r="G44" s="68"/>
+      <c r="H44" s="68"/>
+      <c r="I44" s="68"/>
+      <c r="J44" s="68"/>
+      <c r="K44" s="68"/>
+      <c r="L44" s="68"/>
+      <c r="M44" s="68"/>
+      <c r="N44" s="68"/>
+      <c r="O44" s="68"/>
+      <c r="P44" s="68"/>
+      <c r="Q44" s="68"/>
+      <c r="R44" s="68"/>
+      <c r="S44" s="68"/>
+      <c r="T44" s="68"/>
+      <c r="U44" s="68"/>
+      <c r="V44" s="68"/>
+      <c r="W44" s="68"/>
+      <c r="X44" s="68"/>
+      <c r="Y44" s="68"/>
+      <c r="Z44" s="68"/>
+      <c r="AA44" s="68"/>
+      <c r="AB44" s="68"/>
+      <c r="AC44" s="68"/>
+      <c r="AD44" s="68"/>
+      <c r="AE44" s="68"/>
+      <c r="AF44" s="68"/>
+      <c r="AG44" s="68"/>
+      <c r="AH44" s="68"/>
+      <c r="AI44" s="68"/>
+      <c r="AJ44" s="68"/>
+      <c r="AK44" s="68"/>
+      <c r="AL44" s="68"/>
+      <c r="AM44" s="68"/>
+      <c r="AN44" s="68"/>
+      <c r="AO44" s="68"/>
+      <c r="AP44" s="68"/>
+      <c r="AQ44" s="68"/>
+      <c r="AR44" s="68"/>
+      <c r="AS44" s="68"/>
+      <c r="AT44" s="68"/>
+      <c r="AU44" s="68"/>
+      <c r="AV44" s="68"/>
+      <c r="AW44" s="68"/>
+      <c r="AX44" s="68"/>
+      <c r="AY44" s="68"/>
+      <c r="AZ44" s="68"/>
+      <c r="BA44" s="68"/>
+      <c r="BB44" s="68"/>
+      <c r="BC44" s="68"/>
+      <c r="BD44" s="68"/>
+      <c r="BE44" s="68"/>
+      <c r="BF44" s="68"/>
+      <c r="BG44" s="68"/>
+      <c r="BH44" s="68"/>
+      <c r="BI44" s="68"/>
+      <c r="BJ44" s="68"/>
+      <c r="BK44" s="68"/>
+      <c r="BL44" s="68"/>
+      <c r="BM44" s="68"/>
+      <c r="BN44" s="68"/>
+      <c r="BO44" s="68"/>
+      <c r="BP44" s="68"/>
+      <c r="BQ44" s="68"/>
+      <c r="BR44" s="68"/>
+      <c r="BS44" s="68"/>
+      <c r="BT44" s="68"/>
+      <c r="BU44" s="68"/>
+      <c r="BV44" s="68"/>
+      <c r="BW44" s="68"/>
+      <c r="BX44" s="68"/>
+      <c r="BY44" s="68"/>
+      <c r="BZ44" s="68"/>
+      <c r="CA44" s="68"/>
+      <c r="CB44" s="68"/>
+      <c r="CC44" s="68"/>
+      <c r="CD44" s="68"/>
+      <c r="CE44" s="68"/>
+      <c r="CF44" s="68"/>
+      <c r="CG44" s="68"/>
+      <c r="CH44" s="68"/>
+      <c r="CI44" s="68"/>
+      <c r="CJ44" s="68"/>
+      <c r="CK44" s="68"/>
+      <c r="CL44" s="69"/>
     </row>
-    <row r="41" spans="1:90" s="19" customFormat="1" x14ac:dyDescent="0.15">
-      <c r="A41" s="112" t="s">
-        <v>32</v>
-      </c>
-      <c r="B41" s="114"/>
-      <c r="C41" s="112" t="s">
-        <v>61</v>
-      </c>
-      <c r="D41" s="113"/>
-      <c r="E41" s="113"/>
-      <c r="F41" s="113"/>
-      <c r="G41" s="113"/>
-      <c r="H41" s="114"/>
-      <c r="I41" s="112" t="s">
-        <v>33</v>
-      </c>
-      <c r="J41" s="113"/>
-      <c r="K41" s="113"/>
-      <c r="L41" s="113"/>
-      <c r="M41" s="113"/>
-      <c r="N41" s="114"/>
-      <c r="O41" s="181" t="s">
-        <v>62</v>
-      </c>
-      <c r="P41" s="182"/>
-      <c r="Q41" s="183"/>
-      <c r="R41" s="130" t="s">
-        <v>34</v>
-      </c>
-      <c r="S41" s="131"/>
-      <c r="T41" s="131"/>
-      <c r="U41" s="132"/>
-      <c r="V41" s="181" t="s">
-        <v>35</v>
-      </c>
-      <c r="W41" s="182"/>
-      <c r="X41" s="183"/>
-      <c r="Y41" s="181" t="s">
-        <v>36</v>
-      </c>
-      <c r="Z41" s="182"/>
-      <c r="AA41" s="183"/>
-      <c r="AB41" s="112" t="s">
-        <v>37</v>
-      </c>
-      <c r="AC41" s="113"/>
-      <c r="AD41" s="113"/>
-      <c r="AE41" s="113"/>
-      <c r="AF41" s="114"/>
-      <c r="AG41" s="112" t="s">
-        <v>63</v>
-      </c>
-      <c r="AH41" s="114"/>
-      <c r="AI41" s="112" t="s">
-        <v>44</v>
-      </c>
-      <c r="AJ41" s="114"/>
-      <c r="AK41" s="112" t="s">
-        <v>45</v>
-      </c>
-      <c r="AL41" s="113"/>
-      <c r="AM41" s="114"/>
-      <c r="AN41" s="112" t="s">
-        <v>38</v>
-      </c>
-      <c r="AO41" s="113"/>
-      <c r="AP41" s="113"/>
-      <c r="AQ41" s="113"/>
-      <c r="AR41" s="113"/>
-      <c r="AS41" s="113"/>
-      <c r="AT41" s="113"/>
-      <c r="AU41" s="114"/>
-      <c r="AV41" s="112" t="s">
-        <v>39</v>
-      </c>
-      <c r="AW41" s="113"/>
-      <c r="AX41" s="113"/>
-      <c r="AY41" s="113"/>
-      <c r="AZ41" s="113"/>
-      <c r="BA41" s="113"/>
-      <c r="BB41" s="113"/>
-      <c r="BC41" s="113"/>
-      <c r="BD41" s="113"/>
-      <c r="BE41" s="113"/>
-      <c r="BF41" s="113"/>
-      <c r="BG41" s="114"/>
-      <c r="BH41" s="108" t="s">
-        <v>40</v>
-      </c>
-      <c r="BI41" s="109"/>
-      <c r="BJ41" s="109"/>
-      <c r="BK41" s="109"/>
-      <c r="BL41" s="108" t="s">
-        <v>65</v>
-      </c>
-      <c r="BM41" s="109"/>
-      <c r="BN41" s="109"/>
-      <c r="BO41" s="112" t="s">
-        <v>41</v>
-      </c>
-      <c r="BP41" s="113"/>
-      <c r="BQ41" s="113"/>
-      <c r="BR41" s="113"/>
-      <c r="BS41" s="113"/>
-      <c r="BT41" s="113"/>
-      <c r="BU41" s="113"/>
-      <c r="BV41" s="113"/>
-      <c r="BW41" s="113"/>
-      <c r="BX41" s="113"/>
-      <c r="BY41" s="113"/>
-      <c r="BZ41" s="113"/>
-      <c r="CA41" s="113"/>
-      <c r="CB41" s="113"/>
-      <c r="CC41" s="113"/>
-      <c r="CD41" s="113"/>
-      <c r="CE41" s="113"/>
-      <c r="CF41" s="113"/>
-      <c r="CG41" s="113"/>
-      <c r="CH41" s="113"/>
-      <c r="CI41" s="114"/>
+    <row r="45" spans="1:90" s="29" customFormat="1">
+      <c r="A45" s="67"/>
+      <c r="B45" s="68"/>
+      <c r="C45" s="68"/>
+      <c r="D45" s="68"/>
+      <c r="E45" s="68"/>
+      <c r="F45" s="68"/>
+      <c r="G45" s="68"/>
+      <c r="H45" s="68"/>
+      <c r="I45" s="68"/>
+      <c r="J45" s="68"/>
+      <c r="K45" s="68"/>
+      <c r="L45" s="68"/>
+      <c r="M45" s="68"/>
+      <c r="N45" s="68"/>
+      <c r="O45" s="68"/>
+      <c r="P45" s="68"/>
+      <c r="Q45" s="68"/>
+      <c r="R45" s="68"/>
+      <c r="S45" s="68"/>
+      <c r="T45" s="68"/>
+      <c r="U45" s="68"/>
+      <c r="V45" s="68"/>
+      <c r="W45" s="68"/>
+      <c r="X45" s="68"/>
+      <c r="Y45" s="68"/>
+      <c r="Z45" s="68"/>
+      <c r="AA45" s="68"/>
+      <c r="AB45" s="68"/>
+      <c r="AC45" s="68"/>
+      <c r="AD45" s="68"/>
+      <c r="AE45" s="68"/>
+      <c r="AF45" s="68"/>
+      <c r="AG45" s="68"/>
+      <c r="AH45" s="68"/>
+      <c r="AI45" s="68"/>
+      <c r="AJ45" s="68"/>
+      <c r="AK45" s="68"/>
+      <c r="AL45" s="68"/>
+      <c r="AM45" s="68"/>
+      <c r="AN45" s="68"/>
+      <c r="AO45" s="68"/>
+      <c r="AP45" s="68"/>
+      <c r="AQ45" s="68"/>
+      <c r="AR45" s="68"/>
+      <c r="AS45" s="68"/>
+      <c r="AT45" s="68"/>
+      <c r="AU45" s="68"/>
+      <c r="AV45" s="68"/>
+      <c r="AW45" s="68"/>
+      <c r="AX45" s="68"/>
+      <c r="AY45" s="68"/>
+      <c r="AZ45" s="68"/>
+      <c r="BA45" s="68"/>
+      <c r="BB45" s="68"/>
+      <c r="BC45" s="68"/>
+      <c r="BD45" s="68"/>
+      <c r="BE45" s="68"/>
+      <c r="BF45" s="68"/>
+      <c r="BG45" s="68"/>
+      <c r="BH45" s="68"/>
+      <c r="BI45" s="68"/>
+      <c r="BJ45" s="68"/>
+      <c r="BK45" s="68"/>
+      <c r="BL45" s="68"/>
+      <c r="BM45" s="68"/>
+      <c r="BN45" s="68"/>
+      <c r="BO45" s="68"/>
+      <c r="BP45" s="68"/>
+      <c r="BQ45" s="68"/>
+      <c r="BR45" s="68"/>
+      <c r="BS45" s="68"/>
+      <c r="BT45" s="68"/>
+      <c r="BU45" s="68"/>
+      <c r="BV45" s="68"/>
+      <c r="BW45" s="68"/>
+      <c r="BX45" s="68"/>
+      <c r="BY45" s="68"/>
+      <c r="BZ45" s="68"/>
+      <c r="CA45" s="68"/>
+      <c r="CB45" s="68"/>
+      <c r="CC45" s="68"/>
+      <c r="CD45" s="68"/>
+      <c r="CE45" s="68"/>
+      <c r="CF45" s="68"/>
+      <c r="CG45" s="68"/>
+      <c r="CH45" s="68"/>
+      <c r="CI45" s="68"/>
+      <c r="CJ45" s="68"/>
+      <c r="CK45" s="68"/>
+      <c r="CL45" s="69"/>
     </row>
-    <row r="42" spans="1:90" s="19" customFormat="1" ht="83.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A42" s="115"/>
-      <c r="B42" s="117"/>
-      <c r="C42" s="115"/>
-      <c r="D42" s="116"/>
-      <c r="E42" s="116"/>
-      <c r="F42" s="116"/>
-      <c r="G42" s="116"/>
-      <c r="H42" s="117"/>
-      <c r="I42" s="115"/>
-      <c r="J42" s="116"/>
-      <c r="K42" s="116"/>
-      <c r="L42" s="116"/>
-      <c r="M42" s="116"/>
-      <c r="N42" s="117"/>
-      <c r="O42" s="184"/>
-      <c r="P42" s="185"/>
-      <c r="Q42" s="186"/>
-      <c r="R42" s="17" t="s">
-        <v>54</v>
-      </c>
-      <c r="S42" s="17" t="s">
-        <v>66</v>
-      </c>
-      <c r="T42" s="17" t="s">
-        <v>55</v>
-      </c>
-      <c r="U42" s="17" t="s">
-        <v>56</v>
-      </c>
-      <c r="V42" s="184"/>
-      <c r="W42" s="185"/>
-      <c r="X42" s="186"/>
-      <c r="Y42" s="184"/>
-      <c r="Z42" s="185"/>
-      <c r="AA42" s="186"/>
-      <c r="AB42" s="115"/>
-      <c r="AC42" s="116"/>
-      <c r="AD42" s="116"/>
-      <c r="AE42" s="116"/>
-      <c r="AF42" s="117"/>
-      <c r="AG42" s="115"/>
-      <c r="AH42" s="117"/>
-      <c r="AI42" s="115"/>
-      <c r="AJ42" s="117"/>
-      <c r="AK42" s="115"/>
-      <c r="AL42" s="116"/>
-      <c r="AM42" s="117"/>
-      <c r="AN42" s="115"/>
-      <c r="AO42" s="116"/>
-      <c r="AP42" s="116"/>
-      <c r="AQ42" s="116"/>
-      <c r="AR42" s="116"/>
-      <c r="AS42" s="116"/>
-      <c r="AT42" s="116"/>
-      <c r="AU42" s="117"/>
-      <c r="AV42" s="115"/>
-      <c r="AW42" s="116"/>
-      <c r="AX42" s="116"/>
-      <c r="AY42" s="116"/>
-      <c r="AZ42" s="116"/>
-      <c r="BA42" s="116"/>
-      <c r="BB42" s="116"/>
-      <c r="BC42" s="116"/>
-      <c r="BD42" s="116"/>
-      <c r="BE42" s="116"/>
-      <c r="BF42" s="116"/>
-      <c r="BG42" s="117"/>
-      <c r="BH42" s="110"/>
-      <c r="BI42" s="111"/>
-      <c r="BJ42" s="111"/>
-      <c r="BK42" s="111"/>
-      <c r="BL42" s="110"/>
-      <c r="BM42" s="111"/>
-      <c r="BN42" s="111"/>
-      <c r="BO42" s="115"/>
-      <c r="BP42" s="116"/>
-      <c r="BQ42" s="116"/>
-      <c r="BR42" s="116"/>
-      <c r="BS42" s="116"/>
-      <c r="BT42" s="116"/>
-      <c r="BU42" s="116"/>
-      <c r="BV42" s="116"/>
-      <c r="BW42" s="116"/>
-      <c r="BX42" s="116"/>
-      <c r="BY42" s="116"/>
-      <c r="BZ42" s="116"/>
-      <c r="CA42" s="116"/>
-      <c r="CB42" s="116"/>
-      <c r="CC42" s="116"/>
-      <c r="CD42" s="116"/>
-      <c r="CE42" s="116"/>
-      <c r="CF42" s="116"/>
-      <c r="CG42" s="116"/>
-      <c r="CH42" s="116"/>
-      <c r="CI42" s="117"/>
+    <row r="46" spans="1:90" s="29" customFormat="1">
+      <c r="A46" s="67"/>
+      <c r="B46" s="68"/>
+      <c r="C46" s="68"/>
+      <c r="D46" s="68"/>
+      <c r="E46" s="68"/>
+      <c r="F46" s="68"/>
+      <c r="G46" s="68"/>
+      <c r="H46" s="68"/>
+      <c r="I46" s="68"/>
+      <c r="J46" s="68"/>
+      <c r="K46" s="68"/>
+      <c r="L46" s="68"/>
+      <c r="M46" s="68"/>
+      <c r="N46" s="68"/>
+      <c r="O46" s="68"/>
+      <c r="P46" s="68"/>
+      <c r="Q46" s="68"/>
+      <c r="R46" s="68"/>
+      <c r="S46" s="68"/>
+      <c r="T46" s="68"/>
+      <c r="U46" s="68"/>
+      <c r="V46" s="68"/>
+      <c r="W46" s="68"/>
+      <c r="X46" s="68"/>
+      <c r="Y46" s="68"/>
+      <c r="Z46" s="68"/>
+      <c r="AA46" s="68"/>
+      <c r="AB46" s="68"/>
+      <c r="AC46" s="68"/>
+      <c r="AD46" s="68"/>
+      <c r="AE46" s="68"/>
+      <c r="AF46" s="68"/>
+      <c r="AG46" s="68"/>
+      <c r="AH46" s="68"/>
+      <c r="AI46" s="68"/>
+      <c r="AJ46" s="68"/>
+      <c r="AK46" s="68"/>
+      <c r="AL46" s="68"/>
+      <c r="AM46" s="68"/>
+      <c r="AN46" s="68"/>
+      <c r="AO46" s="68"/>
+      <c r="AP46" s="68"/>
+      <c r="AQ46" s="68"/>
+      <c r="AR46" s="68"/>
+      <c r="AS46" s="68"/>
+      <c r="AT46" s="68"/>
+      <c r="AU46" s="68"/>
+      <c r="AV46" s="68"/>
+      <c r="AW46" s="68"/>
+      <c r="AX46" s="68"/>
+      <c r="AY46" s="68"/>
+      <c r="AZ46" s="68"/>
+      <c r="BA46" s="68"/>
+      <c r="BB46" s="68"/>
+      <c r="BC46" s="68"/>
+      <c r="BD46" s="68"/>
+      <c r="BE46" s="68"/>
+      <c r="BF46" s="68"/>
+      <c r="BG46" s="68"/>
+      <c r="BH46" s="68"/>
+      <c r="BI46" s="68"/>
+      <c r="BJ46" s="68"/>
+      <c r="BK46" s="68"/>
+      <c r="BL46" s="68"/>
+      <c r="BM46" s="68"/>
+      <c r="BN46" s="68"/>
+      <c r="BO46" s="68"/>
+      <c r="BP46" s="68"/>
+      <c r="BQ46" s="68"/>
+      <c r="BR46" s="68"/>
+      <c r="BS46" s="68"/>
+      <c r="BT46" s="68"/>
+      <c r="BU46" s="68"/>
+      <c r="BV46" s="68"/>
+      <c r="BW46" s="68"/>
+      <c r="BX46" s="68"/>
+      <c r="BY46" s="68"/>
+      <c r="BZ46" s="68"/>
+      <c r="CA46" s="68"/>
+      <c r="CB46" s="68"/>
+      <c r="CC46" s="68"/>
+      <c r="CD46" s="68"/>
+      <c r="CE46" s="68"/>
+      <c r="CF46" s="68"/>
+      <c r="CG46" s="68"/>
+      <c r="CH46" s="68"/>
+      <c r="CI46" s="68"/>
+      <c r="CJ46" s="68"/>
+      <c r="CK46" s="68"/>
+      <c r="CL46" s="69"/>
     </row>
-    <row r="43" spans="1:90" s="19" customFormat="1" x14ac:dyDescent="0.15">
-      <c r="A43" s="96" t="s">
-        <v>59</v>
-      </c>
-      <c r="B43" s="98"/>
-      <c r="C43" s="96" t="s">
-        <v>67</v>
-      </c>
-      <c r="D43" s="97"/>
-      <c r="E43" s="97"/>
-      <c r="F43" s="97"/>
-      <c r="G43" s="97"/>
-      <c r="H43" s="98"/>
-      <c r="I43" s="87" t="s">
-        <v>59</v>
-      </c>
-      <c r="J43" s="190"/>
-      <c r="K43" s="190"/>
-      <c r="L43" s="190"/>
-      <c r="M43" s="190"/>
-      <c r="N43" s="88"/>
-      <c r="O43" s="89" t="s">
-        <v>51</v>
-      </c>
-      <c r="P43" s="90"/>
-      <c r="Q43" s="91"/>
-      <c r="R43" s="14" t="s">
-        <v>67</v>
-      </c>
-      <c r="S43" s="14" t="s">
-        <v>58</v>
-      </c>
-      <c r="T43" s="14" t="s">
-        <v>59</v>
-      </c>
-      <c r="U43" s="14" t="s">
-        <v>67</v>
-      </c>
-      <c r="V43" s="191" t="s">
-        <v>58</v>
-      </c>
-      <c r="W43" s="192"/>
-      <c r="X43" s="193"/>
-      <c r="Y43" s="191" t="s">
-        <v>59</v>
-      </c>
-      <c r="Z43" s="192"/>
-      <c r="AA43" s="193"/>
-      <c r="AB43" s="96" t="s">
-        <v>51</v>
-      </c>
-      <c r="AC43" s="97"/>
-      <c r="AD43" s="97"/>
-      <c r="AE43" s="97"/>
-      <c r="AF43" s="98"/>
-      <c r="AG43" s="96" t="s">
-        <v>51</v>
-      </c>
-      <c r="AH43" s="98"/>
-      <c r="AI43" s="96" t="s">
-        <v>51</v>
-      </c>
-      <c r="AJ43" s="98"/>
-      <c r="AK43" s="89" t="s">
-        <v>51</v>
-      </c>
-      <c r="AL43" s="90"/>
-      <c r="AM43" s="91"/>
-      <c r="AN43" s="96" t="s">
-        <v>51</v>
-      </c>
-      <c r="AO43" s="97"/>
-      <c r="AP43" s="97"/>
-      <c r="AQ43" s="97"/>
-      <c r="AR43" s="97"/>
-      <c r="AS43" s="97"/>
-      <c r="AT43" s="97"/>
-      <c r="AU43" s="98"/>
-      <c r="AV43" s="99" t="s">
-        <v>58</v>
-      </c>
-      <c r="AW43" s="100"/>
-      <c r="AX43" s="100"/>
-      <c r="AY43" s="100"/>
-      <c r="AZ43" s="100"/>
-      <c r="BA43" s="100"/>
-      <c r="BB43" s="100"/>
-      <c r="BC43" s="100"/>
-      <c r="BD43" s="100"/>
-      <c r="BE43" s="100"/>
-      <c r="BF43" s="100"/>
-      <c r="BG43" s="101"/>
-      <c r="BH43" s="102" t="s">
-        <v>67</v>
-      </c>
-      <c r="BI43" s="103"/>
-      <c r="BJ43" s="103"/>
-      <c r="BK43" s="104"/>
-      <c r="BL43" s="102" t="s">
-        <v>59</v>
-      </c>
-      <c r="BM43" s="103"/>
-      <c r="BN43" s="104"/>
-      <c r="BO43" s="102" t="s">
-        <v>58</v>
-      </c>
-      <c r="BP43" s="103"/>
-      <c r="BQ43" s="103"/>
-      <c r="BR43" s="103"/>
-      <c r="BS43" s="103"/>
-      <c r="BT43" s="103"/>
-      <c r="BU43" s="103"/>
-      <c r="BV43" s="103"/>
-      <c r="BW43" s="103"/>
-      <c r="BX43" s="103"/>
-      <c r="BY43" s="103"/>
-      <c r="BZ43" s="103"/>
-      <c r="CA43" s="103"/>
-      <c r="CB43" s="103"/>
-      <c r="CC43" s="103"/>
-      <c r="CD43" s="103"/>
-      <c r="CE43" s="103"/>
-      <c r="CF43" s="103"/>
-      <c r="CG43" s="103"/>
-      <c r="CH43" s="103"/>
-      <c r="CI43" s="104"/>
-    </row>
-    <row r="44" spans="1:90" s="29" customFormat="1" x14ac:dyDescent="0.15">
-      <c r="A44" s="40"/>
-      <c r="B44" s="40"/>
-      <c r="C44" s="41"/>
-      <c r="D44" s="41"/>
-      <c r="E44" s="41"/>
-      <c r="F44" s="41"/>
-      <c r="G44" s="41"/>
-      <c r="H44" s="41"/>
-      <c r="I44" s="41"/>
-      <c r="J44" s="41"/>
-      <c r="K44" s="41"/>
-      <c r="L44" s="41"/>
-      <c r="M44" s="41"/>
-      <c r="N44" s="41"/>
-      <c r="O44" s="41"/>
-      <c r="P44" s="41"/>
-      <c r="Q44" s="42"/>
-      <c r="R44" s="42"/>
-      <c r="S44" s="42"/>
-      <c r="T44" s="42"/>
-      <c r="U44" s="42"/>
-      <c r="V44" s="42"/>
-      <c r="W44" s="42"/>
-      <c r="X44" s="42"/>
-      <c r="Y44" s="42"/>
-      <c r="Z44" s="42"/>
-      <c r="AA44" s="42"/>
-      <c r="AB44" s="42"/>
-      <c r="AC44" s="42"/>
-      <c r="AD44" s="42"/>
-      <c r="AE44" s="42"/>
-      <c r="AF44" s="42"/>
-      <c r="AG44" s="42"/>
-      <c r="AH44" s="42"/>
-      <c r="AI44" s="42"/>
-      <c r="AJ44" s="42"/>
-      <c r="AK44" s="41"/>
-      <c r="AL44" s="42"/>
-      <c r="AM44" s="41"/>
-      <c r="AN44" s="41"/>
-      <c r="AO44" s="41"/>
-      <c r="AP44" s="41"/>
-      <c r="AQ44" s="41"/>
-      <c r="AR44" s="42"/>
-      <c r="AS44" s="42"/>
-      <c r="AT44" s="42"/>
-      <c r="AU44" s="42"/>
-      <c r="AV44" s="43"/>
-      <c r="AW44" s="42"/>
-      <c r="AX44" s="41"/>
-      <c r="AY44" s="41"/>
-      <c r="AZ44" s="41"/>
-      <c r="BA44" s="41"/>
-      <c r="BB44" s="41"/>
-      <c r="BC44" s="41"/>
-      <c r="BD44" s="41"/>
-      <c r="BE44" s="41"/>
-      <c r="BF44" s="41"/>
-      <c r="BG44" s="41"/>
-      <c r="BH44" s="41"/>
-      <c r="BI44" s="41"/>
-      <c r="BJ44" s="41"/>
-      <c r="BK44" s="41"/>
-      <c r="BL44" s="41"/>
-      <c r="BM44" s="41"/>
-      <c r="BN44" s="41"/>
-      <c r="BO44" s="41"/>
-      <c r="BP44" s="41"/>
-      <c r="BQ44" s="41"/>
-      <c r="BR44" s="41"/>
-      <c r="BS44" s="41"/>
-      <c r="BT44" s="41"/>
-      <c r="BU44" s="41"/>
-      <c r="BV44" s="41"/>
-      <c r="BW44" s="41"/>
-      <c r="BX44" s="41"/>
-      <c r="BY44" s="41"/>
-      <c r="BZ44" s="41"/>
-      <c r="CA44" s="41"/>
-      <c r="CB44" s="41"/>
-      <c r="CC44" s="41"/>
-      <c r="CD44" s="41"/>
-      <c r="CE44" s="44"/>
-      <c r="CF44" s="44"/>
-      <c r="CG44" s="44"/>
-      <c r="CH44" s="44"/>
-      <c r="CI44" s="44"/>
-      <c r="CJ44" s="44"/>
-      <c r="CK44" s="44"/>
-      <c r="CL44" s="44"/>
-    </row>
-    <row r="45" spans="1:90" s="29" customFormat="1" x14ac:dyDescent="0.15">
-      <c r="A45" s="187" t="s">
-        <v>48</v>
-      </c>
-      <c r="B45" s="188"/>
-      <c r="C45" s="188"/>
-      <c r="D45" s="188"/>
-      <c r="E45" s="188"/>
-      <c r="F45" s="188"/>
-      <c r="G45" s="188"/>
-      <c r="H45" s="189"/>
-      <c r="I45" s="45"/>
-      <c r="J45" s="45"/>
-      <c r="K45" s="45"/>
-      <c r="L45" s="45"/>
-      <c r="M45" s="45"/>
-      <c r="N45" s="45"/>
-      <c r="O45" s="45"/>
-      <c r="P45" s="45"/>
-      <c r="Q45" s="46"/>
-      <c r="R45" s="46"/>
-      <c r="S45" s="46"/>
-      <c r="T45" s="46"/>
-      <c r="U45" s="46"/>
-      <c r="V45" s="46"/>
-      <c r="W45" s="46"/>
-      <c r="X45" s="46"/>
-      <c r="Y45" s="46"/>
-      <c r="Z45" s="46"/>
-      <c r="AA45" s="46"/>
-      <c r="AB45" s="46"/>
-      <c r="AC45" s="46"/>
-      <c r="AD45" s="46"/>
-      <c r="AE45" s="46"/>
-      <c r="AF45" s="46"/>
-      <c r="AG45" s="46"/>
-      <c r="AH45" s="46"/>
-      <c r="AI45" s="46"/>
-      <c r="AJ45" s="46"/>
-      <c r="AK45" s="45"/>
-      <c r="AL45" s="46"/>
-      <c r="AM45" s="45"/>
-      <c r="AN45" s="45"/>
-      <c r="AO45" s="45"/>
-      <c r="AP45" s="45"/>
-      <c r="AQ45" s="45"/>
-      <c r="AR45" s="45"/>
-      <c r="AS45" s="45"/>
-      <c r="AT45" s="45"/>
-      <c r="AU45" s="45"/>
-      <c r="AV45" s="47"/>
-      <c r="AW45" s="45"/>
-      <c r="AX45" s="45"/>
-      <c r="AY45" s="45"/>
-      <c r="AZ45" s="45"/>
-      <c r="BA45" s="45"/>
-      <c r="BB45" s="45"/>
-      <c r="BC45" s="45"/>
-      <c r="BD45" s="45"/>
-      <c r="BE45" s="45"/>
-      <c r="BF45" s="45"/>
-      <c r="BG45" s="48"/>
-      <c r="BH45" s="48"/>
-      <c r="BI45" s="48"/>
-      <c r="BJ45" s="45"/>
-      <c r="BK45" s="45"/>
-      <c r="BL45" s="45"/>
-      <c r="BM45" s="45"/>
-      <c r="BN45" s="45"/>
-      <c r="BO45" s="45"/>
-      <c r="BP45" s="45"/>
-      <c r="BQ45" s="45"/>
-      <c r="BR45" s="45"/>
-      <c r="BS45" s="45"/>
-      <c r="BT45" s="45"/>
-      <c r="BU45" s="45"/>
-      <c r="BV45" s="45"/>
-      <c r="BW45" s="45"/>
-      <c r="BX45" s="45"/>
-      <c r="BY45" s="45"/>
-      <c r="BZ45" s="45"/>
-      <c r="CA45" s="45"/>
-      <c r="CB45" s="45"/>
-      <c r="CC45" s="45"/>
-      <c r="CD45" s="45"/>
-      <c r="CE45" s="45"/>
-      <c r="CF45" s="45"/>
-      <c r="CG45" s="45"/>
-      <c r="CH45" s="45"/>
-      <c r="CI45" s="45"/>
-      <c r="CJ45" s="45"/>
-      <c r="CK45" s="45"/>
-      <c r="CL45" s="45"/>
-    </row>
-    <row r="46" spans="1:90" s="29" customFormat="1" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A46" s="64"/>
-      <c r="B46" s="65"/>
-      <c r="C46" s="65"/>
-      <c r="D46" s="65"/>
-      <c r="E46" s="65"/>
-      <c r="F46" s="65"/>
-      <c r="G46" s="65"/>
-      <c r="H46" s="65"/>
-      <c r="I46" s="65"/>
-      <c r="J46" s="65"/>
-      <c r="K46" s="65"/>
-      <c r="L46" s="65"/>
-      <c r="M46" s="65"/>
-      <c r="N46" s="65"/>
-      <c r="O46" s="65"/>
-      <c r="P46" s="65"/>
-      <c r="Q46" s="65"/>
-      <c r="R46" s="65"/>
-      <c r="S46" s="65"/>
-      <c r="T46" s="65"/>
-      <c r="U46" s="65"/>
-      <c r="V46" s="65"/>
-      <c r="W46" s="65"/>
-      <c r="X46" s="65"/>
-      <c r="Y46" s="65"/>
-      <c r="Z46" s="65"/>
-      <c r="AA46" s="65"/>
-      <c r="AB46" s="65"/>
-      <c r="AC46" s="65"/>
-      <c r="AD46" s="65"/>
-      <c r="AE46" s="65"/>
-      <c r="AF46" s="65"/>
-      <c r="AG46" s="65"/>
-      <c r="AH46" s="65"/>
-      <c r="AI46" s="65"/>
-      <c r="AJ46" s="65"/>
-      <c r="AK46" s="65"/>
-      <c r="AL46" s="65"/>
-      <c r="AM46" s="65"/>
-      <c r="AN46" s="65"/>
-      <c r="AO46" s="65"/>
-      <c r="AP46" s="65"/>
-      <c r="AQ46" s="65"/>
-      <c r="AR46" s="65"/>
-      <c r="AS46" s="65"/>
-      <c r="AT46" s="65"/>
-      <c r="AU46" s="65"/>
-      <c r="AV46" s="65"/>
-      <c r="AW46" s="65"/>
-      <c r="AX46" s="65"/>
-      <c r="AY46" s="65"/>
-      <c r="AZ46" s="65"/>
-      <c r="BA46" s="65"/>
-      <c r="BB46" s="65"/>
-      <c r="BC46" s="65"/>
-      <c r="BD46" s="65"/>
-      <c r="BE46" s="65"/>
-      <c r="BF46" s="65"/>
-      <c r="BG46" s="65"/>
-      <c r="BH46" s="65"/>
-      <c r="BI46" s="65"/>
-      <c r="BJ46" s="65"/>
-      <c r="BK46" s="65"/>
-      <c r="BL46" s="65"/>
-      <c r="BM46" s="65"/>
-      <c r="BN46" s="65"/>
-      <c r="BO46" s="65"/>
-      <c r="BP46" s="65"/>
-      <c r="BQ46" s="65"/>
-      <c r="BR46" s="65"/>
-      <c r="BS46" s="65"/>
-      <c r="BT46" s="65"/>
-      <c r="BU46" s="65"/>
-      <c r="BV46" s="65"/>
-      <c r="BW46" s="65"/>
-      <c r="BX46" s="65"/>
-      <c r="BY46" s="65"/>
-      <c r="BZ46" s="65"/>
-      <c r="CA46" s="65"/>
-      <c r="CB46" s="65"/>
-      <c r="CC46" s="65"/>
-      <c r="CD46" s="65"/>
-      <c r="CE46" s="65"/>
-      <c r="CF46" s="65"/>
-      <c r="CG46" s="65"/>
-      <c r="CH46" s="65"/>
-      <c r="CI46" s="65"/>
-      <c r="CJ46" s="65"/>
-      <c r="CK46" s="65"/>
-      <c r="CL46" s="66"/>
-    </row>
-    <row r="47" spans="1:90" s="29" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="47" spans="1:90" s="29" customFormat="1">
       <c r="A47" s="67"/>
       <c r="B47" s="68"/>
       <c r="C47" s="68"/>
@@ -9380,7 +9241,7 @@
       <c r="CK47" s="68"/>
       <c r="CL47" s="69"/>
     </row>
-    <row r="48" spans="1:90" s="29" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="48" spans="1:90" s="29" customFormat="1">
       <c r="A48" s="67"/>
       <c r="B48" s="68"/>
       <c r="C48" s="68"/>
@@ -9472,7 +9333,7 @@
       <c r="CK48" s="68"/>
       <c r="CL48" s="69"/>
     </row>
-    <row r="49" spans="1:90" s="29" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="49" spans="1:90" s="29" customFormat="1">
       <c r="A49" s="67"/>
       <c r="B49" s="68"/>
       <c r="C49" s="68"/>
@@ -9564,7 +9425,7 @@
       <c r="CK49" s="68"/>
       <c r="CL49" s="69"/>
     </row>
-    <row r="50" spans="1:90" s="29" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="50" spans="1:90" s="29" customFormat="1">
       <c r="A50" s="67"/>
       <c r="B50" s="68"/>
       <c r="C50" s="68"/>
@@ -9656,722 +9517,446 @@
       <c r="CK50" s="68"/>
       <c r="CL50" s="69"/>
     </row>
-    <row r="51" spans="1:90" s="29" customFormat="1" x14ac:dyDescent="0.15">
-      <c r="A51" s="67"/>
-      <c r="B51" s="68"/>
-      <c r="C51" s="68"/>
-      <c r="D51" s="68"/>
-      <c r="E51" s="68"/>
-      <c r="F51" s="68"/>
-      <c r="G51" s="68"/>
-      <c r="H51" s="68"/>
-      <c r="I51" s="68"/>
-      <c r="J51" s="68"/>
-      <c r="K51" s="68"/>
-      <c r="L51" s="68"/>
-      <c r="M51" s="68"/>
-      <c r="N51" s="68"/>
-      <c r="O51" s="68"/>
-      <c r="P51" s="68"/>
-      <c r="Q51" s="68"/>
-      <c r="R51" s="68"/>
-      <c r="S51" s="68"/>
-      <c r="T51" s="68"/>
-      <c r="U51" s="68"/>
-      <c r="V51" s="68"/>
-      <c r="W51" s="68"/>
-      <c r="X51" s="68"/>
-      <c r="Y51" s="68"/>
-      <c r="Z51" s="68"/>
-      <c r="AA51" s="68"/>
-      <c r="AB51" s="68"/>
-      <c r="AC51" s="68"/>
-      <c r="AD51" s="68"/>
-      <c r="AE51" s="68"/>
-      <c r="AF51" s="68"/>
-      <c r="AG51" s="68"/>
-      <c r="AH51" s="68"/>
-      <c r="AI51" s="68"/>
-      <c r="AJ51" s="68"/>
-      <c r="AK51" s="68"/>
-      <c r="AL51" s="68"/>
-      <c r="AM51" s="68"/>
-      <c r="AN51" s="68"/>
-      <c r="AO51" s="68"/>
-      <c r="AP51" s="68"/>
-      <c r="AQ51" s="68"/>
-      <c r="AR51" s="68"/>
-      <c r="AS51" s="68"/>
-      <c r="AT51" s="68"/>
-      <c r="AU51" s="68"/>
-      <c r="AV51" s="68"/>
-      <c r="AW51" s="68"/>
-      <c r="AX51" s="68"/>
-      <c r="AY51" s="68"/>
-      <c r="AZ51" s="68"/>
-      <c r="BA51" s="68"/>
-      <c r="BB51" s="68"/>
-      <c r="BC51" s="68"/>
-      <c r="BD51" s="68"/>
-      <c r="BE51" s="68"/>
-      <c r="BF51" s="68"/>
-      <c r="BG51" s="68"/>
-      <c r="BH51" s="68"/>
-      <c r="BI51" s="68"/>
-      <c r="BJ51" s="68"/>
-      <c r="BK51" s="68"/>
-      <c r="BL51" s="68"/>
-      <c r="BM51" s="68"/>
-      <c r="BN51" s="68"/>
-      <c r="BO51" s="68"/>
-      <c r="BP51" s="68"/>
-      <c r="BQ51" s="68"/>
-      <c r="BR51" s="68"/>
-      <c r="BS51" s="68"/>
-      <c r="BT51" s="68"/>
-      <c r="BU51" s="68"/>
-      <c r="BV51" s="68"/>
-      <c r="BW51" s="68"/>
-      <c r="BX51" s="68"/>
-      <c r="BY51" s="68"/>
-      <c r="BZ51" s="68"/>
-      <c r="CA51" s="68"/>
-      <c r="CB51" s="68"/>
-      <c r="CC51" s="68"/>
-      <c r="CD51" s="68"/>
-      <c r="CE51" s="68"/>
-      <c r="CF51" s="68"/>
-      <c r="CG51" s="68"/>
-      <c r="CH51" s="68"/>
-      <c r="CI51" s="68"/>
-      <c r="CJ51" s="68"/>
-      <c r="CK51" s="68"/>
-      <c r="CL51" s="69"/>
+    <row r="51" spans="1:90" s="29" customFormat="1">
+      <c r="A51" s="70"/>
+      <c r="B51" s="71"/>
+      <c r="C51" s="71"/>
+      <c r="D51" s="71"/>
+      <c r="E51" s="71"/>
+      <c r="F51" s="71"/>
+      <c r="G51" s="71"/>
+      <c r="H51" s="71"/>
+      <c r="I51" s="71"/>
+      <c r="J51" s="71"/>
+      <c r="K51" s="71"/>
+      <c r="L51" s="71"/>
+      <c r="M51" s="71"/>
+      <c r="N51" s="71"/>
+      <c r="O51" s="71"/>
+      <c r="P51" s="71"/>
+      <c r="Q51" s="71"/>
+      <c r="R51" s="71"/>
+      <c r="S51" s="71"/>
+      <c r="T51" s="71"/>
+      <c r="U51" s="71"/>
+      <c r="V51" s="71"/>
+      <c r="W51" s="71"/>
+      <c r="X51" s="71"/>
+      <c r="Y51" s="71"/>
+      <c r="Z51" s="71"/>
+      <c r="AA51" s="71"/>
+      <c r="AB51" s="71"/>
+      <c r="AC51" s="71"/>
+      <c r="AD51" s="71"/>
+      <c r="AE51" s="71"/>
+      <c r="AF51" s="71"/>
+      <c r="AG51" s="71"/>
+      <c r="AH51" s="71"/>
+      <c r="AI51" s="71"/>
+      <c r="AJ51" s="71"/>
+      <c r="AK51" s="71"/>
+      <c r="AL51" s="71"/>
+      <c r="AM51" s="71"/>
+      <c r="AN51" s="71"/>
+      <c r="AO51" s="71"/>
+      <c r="AP51" s="71"/>
+      <c r="AQ51" s="71"/>
+      <c r="AR51" s="71"/>
+      <c r="AS51" s="71"/>
+      <c r="AT51" s="71"/>
+      <c r="AU51" s="71"/>
+      <c r="AV51" s="71"/>
+      <c r="AW51" s="71"/>
+      <c r="AX51" s="71"/>
+      <c r="AY51" s="71"/>
+      <c r="AZ51" s="71"/>
+      <c r="BA51" s="71"/>
+      <c r="BB51" s="71"/>
+      <c r="BC51" s="71"/>
+      <c r="BD51" s="71"/>
+      <c r="BE51" s="71"/>
+      <c r="BF51" s="71"/>
+      <c r="BG51" s="71"/>
+      <c r="BH51" s="71"/>
+      <c r="BI51" s="71"/>
+      <c r="BJ51" s="71"/>
+      <c r="BK51" s="71"/>
+      <c r="BL51" s="71"/>
+      <c r="BM51" s="71"/>
+      <c r="BN51" s="71"/>
+      <c r="BO51" s="71"/>
+      <c r="BP51" s="71"/>
+      <c r="BQ51" s="71"/>
+      <c r="BR51" s="71"/>
+      <c r="BS51" s="71"/>
+      <c r="BT51" s="71"/>
+      <c r="BU51" s="71"/>
+      <c r="BV51" s="71"/>
+      <c r="BW51" s="71"/>
+      <c r="BX51" s="71"/>
+      <c r="BY51" s="71"/>
+      <c r="BZ51" s="71"/>
+      <c r="CA51" s="71"/>
+      <c r="CB51" s="71"/>
+      <c r="CC51" s="71"/>
+      <c r="CD51" s="71"/>
+      <c r="CE51" s="71"/>
+      <c r="CF51" s="71"/>
+      <c r="CG51" s="71"/>
+      <c r="CH51" s="71"/>
+      <c r="CI51" s="71"/>
+      <c r="CJ51" s="71"/>
+      <c r="CK51" s="71"/>
+      <c r="CL51" s="72"/>
     </row>
-    <row r="52" spans="1:90" s="29" customFormat="1" x14ac:dyDescent="0.15">
-      <c r="A52" s="67"/>
-      <c r="B52" s="68"/>
-      <c r="C52" s="68"/>
-      <c r="D52" s="68"/>
-      <c r="E52" s="68"/>
-      <c r="F52" s="68"/>
-      <c r="G52" s="68"/>
-      <c r="H52" s="68"/>
-      <c r="I52" s="68"/>
-      <c r="J52" s="68"/>
-      <c r="K52" s="68"/>
-      <c r="L52" s="68"/>
-      <c r="M52" s="68"/>
-      <c r="N52" s="68"/>
-      <c r="O52" s="68"/>
-      <c r="P52" s="68"/>
-      <c r="Q52" s="68"/>
-      <c r="R52" s="68"/>
-      <c r="S52" s="68"/>
-      <c r="T52" s="68"/>
-      <c r="U52" s="68"/>
-      <c r="V52" s="68"/>
-      <c r="W52" s="68"/>
-      <c r="X52" s="68"/>
-      <c r="Y52" s="68"/>
-      <c r="Z52" s="68"/>
-      <c r="AA52" s="68"/>
-      <c r="AB52" s="68"/>
-      <c r="AC52" s="68"/>
-      <c r="AD52" s="68"/>
-      <c r="AE52" s="68"/>
-      <c r="AF52" s="68"/>
-      <c r="AG52" s="68"/>
-      <c r="AH52" s="68"/>
-      <c r="AI52" s="68"/>
-      <c r="AJ52" s="68"/>
-      <c r="AK52" s="68"/>
-      <c r="AL52" s="68"/>
-      <c r="AM52" s="68"/>
-      <c r="AN52" s="68"/>
-      <c r="AO52" s="68"/>
-      <c r="AP52" s="68"/>
-      <c r="AQ52" s="68"/>
-      <c r="AR52" s="68"/>
-      <c r="AS52" s="68"/>
-      <c r="AT52" s="68"/>
-      <c r="AU52" s="68"/>
-      <c r="AV52" s="68"/>
-      <c r="AW52" s="68"/>
-      <c r="AX52" s="68"/>
-      <c r="AY52" s="68"/>
-      <c r="AZ52" s="68"/>
-      <c r="BA52" s="68"/>
-      <c r="BB52" s="68"/>
-      <c r="BC52" s="68"/>
-      <c r="BD52" s="68"/>
-      <c r="BE52" s="68"/>
-      <c r="BF52" s="68"/>
-      <c r="BG52" s="68"/>
-      <c r="BH52" s="68"/>
-      <c r="BI52" s="68"/>
-      <c r="BJ52" s="68"/>
-      <c r="BK52" s="68"/>
-      <c r="BL52" s="68"/>
-      <c r="BM52" s="68"/>
-      <c r="BN52" s="68"/>
-      <c r="BO52" s="68"/>
-      <c r="BP52" s="68"/>
-      <c r="BQ52" s="68"/>
-      <c r="BR52" s="68"/>
-      <c r="BS52" s="68"/>
-      <c r="BT52" s="68"/>
-      <c r="BU52" s="68"/>
-      <c r="BV52" s="68"/>
-      <c r="BW52" s="68"/>
-      <c r="BX52" s="68"/>
-      <c r="BY52" s="68"/>
-      <c r="BZ52" s="68"/>
-      <c r="CA52" s="68"/>
-      <c r="CB52" s="68"/>
-      <c r="CC52" s="68"/>
-      <c r="CD52" s="68"/>
-      <c r="CE52" s="68"/>
-      <c r="CF52" s="68"/>
-      <c r="CG52" s="68"/>
-      <c r="CH52" s="68"/>
-      <c r="CI52" s="68"/>
-      <c r="CJ52" s="68"/>
-      <c r="CK52" s="68"/>
-      <c r="CL52" s="69"/>
+    <row r="53" spans="1:90">
+      <c r="A53" s="161" t="s">
+        <v>5</v>
+      </c>
+      <c r="B53" s="162"/>
+      <c r="C53" s="162"/>
+      <c r="D53" s="162"/>
+      <c r="E53" s="162"/>
+      <c r="F53" s="162"/>
+      <c r="G53" s="163"/>
+      <c r="H53" s="49"/>
+      <c r="I53" s="50"/>
+      <c r="J53" s="50"/>
+      <c r="K53" s="50"/>
+      <c r="L53" s="50"/>
+      <c r="M53" s="50"/>
+      <c r="N53" s="50"/>
+      <c r="O53" s="50"/>
+      <c r="P53" s="50"/>
+      <c r="Q53" s="50"/>
+      <c r="R53" s="50"/>
+      <c r="S53" s="50"/>
+      <c r="T53" s="50"/>
+      <c r="U53" s="50"/>
+      <c r="V53" s="50"/>
+      <c r="W53" s="50"/>
+      <c r="X53" s="50"/>
+      <c r="Y53" s="50"/>
+      <c r="Z53" s="50"/>
+      <c r="AA53" s="50"/>
+      <c r="AB53" s="50"/>
+      <c r="AC53" s="50"/>
+      <c r="AD53" s="50"/>
+      <c r="AE53" s="50"/>
+      <c r="AF53" s="50"/>
+      <c r="AG53" s="50"/>
+      <c r="AH53" s="50"/>
+      <c r="AI53" s="50"/>
+      <c r="AJ53" s="50"/>
+      <c r="AK53" s="50"/>
+      <c r="AL53" s="50"/>
+      <c r="AM53" s="50"/>
+      <c r="AN53" s="50"/>
+      <c r="AO53" s="50"/>
+      <c r="AP53" s="50"/>
+      <c r="AQ53" s="50"/>
+      <c r="AR53" s="50"/>
+      <c r="AS53" s="50"/>
+      <c r="AT53" s="50"/>
+      <c r="AU53" s="50"/>
+      <c r="AV53" s="51"/>
+      <c r="AW53" s="50"/>
+      <c r="AX53" s="50"/>
+      <c r="AY53" s="50"/>
+      <c r="AZ53" s="50"/>
+      <c r="BA53" s="50"/>
+      <c r="BB53" s="50"/>
+      <c r="BC53" s="50"/>
+      <c r="BD53" s="50"/>
+      <c r="BE53" s="50"/>
+      <c r="BF53" s="50"/>
+      <c r="BG53" s="50"/>
+      <c r="BH53" s="50"/>
+      <c r="BI53" s="50"/>
+      <c r="BJ53" s="50"/>
     </row>
-    <row r="53" spans="1:90" s="29" customFormat="1" x14ac:dyDescent="0.15">
-      <c r="A53" s="67"/>
-      <c r="B53" s="68"/>
-      <c r="C53" s="68"/>
-      <c r="D53" s="68"/>
-      <c r="E53" s="68"/>
-      <c r="F53" s="68"/>
-      <c r="G53" s="68"/>
-      <c r="H53" s="68"/>
-      <c r="I53" s="68"/>
-      <c r="J53" s="68"/>
-      <c r="K53" s="68"/>
-      <c r="L53" s="68"/>
-      <c r="M53" s="68"/>
-      <c r="N53" s="68"/>
-      <c r="O53" s="68"/>
-      <c r="P53" s="68"/>
-      <c r="Q53" s="68"/>
-      <c r="R53" s="68"/>
-      <c r="S53" s="68"/>
-      <c r="T53" s="68"/>
-      <c r="U53" s="68"/>
-      <c r="V53" s="68"/>
-      <c r="W53" s="68"/>
-      <c r="X53" s="68"/>
-      <c r="Y53" s="68"/>
-      <c r="Z53" s="68"/>
-      <c r="AA53" s="68"/>
-      <c r="AB53" s="68"/>
-      <c r="AC53" s="68"/>
-      <c r="AD53" s="68"/>
-      <c r="AE53" s="68"/>
-      <c r="AF53" s="68"/>
-      <c r="AG53" s="68"/>
-      <c r="AH53" s="68"/>
-      <c r="AI53" s="68"/>
-      <c r="AJ53" s="68"/>
-      <c r="AK53" s="68"/>
-      <c r="AL53" s="68"/>
-      <c r="AM53" s="68"/>
-      <c r="AN53" s="68"/>
-      <c r="AO53" s="68"/>
-      <c r="AP53" s="68"/>
-      <c r="AQ53" s="68"/>
-      <c r="AR53" s="68"/>
-      <c r="AS53" s="68"/>
-      <c r="AT53" s="68"/>
-      <c r="AU53" s="68"/>
-      <c r="AV53" s="68"/>
-      <c r="AW53" s="68"/>
-      <c r="AX53" s="68"/>
-      <c r="AY53" s="68"/>
-      <c r="AZ53" s="68"/>
-      <c r="BA53" s="68"/>
-      <c r="BB53" s="68"/>
-      <c r="BC53" s="68"/>
-      <c r="BD53" s="68"/>
-      <c r="BE53" s="68"/>
-      <c r="BF53" s="68"/>
-      <c r="BG53" s="68"/>
-      <c r="BH53" s="68"/>
-      <c r="BI53" s="68"/>
-      <c r="BJ53" s="68"/>
-      <c r="BK53" s="68"/>
-      <c r="BL53" s="68"/>
-      <c r="BM53" s="68"/>
-      <c r="BN53" s="68"/>
-      <c r="BO53" s="68"/>
-      <c r="BP53" s="68"/>
-      <c r="BQ53" s="68"/>
-      <c r="BR53" s="68"/>
-      <c r="BS53" s="68"/>
-      <c r="BT53" s="68"/>
-      <c r="BU53" s="68"/>
-      <c r="BV53" s="68"/>
-      <c r="BW53" s="68"/>
-      <c r="BX53" s="68"/>
-      <c r="BY53" s="68"/>
-      <c r="BZ53" s="68"/>
-      <c r="CA53" s="68"/>
-      <c r="CB53" s="68"/>
-      <c r="CC53" s="68"/>
-      <c r="CD53" s="68"/>
-      <c r="CE53" s="68"/>
-      <c r="CF53" s="68"/>
-      <c r="CG53" s="68"/>
-      <c r="CH53" s="68"/>
-      <c r="CI53" s="68"/>
-      <c r="CJ53" s="68"/>
-      <c r="CK53" s="68"/>
-      <c r="CL53" s="69"/>
+    <row r="54" spans="1:90">
+      <c r="A54" s="75" t="s">
+        <v>131</v>
+      </c>
+      <c r="B54" s="76"/>
+      <c r="C54" s="77" t="s">
+        <v>132</v>
+      </c>
+      <c r="D54" s="53"/>
+      <c r="E54" s="53"/>
+      <c r="F54" s="53"/>
+      <c r="G54" s="53"/>
+      <c r="H54" s="53"/>
+      <c r="I54" s="52"/>
+      <c r="J54" s="52"/>
+      <c r="K54" s="52"/>
+      <c r="L54" s="52"/>
+      <c r="M54" s="52"/>
+      <c r="N54" s="52"/>
+      <c r="O54" s="52"/>
+      <c r="P54" s="52"/>
+      <c r="Q54" s="52"/>
+      <c r="R54" s="52"/>
+      <c r="S54" s="52"/>
+      <c r="T54" s="52"/>
+      <c r="U54" s="52"/>
+      <c r="V54" s="52"/>
+      <c r="W54" s="52"/>
+      <c r="X54" s="52"/>
+      <c r="Y54" s="52"/>
+      <c r="Z54" s="52"/>
+      <c r="AA54" s="52"/>
+      <c r="AB54" s="52"/>
+      <c r="AC54" s="52"/>
+      <c r="AD54" s="52"/>
+      <c r="AE54" s="52"/>
+      <c r="AF54" s="52"/>
+      <c r="AG54" s="52"/>
+      <c r="AH54" s="52"/>
+      <c r="AI54" s="52"/>
+      <c r="AJ54" s="52"/>
+      <c r="AK54" s="52"/>
+      <c r="AL54" s="52"/>
+      <c r="AM54" s="52"/>
+      <c r="AN54" s="52"/>
+      <c r="AO54" s="52"/>
+      <c r="AP54" s="52"/>
+      <c r="AQ54" s="52"/>
+      <c r="AR54" s="52"/>
+      <c r="AS54" s="52"/>
+      <c r="AT54" s="52"/>
+      <c r="AU54" s="52"/>
+      <c r="AV54" s="54"/>
+      <c r="AW54" s="52"/>
+      <c r="AX54" s="52"/>
+      <c r="AY54" s="52"/>
+      <c r="AZ54" s="52"/>
+      <c r="BA54" s="52"/>
+      <c r="BB54" s="52"/>
+      <c r="BC54" s="52"/>
+      <c r="BD54" s="52"/>
+      <c r="BE54" s="52"/>
+      <c r="BF54" s="52"/>
+      <c r="BG54" s="52"/>
+      <c r="BH54" s="52"/>
+      <c r="BI54" s="52"/>
+      <c r="BJ54" s="52"/>
+      <c r="BK54" s="52"/>
+      <c r="BL54" s="52"/>
+      <c r="BM54" s="52"/>
+      <c r="BN54" s="52"/>
+      <c r="BO54" s="52"/>
+      <c r="BP54" s="52"/>
+      <c r="BQ54" s="52"/>
+      <c r="BR54" s="52"/>
+      <c r="BS54" s="52"/>
+      <c r="BT54" s="52"/>
+      <c r="BU54" s="52"/>
+      <c r="BV54" s="52"/>
+      <c r="BW54" s="52"/>
+      <c r="BX54" s="52"/>
+      <c r="BY54" s="52"/>
+      <c r="BZ54" s="52"/>
+      <c r="CA54" s="52"/>
+      <c r="CB54" s="52"/>
+      <c r="CC54" s="52"/>
+      <c r="CD54" s="52"/>
+      <c r="CE54" s="52"/>
+      <c r="CF54" s="52"/>
+      <c r="CG54" s="52"/>
+      <c r="CH54" s="52"/>
+      <c r="CI54" s="52"/>
+      <c r="CJ54" s="52"/>
+      <c r="CK54" s="52"/>
+      <c r="CL54" s="55"/>
     </row>
-    <row r="54" spans="1:90" s="29" customFormat="1" x14ac:dyDescent="0.15">
-      <c r="A54" s="70"/>
-      <c r="B54" s="71"/>
-      <c r="C54" s="71"/>
-      <c r="D54" s="71"/>
-      <c r="E54" s="71"/>
-      <c r="F54" s="71"/>
-      <c r="G54" s="71"/>
-      <c r="H54" s="71"/>
-      <c r="I54" s="71"/>
-      <c r="J54" s="71"/>
-      <c r="K54" s="71"/>
-      <c r="L54" s="71"/>
-      <c r="M54" s="71"/>
-      <c r="N54" s="71"/>
-      <c r="O54" s="71"/>
-      <c r="P54" s="71"/>
-      <c r="Q54" s="71"/>
-      <c r="R54" s="71"/>
-      <c r="S54" s="71"/>
-      <c r="T54" s="71"/>
-      <c r="U54" s="71"/>
-      <c r="V54" s="71"/>
-      <c r="W54" s="71"/>
-      <c r="X54" s="71"/>
-      <c r="Y54" s="71"/>
-      <c r="Z54" s="71"/>
-      <c r="AA54" s="71"/>
-      <c r="AB54" s="71"/>
-      <c r="AC54" s="71"/>
-      <c r="AD54" s="71"/>
-      <c r="AE54" s="71"/>
-      <c r="AF54" s="71"/>
-      <c r="AG54" s="71"/>
-      <c r="AH54" s="71"/>
-      <c r="AI54" s="71"/>
-      <c r="AJ54" s="71"/>
-      <c r="AK54" s="71"/>
-      <c r="AL54" s="71"/>
-      <c r="AM54" s="71"/>
-      <c r="AN54" s="71"/>
-      <c r="AO54" s="71"/>
-      <c r="AP54" s="71"/>
-      <c r="AQ54" s="71"/>
-      <c r="AR54" s="71"/>
-      <c r="AS54" s="71"/>
-      <c r="AT54" s="71"/>
-      <c r="AU54" s="71"/>
-      <c r="AV54" s="71"/>
-      <c r="AW54" s="71"/>
-      <c r="AX54" s="71"/>
-      <c r="AY54" s="71"/>
-      <c r="AZ54" s="71"/>
-      <c r="BA54" s="71"/>
-      <c r="BB54" s="71"/>
-      <c r="BC54" s="71"/>
-      <c r="BD54" s="71"/>
-      <c r="BE54" s="71"/>
-      <c r="BF54" s="71"/>
-      <c r="BG54" s="71"/>
-      <c r="BH54" s="71"/>
-      <c r="BI54" s="71"/>
-      <c r="BJ54" s="71"/>
-      <c r="BK54" s="71"/>
-      <c r="BL54" s="71"/>
-      <c r="BM54" s="71"/>
-      <c r="BN54" s="71"/>
-      <c r="BO54" s="71"/>
-      <c r="BP54" s="71"/>
-      <c r="BQ54" s="71"/>
-      <c r="BR54" s="71"/>
-      <c r="BS54" s="71"/>
-      <c r="BT54" s="71"/>
-      <c r="BU54" s="71"/>
-      <c r="BV54" s="71"/>
-      <c r="BW54" s="71"/>
-      <c r="BX54" s="71"/>
-      <c r="BY54" s="71"/>
-      <c r="BZ54" s="71"/>
-      <c r="CA54" s="71"/>
-      <c r="CB54" s="71"/>
-      <c r="CC54" s="71"/>
-      <c r="CD54" s="71"/>
-      <c r="CE54" s="71"/>
-      <c r="CF54" s="71"/>
-      <c r="CG54" s="71"/>
-      <c r="CH54" s="71"/>
-      <c r="CI54" s="71"/>
-      <c r="CJ54" s="71"/>
-      <c r="CK54" s="71"/>
-      <c r="CL54" s="72"/>
+    <row r="55" spans="1:90">
+      <c r="A55" s="56"/>
+      <c r="B55" s="50"/>
+      <c r="C55" s="49"/>
+      <c r="D55" s="49"/>
+      <c r="E55" s="49"/>
+      <c r="F55" s="49"/>
+      <c r="G55" s="49"/>
+      <c r="H55" s="49"/>
+      <c r="I55" s="50"/>
+      <c r="J55" s="50"/>
+      <c r="K55" s="50"/>
+      <c r="L55" s="50"/>
+      <c r="M55" s="50"/>
+      <c r="N55" s="50"/>
+      <c r="O55" s="50"/>
+      <c r="P55" s="50"/>
+      <c r="Q55" s="50"/>
+      <c r="R55" s="50"/>
+      <c r="S55" s="50"/>
+      <c r="T55" s="50"/>
+      <c r="U55" s="50"/>
+      <c r="V55" s="50"/>
+      <c r="W55" s="50"/>
+      <c r="X55" s="50"/>
+      <c r="Y55" s="50"/>
+      <c r="Z55" s="50"/>
+      <c r="AA55" s="50"/>
+      <c r="AB55" s="50"/>
+      <c r="AC55" s="50"/>
+      <c r="AD55" s="50"/>
+      <c r="AE55" s="50"/>
+      <c r="AF55" s="50"/>
+      <c r="AG55" s="50"/>
+      <c r="AH55" s="50"/>
+      <c r="AI55" s="50"/>
+      <c r="AJ55" s="50"/>
+      <c r="AK55" s="50"/>
+      <c r="AL55" s="50"/>
+      <c r="AM55" s="50"/>
+      <c r="AN55" s="50"/>
+      <c r="AO55" s="50"/>
+      <c r="AP55" s="50"/>
+      <c r="AQ55" s="50"/>
+      <c r="AR55" s="50"/>
+      <c r="AS55" s="50"/>
+      <c r="AT55" s="50"/>
+      <c r="AU55" s="50"/>
+      <c r="AV55" s="51"/>
+      <c r="AW55" s="50"/>
+      <c r="AX55" s="50"/>
+      <c r="AY55" s="50"/>
+      <c r="AZ55" s="50"/>
+      <c r="BA55" s="50"/>
+      <c r="BB55" s="50"/>
+      <c r="BC55" s="50"/>
+      <c r="BD55" s="50"/>
+      <c r="BE55" s="50"/>
+      <c r="BF55" s="50"/>
+      <c r="BG55" s="50"/>
+      <c r="BH55" s="50"/>
+      <c r="BI55" s="50"/>
+      <c r="BJ55" s="50"/>
+      <c r="BK55" s="50"/>
+      <c r="BL55" s="50"/>
+      <c r="BM55" s="50"/>
+      <c r="BN55" s="50"/>
+      <c r="BO55" s="50"/>
+      <c r="BP55" s="50"/>
+      <c r="BQ55" s="50"/>
+      <c r="BR55" s="50"/>
+      <c r="BS55" s="50"/>
+      <c r="BT55" s="50"/>
+      <c r="BU55" s="50"/>
+      <c r="BV55" s="50"/>
+      <c r="BW55" s="50"/>
+      <c r="BX55" s="50"/>
+      <c r="BY55" s="50"/>
+      <c r="BZ55" s="50"/>
+      <c r="CA55" s="50"/>
+      <c r="CB55" s="50"/>
+      <c r="CC55" s="50"/>
+      <c r="CD55" s="50"/>
+      <c r="CE55" s="50"/>
+      <c r="CF55" s="50"/>
+      <c r="CG55" s="50"/>
+      <c r="CH55" s="50"/>
+      <c r="CI55" s="50"/>
+      <c r="CJ55" s="50"/>
+      <c r="CK55" s="50"/>
+      <c r="CL55" s="57"/>
     </row>
-    <row r="56" spans="1:90" x14ac:dyDescent="0.15">
-      <c r="A56" s="161" t="s">
-        <v>5</v>
-      </c>
-      <c r="B56" s="162"/>
-      <c r="C56" s="162"/>
-      <c r="D56" s="162"/>
-      <c r="E56" s="162"/>
-      <c r="F56" s="162"/>
-      <c r="G56" s="163"/>
-      <c r="H56" s="49"/>
-      <c r="I56" s="50"/>
-      <c r="J56" s="50"/>
-      <c r="K56" s="50"/>
-      <c r="L56" s="50"/>
-      <c r="M56" s="50"/>
-      <c r="N56" s="50"/>
-      <c r="O56" s="50"/>
-      <c r="P56" s="50"/>
-      <c r="Q56" s="50"/>
-      <c r="R56" s="50"/>
-      <c r="S56" s="50"/>
-      <c r="T56" s="50"/>
-      <c r="U56" s="50"/>
-      <c r="V56" s="50"/>
-      <c r="W56" s="50"/>
-      <c r="X56" s="50"/>
-      <c r="Y56" s="50"/>
-      <c r="Z56" s="50"/>
-      <c r="AA56" s="50"/>
-      <c r="AB56" s="50"/>
-      <c r="AC56" s="50"/>
-      <c r="AD56" s="50"/>
-      <c r="AE56" s="50"/>
-      <c r="AF56" s="50"/>
-      <c r="AG56" s="50"/>
-      <c r="AH56" s="50"/>
-      <c r="AI56" s="50"/>
-      <c r="AJ56" s="50"/>
-      <c r="AK56" s="50"/>
-      <c r="AL56" s="50"/>
-      <c r="AM56" s="50"/>
-      <c r="AN56" s="50"/>
-      <c r="AO56" s="50"/>
-      <c r="AP56" s="50"/>
-      <c r="AQ56" s="50"/>
-      <c r="AR56" s="50"/>
-      <c r="AS56" s="50"/>
-      <c r="AT56" s="50"/>
-      <c r="AU56" s="50"/>
-      <c r="AV56" s="51"/>
-      <c r="AW56" s="50"/>
-      <c r="AX56" s="50"/>
-      <c r="AY56" s="50"/>
-      <c r="AZ56" s="50"/>
-      <c r="BA56" s="50"/>
-      <c r="BB56" s="50"/>
-      <c r="BC56" s="50"/>
-      <c r="BD56" s="50"/>
-      <c r="BE56" s="50"/>
-      <c r="BF56" s="50"/>
-      <c r="BG56" s="50"/>
-      <c r="BH56" s="50"/>
-      <c r="BI56" s="50"/>
-      <c r="BJ56" s="50"/>
-    </row>
-    <row r="57" spans="1:90" x14ac:dyDescent="0.15">
-      <c r="A57" s="75" t="s">
-        <v>139</v>
-      </c>
-      <c r="B57" s="76"/>
-      <c r="C57" s="77" t="s">
-        <v>140</v>
-      </c>
-      <c r="D57" s="53"/>
-      <c r="E57" s="53"/>
-      <c r="F57" s="53"/>
-      <c r="G57" s="53"/>
-      <c r="H57" s="53"/>
-      <c r="I57" s="52"/>
-      <c r="J57" s="52"/>
-      <c r="K57" s="52"/>
-      <c r="L57" s="52"/>
-      <c r="M57" s="52"/>
-      <c r="N57" s="52"/>
-      <c r="O57" s="52"/>
-      <c r="P57" s="52"/>
-      <c r="Q57" s="52"/>
-      <c r="R57" s="52"/>
-      <c r="S57" s="52"/>
-      <c r="T57" s="52"/>
-      <c r="U57" s="52"/>
-      <c r="V57" s="52"/>
-      <c r="W57" s="52"/>
-      <c r="X57" s="52"/>
-      <c r="Y57" s="52"/>
-      <c r="Z57" s="52"/>
-      <c r="AA57" s="52"/>
-      <c r="AB57" s="52"/>
-      <c r="AC57" s="52"/>
-      <c r="AD57" s="52"/>
-      <c r="AE57" s="52"/>
-      <c r="AF57" s="52"/>
-      <c r="AG57" s="52"/>
-      <c r="AH57" s="52"/>
-      <c r="AI57" s="52"/>
-      <c r="AJ57" s="52"/>
-      <c r="AK57" s="52"/>
-      <c r="AL57" s="52"/>
-      <c r="AM57" s="52"/>
-      <c r="AN57" s="52"/>
-      <c r="AO57" s="52"/>
-      <c r="AP57" s="52"/>
-      <c r="AQ57" s="52"/>
-      <c r="AR57" s="52"/>
-      <c r="AS57" s="52"/>
-      <c r="AT57" s="52"/>
-      <c r="AU57" s="52"/>
-      <c r="AV57" s="54"/>
-      <c r="AW57" s="52"/>
-      <c r="AX57" s="52"/>
-      <c r="AY57" s="52"/>
-      <c r="AZ57" s="52"/>
-      <c r="BA57" s="52"/>
-      <c r="BB57" s="52"/>
-      <c r="BC57" s="52"/>
-      <c r="BD57" s="52"/>
-      <c r="BE57" s="52"/>
-      <c r="BF57" s="52"/>
-      <c r="BG57" s="52"/>
-      <c r="BH57" s="52"/>
-      <c r="BI57" s="52"/>
-      <c r="BJ57" s="52"/>
-      <c r="BK57" s="52"/>
-      <c r="BL57" s="52"/>
-      <c r="BM57" s="52"/>
-      <c r="BN57" s="52"/>
-      <c r="BO57" s="52"/>
-      <c r="BP57" s="52"/>
-      <c r="BQ57" s="52"/>
-      <c r="BR57" s="52"/>
-      <c r="BS57" s="52"/>
-      <c r="BT57" s="52"/>
-      <c r="BU57" s="52"/>
-      <c r="BV57" s="52"/>
-      <c r="BW57" s="52"/>
-      <c r="BX57" s="52"/>
-      <c r="BY57" s="52"/>
-      <c r="BZ57" s="52"/>
-      <c r="CA57" s="52"/>
-      <c r="CB57" s="52"/>
-      <c r="CC57" s="52"/>
-      <c r="CD57" s="52"/>
-      <c r="CE57" s="52"/>
-      <c r="CF57" s="52"/>
-      <c r="CG57" s="52"/>
-      <c r="CH57" s="52"/>
-      <c r="CI57" s="52"/>
-      <c r="CJ57" s="52"/>
-      <c r="CK57" s="52"/>
-      <c r="CL57" s="55"/>
-    </row>
-    <row r="58" spans="1:90" x14ac:dyDescent="0.15">
-      <c r="A58" s="56"/>
-      <c r="B58" s="50"/>
-      <c r="C58" s="49"/>
-      <c r="D58" s="49"/>
-      <c r="E58" s="49"/>
-      <c r="F58" s="49"/>
-      <c r="G58" s="49"/>
-      <c r="H58" s="49"/>
-      <c r="I58" s="50"/>
-      <c r="J58" s="50"/>
-      <c r="K58" s="50"/>
-      <c r="L58" s="50"/>
-      <c r="M58" s="50"/>
-      <c r="N58" s="50"/>
-      <c r="O58" s="50"/>
-      <c r="P58" s="50"/>
-      <c r="Q58" s="50"/>
-      <c r="R58" s="50"/>
-      <c r="S58" s="50"/>
-      <c r="T58" s="50"/>
-      <c r="U58" s="50"/>
-      <c r="V58" s="50"/>
-      <c r="W58" s="50"/>
-      <c r="X58" s="50"/>
-      <c r="Y58" s="50"/>
-      <c r="Z58" s="50"/>
-      <c r="AA58" s="50"/>
-      <c r="AB58" s="50"/>
-      <c r="AC58" s="50"/>
-      <c r="AD58" s="50"/>
-      <c r="AE58" s="50"/>
-      <c r="AF58" s="50"/>
-      <c r="AG58" s="50"/>
-      <c r="AH58" s="50"/>
-      <c r="AI58" s="50"/>
-      <c r="AJ58" s="50"/>
-      <c r="AK58" s="50"/>
-      <c r="AL58" s="50"/>
-      <c r="AM58" s="50"/>
-      <c r="AN58" s="50"/>
-      <c r="AO58" s="50"/>
-      <c r="AP58" s="50"/>
-      <c r="AQ58" s="50"/>
-      <c r="AR58" s="50"/>
-      <c r="AS58" s="50"/>
-      <c r="AT58" s="50"/>
-      <c r="AU58" s="50"/>
-      <c r="AV58" s="51"/>
-      <c r="AW58" s="50"/>
-      <c r="AX58" s="50"/>
-      <c r="AY58" s="50"/>
-      <c r="AZ58" s="50"/>
-      <c r="BA58" s="50"/>
-      <c r="BB58" s="50"/>
-      <c r="BC58" s="50"/>
-      <c r="BD58" s="50"/>
-      <c r="BE58" s="50"/>
-      <c r="BF58" s="50"/>
-      <c r="BG58" s="50"/>
-      <c r="BH58" s="50"/>
-      <c r="BI58" s="50"/>
-      <c r="BJ58" s="50"/>
-      <c r="BK58" s="50"/>
-      <c r="BL58" s="50"/>
-      <c r="BM58" s="50"/>
-      <c r="BN58" s="50"/>
-      <c r="BO58" s="50"/>
-      <c r="BP58" s="50"/>
-      <c r="BQ58" s="50"/>
-      <c r="BR58" s="50"/>
-      <c r="BS58" s="50"/>
-      <c r="BT58" s="50"/>
-      <c r="BU58" s="50"/>
-      <c r="BV58" s="50"/>
-      <c r="BW58" s="50"/>
-      <c r="BX58" s="50"/>
-      <c r="BY58" s="50"/>
-      <c r="BZ58" s="50"/>
-      <c r="CA58" s="50"/>
-      <c r="CB58" s="50"/>
-      <c r="CC58" s="50"/>
-      <c r="CD58" s="50"/>
-      <c r="CE58" s="50"/>
-      <c r="CF58" s="50"/>
-      <c r="CG58" s="50"/>
-      <c r="CH58" s="50"/>
-      <c r="CI58" s="50"/>
-      <c r="CJ58" s="50"/>
-      <c r="CK58" s="50"/>
-      <c r="CL58" s="57"/>
-    </row>
-    <row r="59" spans="1:90" x14ac:dyDescent="0.15">
-      <c r="A59" s="58"/>
-      <c r="B59" s="59"/>
-      <c r="C59" s="60"/>
-      <c r="D59" s="60"/>
-      <c r="E59" s="60"/>
-      <c r="F59" s="60"/>
-      <c r="G59" s="60"/>
-      <c r="H59" s="60"/>
-      <c r="I59" s="59"/>
-      <c r="J59" s="59"/>
-      <c r="K59" s="59"/>
-      <c r="L59" s="59"/>
-      <c r="M59" s="59"/>
-      <c r="N59" s="59"/>
-      <c r="O59" s="59"/>
-      <c r="P59" s="59"/>
-      <c r="Q59" s="59"/>
-      <c r="R59" s="59"/>
-      <c r="S59" s="59"/>
-      <c r="T59" s="59"/>
-      <c r="U59" s="59"/>
-      <c r="V59" s="59"/>
-      <c r="W59" s="59"/>
-      <c r="X59" s="59"/>
-      <c r="Y59" s="59"/>
-      <c r="Z59" s="59"/>
-      <c r="AA59" s="59"/>
-      <c r="AB59" s="59"/>
-      <c r="AC59" s="59"/>
-      <c r="AD59" s="59"/>
-      <c r="AE59" s="59"/>
-      <c r="AF59" s="59"/>
-      <c r="AG59" s="59"/>
-      <c r="AH59" s="59"/>
-      <c r="AI59" s="59"/>
-      <c r="AJ59" s="59"/>
-      <c r="AK59" s="59"/>
-      <c r="AL59" s="59"/>
-      <c r="AM59" s="59"/>
-      <c r="AN59" s="59"/>
-      <c r="AO59" s="59"/>
-      <c r="AP59" s="59"/>
-      <c r="AQ59" s="59"/>
-      <c r="AR59" s="59"/>
-      <c r="AS59" s="59"/>
-      <c r="AT59" s="59"/>
-      <c r="AU59" s="59"/>
-      <c r="AV59" s="61"/>
-      <c r="AW59" s="59"/>
-      <c r="AX59" s="59"/>
-      <c r="AY59" s="59"/>
-      <c r="AZ59" s="59"/>
-      <c r="BA59" s="59"/>
-      <c r="BB59" s="59"/>
-      <c r="BC59" s="59"/>
-      <c r="BD59" s="59"/>
-      <c r="BE59" s="59"/>
-      <c r="BF59" s="59"/>
-      <c r="BG59" s="59"/>
-      <c r="BH59" s="59"/>
-      <c r="BI59" s="59"/>
-      <c r="BJ59" s="59"/>
-      <c r="BK59" s="59"/>
-      <c r="BL59" s="59"/>
-      <c r="BM59" s="59"/>
-      <c r="BN59" s="59"/>
-      <c r="BO59" s="59"/>
-      <c r="BP59" s="59"/>
-      <c r="BQ59" s="59"/>
-      <c r="BR59" s="59"/>
-      <c r="BS59" s="59"/>
-      <c r="BT59" s="59"/>
-      <c r="BU59" s="59"/>
-      <c r="BV59" s="59"/>
-      <c r="BW59" s="59"/>
-      <c r="BX59" s="59"/>
-      <c r="BY59" s="59"/>
-      <c r="BZ59" s="59"/>
-      <c r="CA59" s="59"/>
-      <c r="CB59" s="59"/>
-      <c r="CC59" s="59"/>
-      <c r="CD59" s="59"/>
-      <c r="CE59" s="59"/>
-      <c r="CF59" s="59"/>
-      <c r="CG59" s="59"/>
-      <c r="CH59" s="59"/>
-      <c r="CI59" s="59"/>
-      <c r="CJ59" s="59"/>
-      <c r="CK59" s="59"/>
-      <c r="CL59" s="62"/>
+    <row r="56" spans="1:90">
+      <c r="A56" s="58"/>
+      <c r="B56" s="59"/>
+      <c r="C56" s="60"/>
+      <c r="D56" s="60"/>
+      <c r="E56" s="60"/>
+      <c r="F56" s="60"/>
+      <c r="G56" s="60"/>
+      <c r="H56" s="60"/>
+      <c r="I56" s="59"/>
+      <c r="J56" s="59"/>
+      <c r="K56" s="59"/>
+      <c r="L56" s="59"/>
+      <c r="M56" s="59"/>
+      <c r="N56" s="59"/>
+      <c r="O56" s="59"/>
+      <c r="P56" s="59"/>
+      <c r="Q56" s="59"/>
+      <c r="R56" s="59"/>
+      <c r="S56" s="59"/>
+      <c r="T56" s="59"/>
+      <c r="U56" s="59"/>
+      <c r="V56" s="59"/>
+      <c r="W56" s="59"/>
+      <c r="X56" s="59"/>
+      <c r="Y56" s="59"/>
+      <c r="Z56" s="59"/>
+      <c r="AA56" s="59"/>
+      <c r="AB56" s="59"/>
+      <c r="AC56" s="59"/>
+      <c r="AD56" s="59"/>
+      <c r="AE56" s="59"/>
+      <c r="AF56" s="59"/>
+      <c r="AG56" s="59"/>
+      <c r="AH56" s="59"/>
+      <c r="AI56" s="59"/>
+      <c r="AJ56" s="59"/>
+      <c r="AK56" s="59"/>
+      <c r="AL56" s="59"/>
+      <c r="AM56" s="59"/>
+      <c r="AN56" s="59"/>
+      <c r="AO56" s="59"/>
+      <c r="AP56" s="59"/>
+      <c r="AQ56" s="59"/>
+      <c r="AR56" s="59"/>
+      <c r="AS56" s="59"/>
+      <c r="AT56" s="59"/>
+      <c r="AU56" s="59"/>
+      <c r="AV56" s="61"/>
+      <c r="AW56" s="59"/>
+      <c r="AX56" s="59"/>
+      <c r="AY56" s="59"/>
+      <c r="AZ56" s="59"/>
+      <c r="BA56" s="59"/>
+      <c r="BB56" s="59"/>
+      <c r="BC56" s="59"/>
+      <c r="BD56" s="59"/>
+      <c r="BE56" s="59"/>
+      <c r="BF56" s="59"/>
+      <c r="BG56" s="59"/>
+      <c r="BH56" s="59"/>
+      <c r="BI56" s="59"/>
+      <c r="BJ56" s="59"/>
+      <c r="BK56" s="59"/>
+      <c r="BL56" s="59"/>
+      <c r="BM56" s="59"/>
+      <c r="BN56" s="59"/>
+      <c r="BO56" s="59"/>
+      <c r="BP56" s="59"/>
+      <c r="BQ56" s="59"/>
+      <c r="BR56" s="59"/>
+      <c r="BS56" s="59"/>
+      <c r="BT56" s="59"/>
+      <c r="BU56" s="59"/>
+      <c r="BV56" s="59"/>
+      <c r="BW56" s="59"/>
+      <c r="BX56" s="59"/>
+      <c r="BY56" s="59"/>
+      <c r="BZ56" s="59"/>
+      <c r="CA56" s="59"/>
+      <c r="CB56" s="59"/>
+      <c r="CC56" s="59"/>
+      <c r="CD56" s="59"/>
+      <c r="CE56" s="59"/>
+      <c r="CF56" s="59"/>
+      <c r="CG56" s="59"/>
+      <c r="CH56" s="59"/>
+      <c r="CI56" s="59"/>
+      <c r="CJ56" s="59"/>
+      <c r="CK56" s="59"/>
+      <c r="CL56" s="62"/>
     </row>
   </sheetData>
-  <autoFilter ref="A24:CI25">
+  <autoFilter ref="A24:CI25" xr:uid="{00000000-0009-0000-0000-000002000000}">
     <filterColumn colId="0" showButton="0"/>
     <filterColumn colId="2" showButton="0"/>
     <filterColumn colId="3" showButton="0"/>
@@ -10444,79 +10029,40 @@
     <filterColumn colId="84" showButton="0"/>
     <filterColumn colId="85" showButton="0"/>
   </autoFilter>
-  <mergeCells count="329">
-    <mergeCell ref="Y29:AA29"/>
-    <mergeCell ref="AB29:AF29"/>
+  <mergeCells count="284">
     <mergeCell ref="Y26:AA26"/>
     <mergeCell ref="AB26:AF26"/>
-    <mergeCell ref="BL29:BN29"/>
-    <mergeCell ref="BO29:CI29"/>
-    <mergeCell ref="A30:B30"/>
-    <mergeCell ref="C30:H30"/>
-    <mergeCell ref="I30:N30"/>
-    <mergeCell ref="O30:Q30"/>
-    <mergeCell ref="V30:X30"/>
-    <mergeCell ref="Y30:AA30"/>
-    <mergeCell ref="AB30:AF30"/>
+    <mergeCell ref="AG29:AH29"/>
     <mergeCell ref="AG30:AH30"/>
-    <mergeCell ref="AI30:AJ30"/>
-    <mergeCell ref="AK30:AM30"/>
-    <mergeCell ref="AN30:AU30"/>
-    <mergeCell ref="AV30:BG30"/>
-    <mergeCell ref="BH30:BK30"/>
-    <mergeCell ref="BL30:BN30"/>
-    <mergeCell ref="BO30:CI30"/>
-    <mergeCell ref="A29:B29"/>
-    <mergeCell ref="C29:H29"/>
-    <mergeCell ref="I29:N29"/>
-    <mergeCell ref="O29:Q29"/>
-    <mergeCell ref="V29:X29"/>
-    <mergeCell ref="AG32:AH32"/>
-    <mergeCell ref="AG33:AH33"/>
     <mergeCell ref="BL26:BN26"/>
     <mergeCell ref="BO26:CI26"/>
-    <mergeCell ref="A28:B28"/>
-    <mergeCell ref="C28:H28"/>
-    <mergeCell ref="I28:N28"/>
-    <mergeCell ref="O28:Q28"/>
-    <mergeCell ref="V28:X28"/>
-    <mergeCell ref="Y28:AA28"/>
-    <mergeCell ref="AB28:AF28"/>
-    <mergeCell ref="AG28:AH28"/>
-    <mergeCell ref="AI28:AJ28"/>
-    <mergeCell ref="AK28:AM28"/>
-    <mergeCell ref="AN28:AU28"/>
-    <mergeCell ref="AV28:BG28"/>
-    <mergeCell ref="BH28:BK28"/>
-    <mergeCell ref="BL28:BN28"/>
-    <mergeCell ref="BO28:CI28"/>
     <mergeCell ref="A26:B26"/>
     <mergeCell ref="C26:H26"/>
     <mergeCell ref="I26:N26"/>
     <mergeCell ref="O26:Q26"/>
     <mergeCell ref="V26:X26"/>
-    <mergeCell ref="BO31:CI38"/>
-    <mergeCell ref="BL31:BN31"/>
+    <mergeCell ref="BO28:CI35"/>
+    <mergeCell ref="BL28:BN28"/>
     <mergeCell ref="AN27:AU27"/>
     <mergeCell ref="AV27:BG27"/>
     <mergeCell ref="BH27:BK27"/>
     <mergeCell ref="BL27:BN27"/>
     <mergeCell ref="BO27:CI27"/>
-    <mergeCell ref="BL37:BN37"/>
-    <mergeCell ref="BH38:BK38"/>
-    <mergeCell ref="BL38:BN38"/>
+    <mergeCell ref="BL34:BN34"/>
+    <mergeCell ref="BH35:BK35"/>
+    <mergeCell ref="BL35:BN35"/>
+    <mergeCell ref="BL29:BN29"/>
+    <mergeCell ref="BL30:BN30"/>
+    <mergeCell ref="BL31:BN31"/>
     <mergeCell ref="BL32:BN32"/>
     <mergeCell ref="BL33:BN33"/>
-    <mergeCell ref="BL34:BN34"/>
-    <mergeCell ref="BL35:BN35"/>
-    <mergeCell ref="BL36:BN36"/>
-    <mergeCell ref="AN38:AU38"/>
-    <mergeCell ref="V38:X38"/>
-    <mergeCell ref="O37:Q37"/>
-    <mergeCell ref="O38:Q38"/>
-    <mergeCell ref="O31:Q31"/>
-    <mergeCell ref="O32:Q32"/>
-    <mergeCell ref="O33:Q33"/>
+    <mergeCell ref="AN35:AU35"/>
+    <mergeCell ref="V35:X35"/>
+    <mergeCell ref="O34:Q34"/>
+    <mergeCell ref="O35:Q35"/>
+    <mergeCell ref="O28:Q28"/>
+    <mergeCell ref="O29:Q29"/>
+    <mergeCell ref="O30:Q30"/>
     <mergeCell ref="A27:B27"/>
     <mergeCell ref="C27:H27"/>
     <mergeCell ref="I27:N27"/>
@@ -10526,121 +10072,121 @@
     <mergeCell ref="AB27:AF27"/>
     <mergeCell ref="AG27:AH27"/>
     <mergeCell ref="AI27:AJ27"/>
+    <mergeCell ref="V28:X28"/>
+    <mergeCell ref="V29:X29"/>
+    <mergeCell ref="V30:X30"/>
     <mergeCell ref="V31:X31"/>
     <mergeCell ref="V32:X32"/>
     <mergeCell ref="V33:X33"/>
     <mergeCell ref="V34:X34"/>
-    <mergeCell ref="V35:X35"/>
-    <mergeCell ref="V36:X36"/>
-    <mergeCell ref="V37:X37"/>
-    <mergeCell ref="AI34:AJ34"/>
-    <mergeCell ref="AK34:AM34"/>
-    <mergeCell ref="AG31:AH31"/>
     <mergeCell ref="AI31:AJ31"/>
-    <mergeCell ref="Y37:AA37"/>
     <mergeCell ref="AK31:AM31"/>
-    <mergeCell ref="BH37:BK37"/>
+    <mergeCell ref="AG28:AH28"/>
+    <mergeCell ref="AI28:AJ28"/>
+    <mergeCell ref="Y34:AA34"/>
+    <mergeCell ref="AK28:AM28"/>
+    <mergeCell ref="BH34:BK34"/>
+    <mergeCell ref="BH29:BK29"/>
+    <mergeCell ref="BH30:BK30"/>
+    <mergeCell ref="BH31:BK31"/>
     <mergeCell ref="BH32:BK32"/>
     <mergeCell ref="BH33:BK33"/>
-    <mergeCell ref="BH34:BK34"/>
-    <mergeCell ref="BH35:BK35"/>
-    <mergeCell ref="BH36:BK36"/>
-    <mergeCell ref="AN34:AU34"/>
-    <mergeCell ref="I35:N35"/>
-    <mergeCell ref="I36:N36"/>
-    <mergeCell ref="I37:N37"/>
-    <mergeCell ref="O34:Q34"/>
-    <mergeCell ref="O35:Q35"/>
-    <mergeCell ref="O36:Q36"/>
-    <mergeCell ref="AV36:BG36"/>
-    <mergeCell ref="AV37:BG37"/>
     <mergeCell ref="AN31:AU31"/>
-    <mergeCell ref="Y38:AA38"/>
+    <mergeCell ref="I32:N32"/>
+    <mergeCell ref="I33:N33"/>
+    <mergeCell ref="I34:N34"/>
+    <mergeCell ref="O31:Q31"/>
+    <mergeCell ref="O32:Q32"/>
+    <mergeCell ref="O33:Q33"/>
+    <mergeCell ref="AV33:BG33"/>
+    <mergeCell ref="AV34:BG34"/>
+    <mergeCell ref="AN28:AU28"/>
+    <mergeCell ref="Y35:AA35"/>
+    <mergeCell ref="Y28:AA28"/>
+    <mergeCell ref="Y29:AA29"/>
+    <mergeCell ref="Y30:AA30"/>
     <mergeCell ref="Y31:AA31"/>
     <mergeCell ref="Y32:AA32"/>
     <mergeCell ref="Y33:AA33"/>
-    <mergeCell ref="Y34:AA34"/>
-    <mergeCell ref="Y35:AA35"/>
-    <mergeCell ref="Y36:AA36"/>
-    <mergeCell ref="AB37:AF37"/>
-    <mergeCell ref="AB38:AF38"/>
+    <mergeCell ref="AB34:AF34"/>
+    <mergeCell ref="AB35:AF35"/>
+    <mergeCell ref="AB28:AF28"/>
+    <mergeCell ref="AB29:AF29"/>
+    <mergeCell ref="AB30:AF30"/>
     <mergeCell ref="AB31:AF31"/>
     <mergeCell ref="AB32:AF32"/>
     <mergeCell ref="AB33:AF33"/>
-    <mergeCell ref="AB34:AF34"/>
-    <mergeCell ref="AB35:AF35"/>
-    <mergeCell ref="AB36:AF36"/>
-    <mergeCell ref="AG37:AH37"/>
-    <mergeCell ref="AI37:AJ37"/>
-    <mergeCell ref="AK37:AM37"/>
-    <mergeCell ref="AN37:AU37"/>
-    <mergeCell ref="AN36:AU36"/>
-    <mergeCell ref="C38:H38"/>
+    <mergeCell ref="AG34:AH34"/>
+    <mergeCell ref="AI34:AJ34"/>
+    <mergeCell ref="AK34:AM34"/>
+    <mergeCell ref="AN34:AU34"/>
+    <mergeCell ref="AN33:AU33"/>
+    <mergeCell ref="C35:H35"/>
+    <mergeCell ref="A28:B28"/>
+    <mergeCell ref="A29:B29"/>
+    <mergeCell ref="A30:B30"/>
     <mergeCell ref="A31:B31"/>
     <mergeCell ref="A32:B32"/>
     <mergeCell ref="A33:B33"/>
     <mergeCell ref="A34:B34"/>
     <mergeCell ref="A35:B35"/>
-    <mergeCell ref="A36:B36"/>
-    <mergeCell ref="A37:B37"/>
-    <mergeCell ref="A38:B38"/>
+    <mergeCell ref="C28:H28"/>
+    <mergeCell ref="C29:H29"/>
+    <mergeCell ref="C30:H30"/>
     <mergeCell ref="C31:H31"/>
     <mergeCell ref="C32:H32"/>
     <mergeCell ref="C33:H33"/>
     <mergeCell ref="C34:H34"/>
-    <mergeCell ref="C35:H35"/>
-    <mergeCell ref="C36:H36"/>
-    <mergeCell ref="C37:H37"/>
-    <mergeCell ref="I38:N38"/>
+    <mergeCell ref="I35:N35"/>
+    <mergeCell ref="I28:N28"/>
+    <mergeCell ref="I29:N29"/>
+    <mergeCell ref="I30:N30"/>
     <mergeCell ref="I31:N31"/>
-    <mergeCell ref="I32:N32"/>
-    <mergeCell ref="I33:N33"/>
-    <mergeCell ref="I34:N34"/>
-    <mergeCell ref="BL41:BN42"/>
-    <mergeCell ref="BO41:CI42"/>
-    <mergeCell ref="Y41:AA42"/>
-    <mergeCell ref="AB41:AF42"/>
-    <mergeCell ref="AG41:AH42"/>
-    <mergeCell ref="AI32:AJ32"/>
-    <mergeCell ref="AK32:AM32"/>
+    <mergeCell ref="BL38:BN39"/>
+    <mergeCell ref="BO38:CI39"/>
+    <mergeCell ref="Y38:AA39"/>
+    <mergeCell ref="AB38:AF39"/>
+    <mergeCell ref="AG38:AH39"/>
+    <mergeCell ref="AI29:AJ29"/>
+    <mergeCell ref="AK29:AM29"/>
+    <mergeCell ref="AN29:AU29"/>
+    <mergeCell ref="AI30:AJ30"/>
+    <mergeCell ref="AK30:AM30"/>
+    <mergeCell ref="AN30:AU30"/>
+    <mergeCell ref="BH28:BK28"/>
+    <mergeCell ref="AG35:AH35"/>
+    <mergeCell ref="AG31:AH31"/>
+    <mergeCell ref="AG32:AH32"/>
+    <mergeCell ref="AG33:AH33"/>
     <mergeCell ref="AN32:AU32"/>
     <mergeCell ref="AI33:AJ33"/>
     <mergeCell ref="AK33:AM33"/>
-    <mergeCell ref="AN33:AU33"/>
-    <mergeCell ref="BH31:BK31"/>
-    <mergeCell ref="AG38:AH38"/>
-    <mergeCell ref="AG34:AH34"/>
-    <mergeCell ref="AG35:AH35"/>
-    <mergeCell ref="AG36:AH36"/>
-    <mergeCell ref="AN35:AU35"/>
-    <mergeCell ref="AI36:AJ36"/>
-    <mergeCell ref="AK36:AM36"/>
-    <mergeCell ref="AK43:AM43"/>
-    <mergeCell ref="AN43:AU43"/>
-    <mergeCell ref="AV43:BG43"/>
-    <mergeCell ref="A40:H40"/>
-    <mergeCell ref="BL43:BN43"/>
-    <mergeCell ref="BO43:CI43"/>
-    <mergeCell ref="AI41:AJ42"/>
-    <mergeCell ref="AK41:AM42"/>
-    <mergeCell ref="AN41:AU42"/>
-    <mergeCell ref="AV41:BG42"/>
-    <mergeCell ref="A43:B43"/>
-    <mergeCell ref="C43:H43"/>
-    <mergeCell ref="I43:N43"/>
-    <mergeCell ref="O43:Q43"/>
-    <mergeCell ref="V43:X43"/>
-    <mergeCell ref="Y43:AA43"/>
-    <mergeCell ref="AB43:AF43"/>
-    <mergeCell ref="AG43:AH43"/>
-    <mergeCell ref="AI43:AJ43"/>
-    <mergeCell ref="A45:H45"/>
-    <mergeCell ref="I41:N42"/>
-    <mergeCell ref="O41:Q42"/>
-    <mergeCell ref="R41:U41"/>
-    <mergeCell ref="V41:X42"/>
-    <mergeCell ref="BH41:BK42"/>
-    <mergeCell ref="BH43:BK43"/>
+    <mergeCell ref="AK40:AM40"/>
+    <mergeCell ref="AN40:AU40"/>
+    <mergeCell ref="AV40:BG40"/>
+    <mergeCell ref="A37:H37"/>
+    <mergeCell ref="BL40:BN40"/>
+    <mergeCell ref="BO40:CI40"/>
+    <mergeCell ref="AI38:AJ39"/>
+    <mergeCell ref="AK38:AM39"/>
+    <mergeCell ref="AN38:AU39"/>
+    <mergeCell ref="AV38:BG39"/>
+    <mergeCell ref="A40:B40"/>
+    <mergeCell ref="C40:H40"/>
+    <mergeCell ref="I40:N40"/>
+    <mergeCell ref="O40:Q40"/>
+    <mergeCell ref="V40:X40"/>
+    <mergeCell ref="Y40:AA40"/>
+    <mergeCell ref="AB40:AF40"/>
+    <mergeCell ref="AG40:AH40"/>
+    <mergeCell ref="AI40:AJ40"/>
+    <mergeCell ref="A42:H42"/>
+    <mergeCell ref="I38:N39"/>
+    <mergeCell ref="O38:Q39"/>
+    <mergeCell ref="R38:U38"/>
+    <mergeCell ref="V38:X39"/>
+    <mergeCell ref="BH38:BK39"/>
+    <mergeCell ref="BH40:BK40"/>
     <mergeCell ref="A21:B21"/>
     <mergeCell ref="C21:H21"/>
     <mergeCell ref="I21:N21"/>
@@ -10654,10 +10200,10 @@
     <mergeCell ref="O24:Q25"/>
     <mergeCell ref="V24:X25"/>
     <mergeCell ref="Y24:AA25"/>
-    <mergeCell ref="A41:B42"/>
-    <mergeCell ref="C41:H42"/>
-    <mergeCell ref="AV34:BG34"/>
-    <mergeCell ref="AV35:BG35"/>
+    <mergeCell ref="A38:B39"/>
+    <mergeCell ref="C38:H39"/>
+    <mergeCell ref="AV31:BG31"/>
+    <mergeCell ref="AV32:BG32"/>
     <mergeCell ref="A16:H16"/>
     <mergeCell ref="I16:CL16"/>
     <mergeCell ref="A18:H18"/>
@@ -10689,7 +10235,7 @@
     <mergeCell ref="AG15:AO15"/>
     <mergeCell ref="AP15:AV15"/>
     <mergeCell ref="AW15:BC15"/>
-    <mergeCell ref="A56:G56"/>
+    <mergeCell ref="A53:G53"/>
     <mergeCell ref="AY1:BD1"/>
     <mergeCell ref="A1:K2"/>
     <mergeCell ref="BE1:BJ1"/>
@@ -10715,9 +10261,9 @@
     <mergeCell ref="AP13:AV13"/>
     <mergeCell ref="R24:U24"/>
     <mergeCell ref="AK27:AM27"/>
-    <mergeCell ref="AV31:BG31"/>
-    <mergeCell ref="AV32:BG32"/>
-    <mergeCell ref="AV33:BG33"/>
+    <mergeCell ref="AV28:BG28"/>
+    <mergeCell ref="AV29:BG29"/>
+    <mergeCell ref="AV30:BG30"/>
     <mergeCell ref="A4:G4"/>
     <mergeCell ref="A5:CI7"/>
     <mergeCell ref="A9:H9"/>
@@ -10745,18 +10291,12 @@
     <mergeCell ref="AN26:AU26"/>
     <mergeCell ref="AV26:BG26"/>
     <mergeCell ref="BH26:BK26"/>
-    <mergeCell ref="AK29:AM29"/>
-    <mergeCell ref="AN29:AU29"/>
-    <mergeCell ref="AV29:BG29"/>
-    <mergeCell ref="BH29:BK29"/>
     <mergeCell ref="AI26:AJ26"/>
-    <mergeCell ref="AV38:BG38"/>
-    <mergeCell ref="AI38:AJ38"/>
-    <mergeCell ref="AK38:AM38"/>
+    <mergeCell ref="AV35:BG35"/>
     <mergeCell ref="AI35:AJ35"/>
     <mergeCell ref="AK35:AM35"/>
-    <mergeCell ref="AG29:AH29"/>
-    <mergeCell ref="AI29:AJ29"/>
+    <mergeCell ref="AI32:AJ32"/>
+    <mergeCell ref="AK32:AM32"/>
     <mergeCell ref="CM24:CO25"/>
     <mergeCell ref="AB21:AF21"/>
     <mergeCell ref="AG21:AH21"/>
@@ -10777,22 +10317,23 @@
   </mergeCells>
   <phoneticPr fontId="3"/>
   <dataValidations count="4">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="O43:Q43 AK43:AM43 AK21:AM21 O21:Q21 O26:O38 AK26:AM38">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="O40:Q40 AK40:AM40 AK21:AM21 O21:Q21 AK26:AM35 O26:O35" xr:uid="{00000000-0002-0000-0200-000000000000}">
       <formula1>"ヘッダ,ボディ,フッタ"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AB43:AF43 AB21:AF21 AB26:AB38">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AB40:AF40 AB21:AF21 AB26:AB35" xr:uid="{00000000-0002-0000-0200-000001000000}">
       <formula1>"固定長,可変長"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AI43 AG43 AG21 AI21 AI26:AI38 AG26:AG38">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="AI40 AG40 AG21 AI21 AG26:AG35 AI26:AI35" xr:uid="{00000000-0002-0000-0200-000002000000}">
       <formula1>"○"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" sqref="R43:U43 R21:U21 R26:U38">
+    <dataValidation type="list" allowBlank="1" sqref="R40:U40 R21:U21 R26:U35" xr:uid="{00000000-0002-0000-0200-000003000000}">
       <formula1>"○"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.39" right="0.4" top="0.98425196850393704" bottom="0.41" header="0.51181102362204722" footer="0.17"/>
   <pageSetup paperSize="8" scale="58" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
   <headerFooter alignWithMargins="0"/>
-  <legacyDrawingHF r:id="rId2"/>
+  <legacyDrawing r:id="rId2"/>
+  <legacyDrawingHF r:id="rId3"/>
 </worksheet>
 </file>